--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="National Universities" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liberal Arts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Public Universities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Christian Colleges" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="National Universities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liberal Arts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Public Universities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Christian Colleges" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status'!$A$1:$I$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -16,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -67,6 +70,9 @@
       <strike val="1"/>
       <color rgb="FF0000FF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -88,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -100,9 +106,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -113,6 +117,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,6 +392,549 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" style="19" min="1" max="1"/>
+    <col width="26" customWidth="1" style="19" min="2" max="2"/>
+    <col width="14" customWidth="1" style="19" min="3" max="3"/>
+    <col width="28" customWidth="1" style="19" min="4" max="4"/>
+    <col width="42" customWidth="1" style="19" min="5" max="5"/>
+    <col width="12" customWidth="1" style="19" min="6" max="6"/>
+    <col width="12" customWidth="1" style="19" min="7" max="7"/>
+    <col width="12" customWidth="1" style="19" min="8" max="8"/>
+    <col width="56" customWidth="1" style="19" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>site_key</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>machine</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>started</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>University of Chicago</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>The Chicago Maroon</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>chicago</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>chicagomaroon.com</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@chicago</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Northwestern University</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>The Daily Northwestern</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>northwestern</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>dailynorthwestern.com</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@northwestern</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>The Daily Campus</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>smu</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>smudailycampus.com</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@smu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>Texas Christian University</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>TCU 360</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>tcu</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>tcu360.com</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tcu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>Biola University</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>The Chimes</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>biola</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>chimesnewspaper.com</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@biola; high empty_body on old archive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Union College (NY)</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Concordiensis</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>concordiensis.com</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Finished: 1604 articles of 1626 URLs; 44 empty_body skipped. systemd exited 0 and stayed inactive (Restart=on-failure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@stolaf; near complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Connecticut College</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>The College Voice</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>conncoll</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>thecollegevoice.org</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>200-article test; not a full run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>Franklin &amp; Marshall College</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>The College Reporter</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>fandm</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>the-college-reporter.com</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>200-article test; not a full run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Hillsdale College</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>The Collegian</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>hillsdale</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>hillsdalecollegian.com</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>200-article test; not a full run yet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -422,12 +972,12 @@
       <c r="F1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Princeton University 🌿</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
@@ -439,12 +989,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
@@ -454,19 +1004,19 @@
           <t>https://thetech.com/</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Harvard 🌿</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
@@ -478,12 +1028,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Stanford University</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
@@ -495,12 +1045,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Yale Universty 🌿</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
@@ -512,12 +1062,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>University of Chicago</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
@@ -530,12 +1080,12 @@
       <c r="E7" s="9" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Duke University</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -547,12 +1097,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Johns Hopkins University</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -564,12 +1114,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Northwestern Univeristy</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -581,12 +1131,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Univeristy of Pennsylvania 🌿</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -598,12 +1148,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Cornell University 🌿</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
@@ -615,12 +1165,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Brown University 🌿</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -632,12 +1182,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Dartmouth College 🌿</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -649,12 +1199,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Columbia Univeristy 🌿</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
@@ -664,7 +1214,7 @@
           <t>https://www.columbiaspectator.com/</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>done</t>
         </is>
@@ -698,12 +1248,12 @@
       <c r="E17" s="18" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Rice University</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
@@ -734,12 +1284,12 @@
       <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Vanderbilt University</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>#17</t>
         </is>
@@ -751,12 +1301,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Carnegie Mellon Univeristy</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>#20</t>
         </is>
@@ -787,12 +1337,12 @@
       <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Univeristy of Notre Dame</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>#20</t>
         </is>
@@ -805,12 +1355,12 @@
       <c r="E23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Washington Univeristy in St. Louis</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>#20</t>
         </is>
@@ -822,12 +1372,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Emory University</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>#24</t>
         </is>
@@ -839,12 +1389,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Georgetown University</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>#24</t>
         </is>
@@ -856,12 +1406,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Univeristy of North Carolina, Chapel Hill</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>#26</t>
         </is>
@@ -873,12 +1423,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Univeristy of Virginia</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>#26</t>
         </is>
@@ -890,12 +1440,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>University of Southern California</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>#28</t>
         </is>
@@ -907,12 +1457,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Univeristy of California San Diego</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>#29</t>
         </is>
@@ -924,12 +1474,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Univeristy of Florida</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>#30</t>
         </is>
@@ -941,12 +1491,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>The University of Texas, Austin</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>#30</t>
         </is>
@@ -958,12 +1508,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Georgia Institute of Technology</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>#32</t>
         </is>
@@ -975,12 +1525,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>New York University</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>#32</t>
         </is>
@@ -992,12 +1542,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>University of California, Davis</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>#32</t>
         </is>
@@ -1009,12 +1559,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Univeristy of California, Irvine</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>#32</t>
         </is>
@@ -1026,12 +1576,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Boston College</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>#36</t>
         </is>
@@ -1043,12 +1593,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Tufts University</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>#36</t>
         </is>
@@ -1060,12 +1610,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>University of Illinois Urbana, Champaign</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>#36</t>
         </is>
@@ -1077,12 +1627,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>University of Wisconsin, Madison</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>#36</t>
         </is>
@@ -1094,12 +1644,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>University of California, Santa Barbara</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>#40</t>
         </is>
@@ -1111,12 +1661,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>The Ohio State University</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>#41</t>
         </is>
@@ -1128,12 +1678,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Boston University</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>#42</t>
         </is>
@@ -1145,12 +1695,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Rutgers University, New Brunswick</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>#42</t>
         </is>
@@ -1162,12 +1712,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>University of Maryland, College Park</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>#42</t>
         </is>
@@ -1179,12 +1729,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>University of Washington</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>#42</t>
         </is>
@@ -1196,12 +1746,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Lehigh University</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>#46</t>
         </is>
@@ -1213,12 +1763,12 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Northeastern University</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>#46</t>
         </is>
@@ -1230,12 +1780,12 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Purdue Univeristy</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>#46</t>
         </is>
@@ -1247,12 +1797,12 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>University of Georgia</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>#46</t>
         </is>
@@ -1264,12 +1814,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>University of Rochester</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>#46</t>
         </is>
@@ -1281,12 +1831,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Case Western Reserve University</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>#51</t>
         </is>
@@ -1298,12 +1848,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Florida State University</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>#51</t>
         </is>
@@ -1315,12 +1865,12 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Texas A&amp;M University</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>#51</t>
         </is>
@@ -1332,12 +1882,12 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Virginia Tech</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>#51</t>
         </is>
@@ -1349,12 +1899,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Wake Forest University</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>#51</t>
         </is>
@@ -1366,12 +1916,12 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>William &amp; Mary</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>#51</t>
         </is>
@@ -1383,12 +1933,12 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Univeristy of California, Merced</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>#57</t>
         </is>
@@ -1400,12 +1950,12 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Villanova University</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>#57</t>
         </is>
@@ -1417,12 +1967,12 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>George Washington University</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>#59</t>
         </is>
@@ -1434,12 +1984,12 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>The Pennsylvania State University, University Park</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>#59</t>
         </is>
@@ -1451,12 +2001,12 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>Santa Clara University</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>#59</t>
         </is>
@@ -1468,12 +2018,12 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>Stony Brook University, SUNY</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>#59</t>
         </is>
@@ -1485,12 +2035,12 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>#59</t>
         </is>
@@ -1502,12 +2052,12 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Michigan State University</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>#64</t>
         </is>
@@ -1519,12 +2069,12 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>North Carolina State University</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>#64</t>
         </is>
@@ -1536,12 +2086,12 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>#64</t>
         </is>
@@ -1553,12 +2103,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>University of Massachusetts, Amherst</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>#64</t>
         </is>
@@ -1570,12 +2120,12 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>University of Miami</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>#64</t>
         </is>
@@ -1587,12 +2137,12 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>Brandeis University</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>#69</t>
         </is>
@@ -1604,12 +2154,12 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Tulane University of Louisiana </t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>#69</t>
         </is>
@@ -1621,12 +2171,12 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>University of Connecticut</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>#69</t>
         </is>
@@ -1638,12 +2188,12 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>University of Pittsburgh</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>#69</t>
         </is>
@@ -1655,12 +2205,12 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>Binghamton University, SUNY</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>#73</t>
         </is>
@@ -1672,12 +2222,12 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>Indiana University, Bloomington</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>#73</t>
         </is>
@@ -1689,12 +2239,12 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>Clemson University</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>#75</t>
         </is>
@@ -1706,12 +2256,12 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>Rutgers University, Newark</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>#75</t>
         </is>
@@ -1723,12 +2273,12 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>Syracuse University</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>#75</t>
         </is>
@@ -1740,12 +2290,12 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>University at Buffalo, SUNY</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>#75</t>
         </is>
@@ -1757,12 +2307,12 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>University of California, Riverside</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>#75</t>
         </is>
@@ -1774,12 +2324,12 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Colorado School of Mines</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>#80</t>
         </is>
@@ -1791,12 +2341,12 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Drexel University </t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>#80</t>
         </is>
@@ -1808,12 +2358,12 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>New Jersy Institute of Technology</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>#80</t>
         </is>
@@ -1825,12 +2375,12 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Stevens Institute of Technology</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>#80</t>
         </is>
@@ -1842,12 +2392,12 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>Pepperdine University</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
@@ -1859,12 +2409,12 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>University of Illinois Chicago</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
@@ -1876,12 +2426,12 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
@@ -1893,12 +2443,12 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>Yashiva University</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
@@ -1910,12 +2460,12 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>American University</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -1927,12 +2477,12 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>Baylor University</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -1944,12 +2494,12 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>Howard University</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -1961,12 +2511,12 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>Marquette University</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -1978,12 +2528,12 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>Rochester Institute of Technology</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -1995,12 +2545,12 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>Southern Methodist University</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -2012,12 +2562,12 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>University of California Santa Cruz</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -2029,12 +2579,12 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>University of Delaware</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -2046,12 +2596,12 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>University of South Florida</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
@@ -2063,12 +2613,12 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>Florida International University</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>#97</t>
         </is>
@@ -2080,12 +2630,12 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>Fordham University</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>#97</t>
         </is>
@@ -2097,12 +2647,12 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>Rutgers University, Camden</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr">
         <is>
           <t>#97</t>
         </is>
@@ -2114,12 +2664,12 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Texas Christian University </t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>#97</t>
         </is>
@@ -2131,12 +2681,12 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>University of Colorado Boulder</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>#97</t>
         </is>
@@ -2148,12 +2698,12 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>Auburn University</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>#102</t>
         </is>
@@ -2273,7 +2823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2304,12 +2854,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Williams College</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
@@ -2321,12 +2871,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Amherst College</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
@@ -2338,12 +2888,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>United States Naval Academy</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
@@ -2355,12 +2905,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Swarthmore College</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
@@ -2372,12 +2922,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Bowdoin College</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
@@ -2389,29 +2939,29 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>United States Air Force Academy</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Claremont McKenna College</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -2423,12 +2973,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Pomona College</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -2440,12 +2990,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Wellesley College</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -2457,12 +3007,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Carleton College</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
@@ -2474,12 +3024,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Harvey Mudd College</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
@@ -2491,29 +3041,29 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">United States Military Academy at West Point </t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Barnard College</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2525,12 +3075,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Davidson College</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2542,12 +3092,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Grinnell College</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2559,12 +3109,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Hamilton College</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2576,12 +3126,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Middlebury College</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2593,12 +3143,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Smith College</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2610,12 +3160,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Vassar College</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2628,12 +3178,12 @@
       <c r="E20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Wesleyan University</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2645,12 +3195,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Washington and Lee Univeristy</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -2667,12 +3217,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Colgate Univeristy</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>#22</t>
         </is>
@@ -2684,12 +3234,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Univeristy of Richmond</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>#22</t>
         </is>
@@ -2701,12 +3251,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Bates College</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>#24</t>
         </is>
@@ -2718,12 +3268,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Colby College</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>#24</t>
         </is>
@@ -2735,12 +3285,12 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Haverford College</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>#24</t>
         </is>
@@ -2752,12 +3302,12 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>College of the Holy Cross</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>#27</t>
         </is>
@@ -2769,12 +3319,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Macalester College</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>#28</t>
         </is>
@@ -2786,12 +3336,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Mount Holyoke College</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>#29</t>
         </is>
@@ -2803,12 +3353,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Bryn Mawr College</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>#30</t>
         </is>
@@ -2820,12 +3370,12 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Bucknell University</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>#30</t>
         </is>
@@ -2837,12 +3387,12 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Colorado College</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>#30</t>
         </is>
@@ -2854,12 +3404,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Lafayette College</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>#30</t>
         </is>
@@ -2871,12 +3421,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Denison University</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>#34</t>
         </is>
@@ -2888,12 +3438,12 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Franklin &amp; Marshell College</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>#35</t>
         </is>
@@ -2905,12 +3455,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Occidental College</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>#35</t>
         </is>
@@ -2922,12 +3472,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Pitzer College </t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>#37</t>
         </is>
@@ -2939,12 +3489,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Scripps College</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>#37</t>
         </is>
@@ -2956,12 +3506,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Skidmore College</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>#37</t>
         </is>
@@ -2973,12 +3523,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Soka Univeristy of America</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>#37</t>
         </is>
@@ -2990,12 +3540,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Spelman College</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>#37</t>
         </is>
@@ -3007,12 +3557,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Trinity College</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>#37</t>
         </is>
@@ -3024,12 +3574,12 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Trinity University </t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>#37</t>
         </is>
@@ -3041,12 +3591,12 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Union College</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>#44</t>
         </is>
@@ -3058,12 +3608,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Berea College</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>#45</t>
         </is>
@@ -3075,12 +3625,12 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Dickinson College</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>#45</t>
         </is>
@@ -3092,12 +3642,12 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Furman Univeristy</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>#45</t>
         </is>
@@ -3109,12 +3659,12 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Kenyon College</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>#45</t>
         </is>
@@ -3126,12 +3676,12 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>The Univeristy of the South</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>#45</t>
         </is>
@@ -3143,12 +3693,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Connecticut College</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>#50</t>
         </is>
@@ -3160,12 +3710,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Hillsdale College</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>#50</t>
         </is>
@@ -3177,612 +3727,612 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>St. Olaf College</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>#50</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Wabash College</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>#50</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Wheaton College</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>#50</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Centre College</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>#55</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Rhodes College</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>#55</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Thomas Aquinas College</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>#55</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>DePauw University</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>#58</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Gettysburg College</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>#58</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Oberlin College</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>#58</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">St. Lawrence University </t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>#58</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>Whitman College</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>#58</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>Principia College</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>#63</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Reed College</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>#63</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>Lawrence University</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>#65</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Virginia Military Institute</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>#65</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>Agnes Scott College</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>#67</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>Kalamazoo College</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>#67</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>Wofford College</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>#67</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>Bard College</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>#70</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>Gustavus Adolphus College</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>#70</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>Muhlenberg College</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>#70</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">College of St. Benedict </t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>#73</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>Hobart and William Smith Colleges</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>#73</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>Lake Forest College</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>#75</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>Allegheny College</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>#76</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>The College of Wooster</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>#76</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>Earlham College</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>#76</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>Knox College</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>#76</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Wheaton College</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>#76</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Willamette University</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>#76</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>Saint Johns University</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>#82</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Stonehill College</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>#82</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>Austin College</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Drew University </t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">#84 </t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>Hope College</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>Saint Mary's College</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Southwestern Univeristy </t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>St. John's College (MD)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>Ursinus College</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>Washington &amp; Jefferson College</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>#84</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>Beloit College</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>#92</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>Juniata College</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>#92</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>Washington College</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>#92</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>Whittier College</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>#92</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>Augustana College</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>Lewis &amp; Clark College</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>Lycoming College</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>Morehouse College</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="9" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>Randolph-Macon College</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>Saint Anselm College</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="9" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>St. Mary's College of Maryland</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
@@ -3845,7 +4395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3881,7 +4431,7 @@
           <t>University of California, Berkeley</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
@@ -3894,12 +4444,12 @@
       <c r="D2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>University of California, Los Angeles</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
@@ -3916,7 +4466,7 @@
           <t>University of Michigan--Ann Arbor</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
@@ -3933,7 +4483,7 @@
           <t>University of North Carolina--Chapel Hill</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
@@ -3945,12 +4495,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>University of Virginia</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
@@ -3962,12 +4512,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>University of California San Diego</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
@@ -3979,12 +4529,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>University of Florida</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -4001,7 +4551,7 @@
           <t>The University of Texas--Austin</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
@@ -4013,12 +4563,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Georgia Institute of Technology</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">#9 </t>
         </is>
@@ -4035,7 +4585,7 @@
           <t>University of California, Davis</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">#9 </t>
         </is>
@@ -4052,7 +4602,7 @@
           <t>University of California, Irvine</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">#9 </t>
         </is>
@@ -4064,12 +4614,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
@@ -4081,12 +4631,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>University of Wisconsin--Madison</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
@@ -4098,12 +4648,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>University of California, Santa Barbara</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
@@ -4120,7 +4670,7 @@
           <t>The Ohio State University</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
@@ -4132,12 +4682,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Rutgers University--New Brunswick</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>#16</t>
         </is>
@@ -4154,7 +4704,7 @@
           <t>University of Maryland, College Park</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>#16</t>
         </is>
@@ -4166,12 +4716,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>University of Washington</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>#16</t>
         </is>
@@ -4183,12 +4733,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Purdue University--Main Campus</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>#19</t>
         </is>
@@ -4200,12 +4750,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>University of Georgia</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>#19</t>
         </is>
@@ -4244,7 +4794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4275,12 +4825,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Texas Christian University </t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
@@ -4292,12 +4842,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Southern Methodist Univeristy </t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
@@ -4309,12 +4859,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>College of the Ozarks</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
@@ -4326,12 +4876,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>St. Olaf College</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
@@ -4343,12 +4893,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Oklahoma City Univeristy </t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
@@ -4360,12 +4910,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Wheaton College--Illinois</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
@@ -4377,29 +4927,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Moody Bible Institute</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Newspaper was the "The Moody Standard" but was discontinued in 2019</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Harding Univeristy </t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
@@ -4411,12 +4961,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Biola Univeristy </t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
@@ -4428,12 +4978,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Union Univeristy</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
@@ -4445,12 +4995,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Hope College</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
@@ -4462,12 +5012,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Baylor Univeristy</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
@@ -4479,12 +5029,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Lipscomb Univeristy</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
@@ -4496,12 +5046,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Point Loma Nazarene Univeristy</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
@@ -4513,12 +5063,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>California Baptist University</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
@@ -4530,12 +5080,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Cedarville University</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>#16</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Christian Colleges" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -120,6 +120,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -395,7 +396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="19" min="1" max="1"/>
@@ -406,7 +407,8 @@
     <col width="12" customWidth="1" style="19" min="6" max="6"/>
     <col width="12" customWidth="1" style="19" min="7" max="7"/>
     <col width="12" customWidth="1" style="19" min="8" max="8"/>
-    <col width="56" customWidth="1" style="19" min="9" max="9"/>
+    <col width="12" customWidth="1" style="19" min="9" max="9"/>
+    <col width="64" customWidth="1" style="19" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,15 +444,20 @@
       </c>
       <c r="G1" s="20" t="inlineStr">
         <is>
+          <t>articles</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
           <t>machine</t>
         </is>
       </c>
-      <c r="H1" s="20" t="inlineStr">
+      <c r="I1" s="20" t="inlineStr">
         <is>
           <t>started</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="J1" s="20" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -487,17 +494,17 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>newspaper-scraper@chicago</t>
         </is>
@@ -534,17 +541,17 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>newspaper-scraper@northwestern</t>
         </is>
@@ -581,17 +588,17 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>newspaper-scraper@smu</t>
         </is>
@@ -628,17 +635,17 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>newspaper-scraper@tcu</t>
         </is>
@@ -675,19 +682,19 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G6" s="0" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H6" s="0" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@biola; high empty_body on old archive</t>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@biola; resumed after href crash fix</t>
         </is>
       </c>
     </row>
@@ -722,19 +729,22 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G7" s="0" t="inlineStr">
+      <c r="G7" s="21" t="n">
+        <v>1604</v>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="I7" s="0" t="inlineStr">
-        <is>
-          <t>Finished: 1604 articles of 1626 URLs; 44 empty_body skipped. systemd exited 0 and stayed inactive (Restart=on-failure).</t>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Finished. 1604 articles (44 empty_body skipped). Downloaded separately if needed.</t>
         </is>
       </c>
     </row>
@@ -766,22 +776,25 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@stolaf; near complete</t>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); rest empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
         </is>
       </c>
     </row>
@@ -813,22 +826,22 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>testing</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>200-article test; not a full run yet</t>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@conncoll full run</t>
         </is>
       </c>
     </row>
@@ -860,22 +873,22 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>testing</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>200-article test; not a full run yet</t>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@fandm full run</t>
         </is>
       </c>
     </row>
@@ -907,27 +920,168 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@hillsdale full run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>testing</t>
         </is>
       </c>
-      <c r="G11" s="0" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>200-article test; not a full run yet</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Occidental College</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Occidental</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>occidental</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>theoccidentalnews.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>200-article test; not a full run yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Lipscomb University</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lipscomb Media</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lipscomb</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lipscombmedia.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>200-article test; not a full run yet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
+  <autoFilter ref="A1:J14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -494,6 +494,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G2" s="21" t="n">
+        <v>14400</v>
+      </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -506,7 +509,7 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@chicago</t>
+          <t>newspaper-scraper@chicago; 14400/22493 at last check</t>
         </is>
       </c>
     </row>
@@ -541,6 +544,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G3" s="21" t="n">
+        <v>17400</v>
+      </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -553,7 +559,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@northwestern</t>
+          <t>newspaper-scraper@northwestern; 17400/70720; 403s still 32</t>
         </is>
       </c>
     </row>
@@ -588,6 +594,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G4" s="21" t="n">
+        <v>8800</v>
+      </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -600,7 +609,7 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@smu</t>
+          <t>newspaper-scraper@smu; 8800/26572 at last check</t>
         </is>
       </c>
     </row>
@@ -635,6 +644,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G5" s="21" t="n">
+        <v>8546</v>
+      </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -647,7 +659,7 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tcu</t>
+          <t>newspaper-scraper@tcu; 8546/26172 at last check</t>
         </is>
       </c>
     </row>
@@ -682,6 +694,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G6" s="21" t="n">
+        <v>5150</v>
+      </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -694,7 +709,7 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@biola; resumed after href crash fix</t>
+          <t>newspaper-scraper@biola; 5150/11390 after href fix</t>
         </is>
       </c>
     </row>
@@ -744,7 +759,7 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t>Finished. 1604 articles (44 empty_body skipped). Downloaded separately if needed.</t>
+          <t>Finished. 1604 articles of 1626 URLs; 44 empty_body skipped.</t>
         </is>
       </c>
     </row>
@@ -794,7 +809,7 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); rest empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
         </is>
       </c>
     </row>
@@ -829,6 +844,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G9" s="21" t="n">
+        <v>3098</v>
+      </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -841,7 +859,7 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@conncoll full run</t>
+          <t>newspaper-scraper@conncoll; 3098/4320 at last check</t>
         </is>
       </c>
     </row>
@@ -876,6 +894,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G10" s="21" t="n">
+        <v>1946</v>
+      </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -888,7 +909,7 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@fandm full run</t>
+          <t>newspaper-scraper@fandm; 1946/3583 at last check</t>
         </is>
       </c>
     </row>
@@ -923,6 +944,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G11" s="21" t="n">
+        <v>3393</v>
+      </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -935,148 +959,157 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@hillsdale full run</t>
+          <t>newspaper-scraper@hillsdale; 3393/15690 at last check</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>Swarthmore College</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>The Phoenix</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>swarthmore</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>swarthmorephoenix.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>200-article test; not a full run yet</t>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>200-test wrote 0: first 200 URLs were 1998 (pre-2000 skip). Wait for URL-skip fix before full run.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>Occidental College</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>The Occidental</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>occidental</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>theoccidentalnews.com</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="n">
+        <v>183</v>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>200-article test; not a full run yet</t>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>200-test done: 183 articles. Ready for systemd full run.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>Lipscomb University</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Lipscomb Media</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>lipscomb</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>lipscombmedia.com</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>testing</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="G14" t="n">
+        <v>186</v>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>200-article test; not a full run yet</t>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>200-test done: 186 articles. Ready for systemd full run.</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Arial"/>
@@ -94,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -121,6 +123,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,7 +402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="19" min="1" max="1"/>
@@ -495,7 +501,7 @@
         </is>
       </c>
       <c r="G2" s="21" t="n">
-        <v>14400</v>
+        <v>20750</v>
       </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
@@ -509,7 +515,7 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@chicago; 14400/22493 at last check</t>
+          <t>newspaper-scraper@chicago; 20750/22493 at 2026-09-28 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -545,7 +551,7 @@
         </is>
       </c>
       <c r="G3" s="21" t="n">
-        <v>17400</v>
+        <v>21000</v>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
@@ -559,7 +565,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@northwestern; 17400/70720; 403s still 32</t>
+          <t>newspaper-scraper@northwestern; 21000/70720 at 2026-09-28 15:48 UTC; 403s still 32, network_error=1083</t>
         </is>
       </c>
     </row>
@@ -595,7 +601,7 @@
         </is>
       </c>
       <c r="G4" s="21" t="n">
-        <v>8800</v>
+        <v>12650</v>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
@@ -609,7 +615,7 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@smu; 8800/26572 at last check</t>
+          <t>newspaper-scraper@smu; 12650/26572 at 2026-09-28 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -645,7 +651,7 @@
         </is>
       </c>
       <c r="G5" s="21" t="n">
-        <v>8546</v>
+        <v>12296</v>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
@@ -659,7 +665,7 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tcu; 8546/26172 at last check</t>
+          <t>newspaper-scraper@tcu; 12296/26172 at 2026-09-28 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -695,7 +701,7 @@
         </is>
       </c>
       <c r="G6" s="21" t="n">
-        <v>5150</v>
+        <v>9000</v>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
@@ -709,7 +715,7 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@biola; 5150/11390 after href fix</t>
+          <t>newspaper-scraper@biola; 9000/11390 at 2026-09-28 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -841,11 +847,11 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G9" s="21" t="n">
-        <v>3098</v>
+        <v>4039</v>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
@@ -859,7 +865,7 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@conncoll; 3098/4320 at last check</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
         </is>
       </c>
     </row>
@@ -891,11 +897,11 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G10" s="21" t="n">
-        <v>1946</v>
+        <v>3449</v>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
@@ -909,7 +915,7 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@fandm; 1946/3583 at last check</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
         </is>
       </c>
     </row>
@@ -945,7 +951,7 @@
         </is>
       </c>
       <c r="G11" s="21" t="n">
-        <v>3393</v>
+        <v>9793</v>
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
@@ -959,7 +965,7 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@hillsdale; 3393/15690 at last check</t>
+          <t>newspaper-scraper@hillsdale; 9793/15690 at 2026-09-28 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -991,11 +997,11 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>testing</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
@@ -1009,7 +1015,7 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>200-test wrote 0: first 200 URLs were 1998 (pre-2000 skip). Wait for URL-skip fix before full run.</t>
+          <t>newspaper-scraper@swarthmore; 700/13251 at 2026-09-28 15:48 UTC; pre_2000 skip working (578 skipped)</t>
         </is>
       </c>
     </row>
@@ -1041,11 +1047,11 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>testing</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>183</v>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>783</v>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
@@ -1059,7 +1065,7 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>200-test done: 183 articles. Ready for systemd full run.</t>
+          <t>newspaper-scraper@occidental; 783/10055 at 2026-09-28 15:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1091,11 +1097,11 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>testing</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>186</v>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>682</v>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
@@ -1109,7 +1115,191 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>200-test done: 186 articles. Ready for systemd full run.</t>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Michigan Daily</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>michigan</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>michigandaily.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Wave 4. Open WordPress. Probe + 200-test before full run. ~120k URLs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>University of California, Irvine</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>New University</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>newuniversity.org</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Wave 4. Open WordPress. 200-test required: recon empty on 2003-04 URLs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>University of Miami</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Miami Hurricane</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>miami</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>themiamihurricane.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Wave 4. Open WordPress behind Sucuri. Probe + 200-test before full run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Reporter</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>rit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>reporter.rit.edu</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Wave 4. Open SNO, Crawl-delay 6. Probe + 200-test before full run.</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -9,19 +9,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Public Universities" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Christian Colleges" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status'!$A$1:$J$14</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -75,8 +74,18 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +98,11 @@
         <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F4F6F"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -96,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -127,6 +141,38 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,909 +448,1052 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="19" min="1" max="1"/>
+    <col width="34" customWidth="1" style="19" min="1" max="1"/>
     <col width="26" customWidth="1" style="19" min="2" max="2"/>
     <col width="14" customWidth="1" style="19" min="3" max="3"/>
     <col width="28" customWidth="1" style="19" min="4" max="4"/>
-    <col width="42" customWidth="1" style="19" min="5" max="5"/>
+    <col width="44" customWidth="1" style="19" min="5" max="5"/>
     <col width="12" customWidth="1" style="19" min="6" max="6"/>
     <col width="12" customWidth="1" style="19" min="7" max="7"/>
     <col width="12" customWidth="1" style="19" min="8" max="8"/>
     <col width="12" customWidth="1" style="19" min="9" max="9"/>
-    <col width="64" customWidth="1" style="19" min="10" max="10"/>
+    <col width="80" customWidth="1" style="19" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>university</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>paper</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>site_key</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F1" s="20" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G1" s="20" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>articles</t>
         </is>
       </c>
-      <c r="H1" s="20" t="inlineStr">
+      <c r="H1" s="24" t="inlineStr">
         <is>
           <t>machine</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="I1" s="24" t="inlineStr">
         <is>
           <t>started</t>
         </is>
       </c>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="n"/>
+      <c r="C2" s="32" t="n"/>
+      <c r="D2" s="32" t="n"/>
+      <c r="E2" s="32" t="n"/>
+      <c r="F2" s="32" t="n"/>
+      <c r="G2" s="32" t="n"/>
+      <c r="H2" s="32" t="n"/>
+      <c r="I2" s="32" t="n"/>
+      <c r="J2" s="32" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Rochester Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Reporter</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>rit</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>reporter.rit.edu</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G3" s="30" t="n">
+        <v>2137</v>
+      </c>
+      <c r="H3" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J3" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 2137 articles of 2140 URLs (99.9%); 5 empty_body. systemd inactive. File: ~/Downloads/rit.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>University of Chicago</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>The Chicago Maroon</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t>chicago</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>chicagomaroon.com</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>National Universities</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="n">
+        <v>22117</v>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I4" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J4" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 22117 articles of 22493 URLs (98.3%); 371 empty_body, 2 http_301, 3 http_404. systemd inactive. File: ~/Downloads/chicago.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>Northwestern University</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Northwestern</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>northwestern</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>dailynorthwestern.com</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G2" s="21" t="n">
-        <v>20750</v>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="J5" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@northwestern; 403s still present at last check</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>University of Miami</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>The Miami Hurricane</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>miami</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>themiamihurricane.com</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J6" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@miami; full run started 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>University of California, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>City on a Hill Press</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>ucsc</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>cityonahillpress.com</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="n"/>
+      <c r="H7" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J7" s="34" t="inlineStr">
+        <is>
+          <t>Wave 5. Open WordPress. Probe + 200-test before full run. ~7k URLs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Public Universities</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="32" t="n"/>
+      <c r="J8" s="32" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>University of California, Irvine</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>New University</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>newuniversity.org</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J9" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@uci; full run started 2026-09-28 after td-post-content fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>The Michigan Daily</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>michigan</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>michigandaily.com</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J10" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@michigan; full run started 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Connecticut College</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>The College Voice</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>conncoll</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>thecollegevoice.org</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>4039</v>
+      </c>
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J12" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Franklin &amp; Marshall College</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>The College Reporter</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>fandm</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>the-college-reporter.com</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>3449</v>
+      </c>
+      <c r="H13" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J13" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H14" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J14" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Union College (NY)</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Concordiensis</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>concordiensis.com</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>1604</v>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J15" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 1604 articles of 1626 URLs; 44 empty_body skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Hillsdale College</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>The Collegian</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>hillsdale</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>hillsdalecollegian.com</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G16" s="33" t="n"/>
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J16" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@hillsdale</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>Occidental College</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>The Occidental</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>occidental</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>theoccidentalnews.com</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J17" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@occidental</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G18" s="33" t="n"/>
+      <c r="H18" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J18" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@swarthmore; pre-2000 permalinks skipped without fetch</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="32" t="n"/>
+      <c r="J19" s="32" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Lipscomb University</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>Lipscomb Media</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>lipscomb</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>lipscombmedia.com</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>682</v>
+      </c>
+      <c r="H20" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I20" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J20" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>Biola University</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>The Chimes</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>biola</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>chimesnewspaper.com</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="n"/>
+      <c r="H21" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I21" s="33" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@chicago; 20750/22493 at 2026-09-28 15:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>Northwestern University</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>The Daily Northwestern</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>northwestern</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>dailynorthwestern.com</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>National Universities</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="J21" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@biola; recovered after href fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Campus</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>smu</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>smudailycampus.com</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G3" s="21" t="n">
-        <v>21000</v>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I3" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="J3" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@northwestern; 21000/70720 at 2026-09-28 15:48 UTC; 403s still 32, network_error=1083</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>Southern Methodist University</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>The Daily Campus</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>smu</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>smudailycampus.com</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J22" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@smu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>Texas Christian University</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>TCU 360</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>tcu</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>tcu360.com</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G4" s="21" t="n">
-        <v>12650</v>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="G23" s="33" t="n"/>
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@smu; 12650/26572 at 2026-09-28 15:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>Texas Christian University</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>TCU 360</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>tcu</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>tcu360.com</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>Christian Colleges | National Universities</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>12296</v>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="J23" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tcu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>Point Loma Nazarene University</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Loma Beat</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat.com</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J5" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@tcu; 12296/26172 at 2026-09-28 15:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I6" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J6" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@biola; 9000/11390 at 2026-09-28 15:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>Union College (NY)</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>Concordiensis</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>union</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>concordiensis.com</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>1604</v>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J7" s="0" t="inlineStr">
-        <is>
-          <t>Finished. 1604 articles of 1626 URLs; 44 empty_body skipped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>St. Olaf College</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>Manitou Messenger</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>stolaf</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>olafmessenger.com</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>Christian Colleges | Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>5048</v>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="inlineStr">
-        <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J9" s="0" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>Franklin &amp; Marshall College</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>The College Reporter</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>fandm</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>the-college-reporter.com</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>3449</v>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="inlineStr">
-        <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>Hillsdale College</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>The Collegian</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>hillsdale</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>hillsdalecollegian.com</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>9793</v>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@hillsdale; 9793/15690 at 2026-09-28 15:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>Swarthmore College</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>The Phoenix</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>swarthmore</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="inlineStr">
-        <is>
-          <t>swarthmorephoenix.com</t>
-        </is>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>700</v>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J12" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@swarthmore; 700/13251 at 2026-09-28 15:48 UTC; pre_2000 skip working (578 skipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>Occidental College</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>The Occidental</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>occidental</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t>theoccidentalnews.com</t>
-        </is>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>783</v>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J13" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@occidental; 783/10055 at 2026-09-28 15:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>682</v>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J14" s="0" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>University of Michigan</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>The Michigan Daily</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>michigan</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>michigandaily.com</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I15" s="23" t="n">
+      <c r="I24" s="35" t="n">
         <v>46293</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Wave 4. Open WordPress. Probe + 200-test before full run. ~120k URLs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>University of California, Irvine</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>New University</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>uci</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>newuniversity.org</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I16" s="23" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Wave 4. Open WordPress. 200-test required: recon empty on 2003-04 URLs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>University of Miami</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The Miami Hurricane</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>miami</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>themiamihurricane.com</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>National Universities</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I17" s="23" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Wave 4. Open WordPress behind Sucuri. Probe + 200-test before full run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Rochester Institute of Technology</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Reporter</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>reporter.rit.edu</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>National Universities</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I18" s="23" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Wave 4. Open SNO, Crawl-delay 6. Probe + 200-test before full run.</t>
+      <c r="J24" s="34" t="inlineStr">
+        <is>
+          <t>Wave 5. Open WordPress. Probe + 200-test before full run. ~4k URLs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -680,22 +680,22 @@
     <row r="6">
       <c r="A6" s="33" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>The Miami Hurricane</t>
+          <t>City on a Hill Press</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>miami</t>
+          <t>ucsc</t>
         </is>
       </c>
       <c r="D6" s="33" t="inlineStr">
         <is>
-          <t>themiamihurricane.com</t>
+          <t>cityonahillpress.com</t>
         </is>
       </c>
       <c r="E6" s="33" t="inlineStr">
@@ -719,29 +719,29 @@
       </c>
       <c r="J6" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@miami; full run started 2026-09-28</t>
+          <t>newspaper-scraper@ucsc; full run started 2026-09-28 after 200-row 200-test</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>City on a Hill Press</t>
+          <t>The Miami Hurricane</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>ucsc</t>
+          <t>miami</t>
         </is>
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
-          <t>cityonahillpress.com</t>
+          <t>themiamihurricane.com</t>
         </is>
       </c>
       <c r="E7" s="33" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="F7" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G7" s="33" t="n"/>
@@ -765,91 +765,91 @@
       </c>
       <c r="J7" s="34" t="inlineStr">
         <is>
-          <t>Wave 5. Open WordPress. Probe + 200-test before full run. ~7k URLs.</t>
+          <t>newspaper-scraper@miami; full run started 2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>University of South Florida</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>The Oracle</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>usf</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>usforacle.com</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J8" s="34" t="inlineStr">
+        <is>
+          <t>Wave 5. Open WordPress. Probe + 200-test before full run. ~32k URLs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Public Universities</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>University of California, Irvine</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>New University</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="inlineStr">
-        <is>
-          <t>uci</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>newuniversity.org</t>
-        </is>
-      </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I9" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J9" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@uci; full run started 2026-09-28 after td-post-content fix</t>
-        </is>
-      </c>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
+      <c r="E9" s="32" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="32" t="n"/>
+      <c r="J9" s="32" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>The Michigan Daily</t>
+          <t>New University</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>michigan</t>
+          <t>uci</t>
         </is>
       </c>
       <c r="D10" s="33" t="inlineStr">
         <is>
-          <t>michigandaily.com</t>
+          <t>newuniversity.org</t>
         </is>
       </c>
       <c r="E10" s="33" t="inlineStr">
@@ -873,95 +873,91 @@
       </c>
       <c r="J10" s="34" t="inlineStr">
         <is>
+          <t>newspaper-scraper@uci; full run started 2026-09-28 after td-post-content fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>The Michigan Daily</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>michigan</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>michigandaily.com</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="n"/>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J11" s="34" t="inlineStr">
+        <is>
           <t>newspaper-scraper@michigan; full run started 2026-09-28</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n"/>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="32" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D12" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E12" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G12" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I12" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J12" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
-        </is>
-      </c>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>Franklin &amp; Marshall College</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>The College Reporter</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>fandm</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>the-college-reporter.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
@@ -975,7 +971,7 @@
         </is>
       </c>
       <c r="G13" s="30" t="n">
-        <v>3449</v>
+        <v>4039</v>
       </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
@@ -989,34 +985,34 @@
       </c>
       <c r="J13" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Liberal Arts</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -1025,7 +1021,7 @@
         </is>
       </c>
       <c r="G14" s="30" t="n">
-        <v>5048</v>
+        <v>3449</v>
       </c>
       <c r="H14" s="33" t="inlineStr">
         <is>
@@ -1039,127 +1035,129 @@
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J15" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
           <t>Union College (NY)</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Concordiensis</t>
         </is>
       </c>
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>union</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>concordiensis.com</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G16" s="30" t="n">
         <v>1604</v>
       </c>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I15" s="33" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="J15" s="34" t="inlineStr">
+      <c r="J16" s="34" t="inlineStr">
         <is>
           <t>Finished. 1604 articles of 1626 URLs; 44 empty_body skipped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>Hillsdale College</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>The Collegian</t>
-        </is>
-      </c>
-      <c r="C16" s="33" t="inlineStr">
-        <is>
-          <t>hillsdale</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>hillsdalecollegian.com</t>
-        </is>
-      </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F16" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G16" s="33" t="n"/>
-      <c r="H16" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I16" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J16" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@hillsdale</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>Occidental College</t>
+          <t>Hillsdale College</t>
         </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>The Occidental</t>
+          <t>The Collegian</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>occidental</t>
+          <t>hillsdale</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
         <is>
-          <t>theoccidentalnews.com</t>
+          <t>hillsdalecollegian.com</t>
         </is>
       </c>
       <c r="E17" s="33" t="inlineStr">
@@ -1185,29 +1183,29 @@
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@occidental</t>
+          <t>newspaper-scraper@hillsdale</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="inlineStr">
         <is>
-          <t>Swarthmore College</t>
+          <t>Occidental College</t>
         </is>
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>The Phoenix</t>
+          <t>The Occidental</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>swarthmore</t>
+          <t>occidental</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
         <is>
-          <t>swarthmorephoenix.com</t>
+          <t>theoccidentalnews.com</t>
         </is>
       </c>
       <c r="E18" s="33" t="inlineStr">
@@ -1233,196 +1231,198 @@
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
+          <t>newspaper-scraper@occidental</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="n"/>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J19" s="34" t="inlineStr">
+        <is>
           <t>newspaper-scraper@swarthmore; pre-2000 permalinks skipped without fetch</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="32" t="n"/>
-      <c r="G19" s="32" t="n"/>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="32" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="32" t="n"/>
+      <c r="H20" s="32" t="n"/>
+      <c r="I20" s="32" t="n"/>
+      <c r="J20" s="32" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Biola University</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>The Chimes</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>biola</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>chimesnewspaper.com</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>11331</v>
+      </c>
+      <c r="H21" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I21" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J21" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Lipscomb University</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Lipscomb Media</t>
         </is>
       </c>
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>lipscomb</t>
         </is>
       </c>
-      <c r="D20" s="33" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>lipscombmedia.com</t>
         </is>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G22" s="30" t="n">
         <v>682</v>
       </c>
-      <c r="H20" s="33" t="inlineStr">
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I20" s="33" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="J20" s="34" t="inlineStr">
+      <c r="J22" s="34" t="inlineStr">
         <is>
           <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E21" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F21" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G21" s="33" t="n"/>
-      <c r="H21" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I21" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J21" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@biola; recovered after href fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>Southern Methodist University</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>The Daily Campus</t>
-        </is>
-      </c>
-      <c r="C22" s="33" t="inlineStr">
-        <is>
-          <t>smu</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>smudailycampus.com</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges | National Universities</t>
-        </is>
-      </c>
-      <c r="F22" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G22" s="33" t="n"/>
-      <c r="H22" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I22" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J22" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@smu</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="33" t="inlineStr">
         <is>
-          <t>Texas Christian University</t>
+          <t>Point Loma Nazarene University</t>
         </is>
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>TCU 360</t>
+          <t>Loma Beat</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>tcu</t>
+          <t>lomabeat</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
-          <t>tcu360.com</t>
+          <t>lomabeat.com</t>
         </is>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | National Universities</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F23" s="33" t="inlineStr">
@@ -1436,46 +1436,44 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I23" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
+      <c r="I23" s="35" t="n">
+        <v>46293</v>
       </c>
       <c r="J23" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tcu</t>
+          <t>newspaper-scraper@lomabeat; full run started 2026-09-28 after 196-row 200-test</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>Point Loma Nazarene University</t>
+          <t>Southern Methodist University</t>
         </is>
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>Loma Beat</t>
+          <t>The Daily Campus</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>lomabeat</t>
+          <t>smu</t>
         </is>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
-          <t>lomabeat.com</t>
+          <t>smudailycampus.com</t>
         </is>
       </c>
       <c r="E24" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges</t>
+          <t>Christian Colleges | National Universities</t>
         </is>
       </c>
       <c r="F24" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G24" s="33" t="n"/>
@@ -1484,12 +1482,62 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I24" s="35" t="n">
-        <v>46293</v>
+      <c r="I24" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
       </c>
       <c r="J24" s="34" t="inlineStr">
         <is>
-          <t>Wave 5. Open WordPress. Probe + 200-test before full run. ~4k URLs.</t>
+          <t>newspaper-scraper@smu</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>Texas Christian University</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>TCU 360</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>tcu</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>tcu360.com</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G25" s="33" t="n"/>
+      <c r="H25" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J25" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tcu</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -797,7 +797,7 @@
       </c>
       <c r="F8" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G8" s="33" t="n"/>
@@ -811,91 +811,91 @@
       </c>
       <c r="J8" s="34" t="inlineStr">
         <is>
-          <t>Wave 5. Open WordPress. Probe + 200-test before full run. ~32k URLs.</t>
+          <t>newspaper-scraper@usf; full run started 2026-09-28 after 199-row 200-test</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>Yeshiva University</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>The Commentator</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>yu</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>yucommentator.org</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J9" s="34" t="inlineStr">
+        <is>
+          <t>Wave 6. Open WordPress. Probe + 200-test before full run. ~4.7k URLs; Crawl-delay 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Public Universities</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n"/>
-      <c r="C9" s="32" t="n"/>
-      <c r="D9" s="32" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="32" t="n"/>
-      <c r="G9" s="32" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="32" t="n"/>
-      <c r="J9" s="32" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>University of California, Irvine</t>
-        </is>
-      </c>
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>New University</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="inlineStr">
-        <is>
-          <t>uci</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>newuniversity.org</t>
-        </is>
-      </c>
-      <c r="E10" s="33" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F10" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G10" s="33" t="n"/>
-      <c r="H10" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I10" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J10" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@uci; full run started 2026-09-28 after td-post-content fix</t>
-        </is>
-      </c>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="32" t="n"/>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="32" t="n"/>
+      <c r="J10" s="32" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="33" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>The Michigan Daily</t>
+          <t>New University</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>michigan</t>
+          <t>uci</t>
         </is>
       </c>
       <c r="D11" s="33" t="inlineStr">
         <is>
-          <t>michigandaily.com</t>
+          <t>newuniversity.org</t>
         </is>
       </c>
       <c r="E11" s="33" t="inlineStr">
@@ -919,95 +919,91 @@
       </c>
       <c r="J11" s="34" t="inlineStr">
         <is>
+          <t>newspaper-scraper@uci; full run started 2026-09-28 after td-post-content fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>The Michigan Daily</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>michigan</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>michigandaily.com</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G12" s="33" t="n"/>
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J12" s="34" t="inlineStr">
+        <is>
           <t>newspaper-scraper@michigan; full run started 2026-09-28</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="32" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G13" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H13" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I13" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J13" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
-        </is>
-      </c>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n"/>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="32" t="n"/>
+      <c r="J13" s="32" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>Franklin &amp; Marshall College</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>The College Reporter</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>fandm</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>the-college-reporter.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
@@ -1021,7 +1017,7 @@
         </is>
       </c>
       <c r="G14" s="30" t="n">
-        <v>3449</v>
+        <v>4039</v>
       </c>
       <c r="H14" s="33" t="inlineStr">
         <is>
@@ -1035,34 +1031,34 @@
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Liberal Arts</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -1071,7 +1067,7 @@
         </is>
       </c>
       <c r="G15" s="30" t="n">
-        <v>5048</v>
+        <v>3449</v>
       </c>
       <c r="H15" s="33" t="inlineStr">
         <is>
@@ -1085,457 +1081,605 @@
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
+          <t>Hillsdale College</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>The Collegian</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>hillsdale</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>hillsdalecollegian.com</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>15573</v>
+      </c>
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J16" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>Occidental College</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>The Occidental</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>occidental</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>theoccidentalnews.com</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>9892</v>
+      </c>
+      <c r="H17" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J17" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H18" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J18" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
           <t>Union College (NY)</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Concordiensis</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>union</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>concordiensis.com</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G19" s="30" t="n">
         <v>1604</v>
       </c>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="J16" s="34" t="inlineStr">
+      <c r="J19" s="34" t="inlineStr">
         <is>
           <t>Finished. 1604 articles of 1626 URLs; 44 empty_body skipped.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>Hillsdale College</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>The Collegian</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>hillsdale</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>hillsdalecollegian.com</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F17" s="33" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G17" s="33" t="n"/>
-      <c r="H17" s="33" t="inlineStr">
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I17" s="33" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="J17" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@hillsdale</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>Occidental College</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>The Occidental</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>occidental</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>theoccidentalnews.com</t>
-        </is>
-      </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="J20" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@swarthmore; pre-2000 permalinks skipped without fetch</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>Denison University</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>The Denisonian</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>denison</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>denisonian.com</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="n"/>
+      <c r="H21" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J21" s="34" t="inlineStr">
+        <is>
+          <t>Wave 6. Open WordPress. Probe + 200-test before full run. ~3.7k URLs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>Wesleyan University</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>The Wesleyan Argus</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>wesleyan</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>wesleyanargus.com</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="n"/>
+      <c r="H22" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J22" s="34" t="inlineStr">
+        <is>
+          <t>Wave 6. Open WordPress. Probe + 200-test before full run. ~22k URLs; titles/authors may be thin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
+      <c r="J23" s="32" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Biola University</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>The Chimes</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>biola</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>chimesnewspaper.com</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>11331</v>
+      </c>
+      <c r="H24" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I24" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J24" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Lipscomb University</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Lipscomb Media</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>lipscomb</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>lipscombmedia.com</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>682</v>
+      </c>
+      <c r="H25" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J25" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Point Loma Nazarene University</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>Loma Beat</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat.com</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H26" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J26" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Campus</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>smu</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>smudailycampus.com</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G18" s="33" t="n"/>
-      <c r="H18" s="33" t="inlineStr">
+      <c r="G27" s="33" t="n"/>
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I18" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J18" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@occidental</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>Swarthmore College</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>The Phoenix</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>swarthmore</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>swarthmorephoenix.com</t>
-        </is>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="J27" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@smu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>Texas Christian University</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>TCU 360</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>tcu</t>
+        </is>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>tcu360.com</t>
+        </is>
+      </c>
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G19" s="33" t="n"/>
-      <c r="H19" s="33" t="inlineStr">
+      <c r="G28" s="33" t="n"/>
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I19" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J19" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@swarthmore; pre-2000 permalinks skipped without fetch</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="B20" s="32" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="n"/>
-      <c r="G20" s="32" t="n"/>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="32" t="n"/>
-      <c r="J20" s="32" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E21" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G21" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H21" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I21" s="33" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="J21" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C22" s="33" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G22" s="30" t="n">
-        <v>682</v>
-      </c>
-      <c r="H22" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I22" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J22" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="33" t="inlineStr">
-        <is>
-          <t>Point Loma Nazarene University</t>
-        </is>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Loma Beat</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat.com</t>
-        </is>
-      </c>
-      <c r="E23" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F23" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G23" s="33" t="n"/>
-      <c r="H23" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I23" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J23" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@lomabeat; full run started 2026-09-28 after 196-row 200-test</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>Southern Methodist University</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>The Daily Campus</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>smu</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>smudailycampus.com</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges | National Universities</t>
-        </is>
-      </c>
-      <c r="F24" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G24" s="33" t="n"/>
-      <c r="H24" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I24" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J24" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@smu</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="33" t="inlineStr">
-        <is>
-          <t>Texas Christian University</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>TCU 360</t>
-        </is>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>tcu</t>
-        </is>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>tcu360.com</t>
-        </is>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges | National Universities</t>
-        </is>
-      </c>
-      <c r="F25" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G25" s="33" t="n"/>
-      <c r="H25" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I25" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J25" s="34" t="inlineStr">
+      <c r="J28" s="34" t="inlineStr">
         <is>
           <t>newspaper-scraper@tcu</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <col width="12" customWidth="1" style="19" min="7" max="7"/>
     <col width="12" customWidth="1" style="19" min="8" max="8"/>
     <col width="12" customWidth="1" style="19" min="9" max="9"/>
-    <col width="80" customWidth="1" style="19" min="10" max="10"/>
+    <col width="90" customWidth="1" style="19" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,173 +575,173 @@
       </c>
       <c r="J3" s="34" t="inlineStr">
         <is>
-          <t>Finished. 2137 articles of 2140 URLs (99.9%); 5 empty_body. systemd inactive. File: ~/Downloads/rit.csv</t>
+          <t>Finished. 2137 articles of 2140 URLs (99.9%); 5 empty_body. systemd inactive. File: repo output/rit.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="24" t="inlineStr">
         <is>
+          <t>University of California, Santa Cruz</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>City on a Hill Press</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>ucsc</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>cityonahillpress.com</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="n">
+        <v>6899</v>
+      </c>
+      <c r="H4" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J4" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 6899 articles of 6992 URLs (98.7%); 67 empty_body, 26 pre_2000. systemd inactive. File: ~/Downloads/ucsc.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
           <t>University of Chicago</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>The Chicago Maroon</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>chicago</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>chicagomaroon.com</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>National Universities</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G4" s="30" t="n">
+      <c r="G5" s="30" t="n">
         <v>22117</v>
       </c>
-      <c r="H4" s="33" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I4" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J4" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 22117 articles of 22493 URLs (98.3%); 371 empty_body, 2 http_301, 3 http_404. systemd inactive. File: ~/Downloads/chicago.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>Northwestern University</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>The Daily Northwestern</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>northwestern</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>dailynorthwestern.com</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="I5" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J5" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 22117 articles of 22493 URLs (98.3%); 371 empty_body, 2 http_301, 3 http_404. systemd inactive. File: repo output/chicago.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Yeshiva University</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>The Commentator</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>yu</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>yucommentator.org</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>National Universities</t>
         </is>
       </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="n"/>
-      <c r="H5" s="33" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>4175</v>
+      </c>
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="J5" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@northwestern; 403s still present at last check</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>University of California, Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>City on a Hill Press</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>ucsc</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>cityonahillpress.com</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>National Universities</t>
-        </is>
-      </c>
-      <c r="F6" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G6" s="33" t="n"/>
-      <c r="H6" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
       <c r="I6" s="35" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="J6" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@ucsc; full run started 2026-09-28 after 200-row 200-test</t>
+          <t>Finished. 4175 articles of 4678 URLs (89.2%); 41 empty_body, 464 pre_2000. systemd inactive. File: ~/Downloads/yu.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Northwestern University</t>
         </is>
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>The Miami Hurricane</t>
+          <t>The Daily Northwestern</t>
         </is>
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>miami</t>
+          <t>northwestern</t>
         </is>
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
-          <t>themiamihurricane.com</t>
+          <t>dailynorthwestern.com</t>
         </is>
       </c>
       <c r="E7" s="33" t="inlineStr">
@@ -761,33 +761,33 @@
         </is>
       </c>
       <c r="I7" s="35" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="J7" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@miami; full run started 2026-09-28</t>
+          <t>newspaper-scraper@northwestern; 32750 of 70720 (46.3%). 403s still 32; network_error 1083.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="33" t="inlineStr">
         <is>
-          <t>University of South Florida</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>The Oracle</t>
+          <t>The Miami Hurricane</t>
         </is>
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>usf</t>
+          <t>miami</t>
         </is>
       </c>
       <c r="D8" s="33" t="inlineStr">
         <is>
-          <t>usforacle.com</t>
+          <t>themiamihurricane.com</t>
         </is>
       </c>
       <c r="E8" s="33" t="inlineStr">
@@ -811,29 +811,29 @@
       </c>
       <c r="J8" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@usf; full run started 2026-09-28 after 199-row 200-test</t>
+          <t>newspaper-scraper@miami; 15050 of 25641 (58.7%). Watch http_403=2.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="33" t="inlineStr">
         <is>
-          <t>Yeshiva University</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>The Commentator</t>
+          <t>The Oracle</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>yu</t>
+          <t>usf</t>
         </is>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
-          <t>yucommentator.org</t>
+          <t>usforacle.com</t>
         </is>
       </c>
       <c r="E9" s="33" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="F9" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G9" s="33" t="n"/>
@@ -853,108 +853,110 @@
         </is>
       </c>
       <c r="I9" s="35" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="J9" s="34" t="inlineStr">
         <is>
-          <t>Wave 6. Open WordPress. Probe + 200-test before full run. ~4.7k URLs; Crawl-delay 10.</t>
+          <t>newspaper-scraper@usf; 18099 of 32243 (56.1%).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>Howard University</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>The Hilltop</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>hilltop</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>thehilltoponline.com</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J10" s="34" t="inlineStr">
+        <is>
+          <t>Wave 7. Open WordPress Yoast. Probe + 200-test before full run. Crawl-delay 30; ~8.2k URLs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Public Universities</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n"/>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="32" t="n"/>
-      <c r="J10" s="32" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>University of California, Irvine</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>New University</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>uci</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>newuniversity.org</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="n"/>
-      <c r="H11" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I11" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J11" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@uci; full run started 2026-09-28 after td-post-content fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>University of Michigan</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>The Michigan Daily</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="inlineStr">
-        <is>
-          <t>michigan</t>
-        </is>
-      </c>
-      <c r="D12" s="33" t="inlineStr">
-        <is>
-          <t>michigandaily.com</t>
-        </is>
-      </c>
-      <c r="E12" s="33" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F12" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G12" s="33" t="n"/>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>17411</v>
+      </c>
       <c r="H12" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -965,95 +967,91 @@
       </c>
       <c r="J12" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan; full run started 2026-09-28</t>
+          <t>Finished. 17411 articles of 17447 URLs (99.8%); 165 empty_body. systemd inactive. File: ~/Downloads/uci.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>University of Michigan</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>The Michigan Daily</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>michigan</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>michigandaily.com</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="n"/>
+      <c r="H13" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J13" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@michigan resumed after 168 KB field-limit crash. 16443 of 119764 (13.7%). http_301=440.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="32" t="n"/>
-      <c r="D13" s="32" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="32" t="n"/>
-      <c r="G13" s="32" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C14" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D14" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E14" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G14" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H14" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I14" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J14" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive.</t>
-        </is>
-      </c>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="32" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Franklin &amp; Marshall College</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>The College Reporter</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>fandm</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>the-college-reporter.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
@@ -1067,43 +1065,41 @@
         </is>
       </c>
       <c r="G15" s="30" t="n">
-        <v>3449</v>
+        <v>4039</v>
       </c>
       <c r="H15" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
+      <c r="I15" s="35" t="n">
+        <v>46292</v>
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive.</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Hillsdale College</t>
+          <t>Denison University</t>
         </is>
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>The Collegian</t>
+          <t>The Denisonian</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>hillsdale</t>
+          <t>denison</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr">
         <is>
-          <t>hillsdalecollegian.com</t>
+          <t>denisonian.com</t>
         </is>
       </c>
       <c r="E16" s="33" t="inlineStr">
@@ -1117,43 +1113,41 @@
         </is>
       </c>
       <c r="G16" s="30" t="n">
-        <v>15573</v>
+        <v>3671</v>
       </c>
       <c r="H16" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
+      <c r="I16" s="35" t="n">
+        <v>46294</v>
       </c>
       <c r="J16" s="34" t="inlineStr">
         <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive.</t>
+          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>Occidental College</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>The Occidental</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>occidental</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
         <is>
-          <t>theoccidentalnews.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E17" s="33" t="inlineStr">
@@ -1167,48 +1161,46 @@
         </is>
       </c>
       <c r="G17" s="30" t="n">
-        <v>9892</v>
+        <v>3449</v>
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I17" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
+      <c r="I17" s="35" t="n">
+        <v>46292</v>
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive.</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Hillsdale College</t>
         </is>
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>The Collegian</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>hillsdale</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>hillsdalecollegian.com</t>
         </is>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Liberal Arts</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -1217,165 +1209,163 @@
         </is>
       </c>
       <c r="G18" s="30" t="n">
-        <v>5048</v>
+        <v>15573</v>
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I18" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
+      <c r="I18" s="35" t="n">
+        <v>46292</v>
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%). File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
+          <t>Occidental College</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>The Occidental</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>occidental</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>theoccidentalnews.com</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>9892</v>
+      </c>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J19" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>12798</v>
+      </c>
+      <c r="H20" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I20" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J20" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
           <t>Union College (NY)</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Concordiensis</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>union</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>concordiensis.com</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G21" s="30" t="n">
         <v>1604</v>
       </c>
-      <c r="H19" s="33" t="inlineStr">
+      <c r="H21" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I19" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J19" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 1604 articles of 1626 URLs; 44 empty_body skipped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>Swarthmore College</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>The Phoenix</t>
-        </is>
-      </c>
-      <c r="C20" s="33" t="inlineStr">
-        <is>
-          <t>swarthmore</t>
-        </is>
-      </c>
-      <c r="D20" s="33" t="inlineStr">
-        <is>
-          <t>swarthmorephoenix.com</t>
-        </is>
-      </c>
-      <c r="E20" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F20" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G20" s="33" t="n"/>
-      <c r="H20" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I20" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="J20" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@swarthmore; pre-2000 permalinks skipped without fetch</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>Denison University</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>The Denisonian</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>denison</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>denisonian.com</t>
-        </is>
-      </c>
-      <c r="E21" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F21" s="33" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G21" s="33" t="n"/>
-      <c r="H21" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
       <c r="I21" s="35" t="n">
-        <v>46294</v>
+        <v>46292</v>
       </c>
       <c r="J21" s="34" t="inlineStr">
         <is>
-          <t>Wave 6. Open WordPress. Probe + 200-test before full run. ~3.7k URLs.</t>
+          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1397,7 @@
       </c>
       <c r="F22" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G22" s="33" t="n"/>
@@ -1421,95 +1411,91 @@
       </c>
       <c r="J22" s="34" t="inlineStr">
         <is>
-          <t>Wave 6. Open WordPress. Probe + 200-test before full run. ~22k URLs; titles/authors may be thin.</t>
+          <t>newspaper-scraper@wesleyan; 13300 of 21917 (60.7%). Titles present, authors empty.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>Claremont Colleges</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>The Student Life</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>tsl</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>tsl.news</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G23" s="33" t="n"/>
+      <c r="H23" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J23" s="34" t="inlineStr">
+        <is>
+          <t>Wave 7. Open WordPress Yoast. Probe + 200-test before full run. ~22.7k URLs; five Claremont colleges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G24" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H24" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I24" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J24" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive.</t>
-        </is>
-      </c>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="32" t="n"/>
+      <c r="I24" s="32" t="n"/>
+      <c r="J24" s="32" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>Lipscomb University</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>Lipscomb Media</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
-          <t>lipscomb</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
-          <t>lipscombmedia.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E25" s="33" t="inlineStr">
@@ -1523,165 +1509,259 @@
         </is>
       </c>
       <c r="G25" s="30" t="n">
-        <v>682</v>
+        <v>11331</v>
       </c>
       <c r="H25" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I25" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
+      <c r="I25" s="35" t="n">
+        <v>46291</v>
       </c>
       <c r="J25" s="34" t="inlineStr">
         <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive.</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
+          <t>Lipscomb University</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>Lipscomb Media</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>lipscomb</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>lipscombmedia.com</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="n">
+        <v>682</v>
+      </c>
+      <c r="H26" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J26" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
           <t>Point Loma Nazarene University</t>
         </is>
       </c>
-      <c r="B26" s="33" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Loma Beat</t>
         </is>
       </c>
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>lomabeat</t>
         </is>
       </c>
-      <c r="D26" s="33" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>lomabeat.com</t>
         </is>
       </c>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G26" s="30" t="n">
+      <c r="G27" s="30" t="n">
         <v>3950</v>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I26" s="35" t="n">
+      <c r="I27" s="35" t="n">
         <v>46293</v>
       </c>
-      <c r="J26" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="J27" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Southern Methodist University</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>The Daily Campus</t>
         </is>
       </c>
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>smu</t>
         </is>
       </c>
-      <c r="D27" s="33" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>smudailycampus.com</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F27" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G27" s="33" t="n"/>
-      <c r="H27" s="33" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="n">
+        <v>26208</v>
+      </c>
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I27" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J27" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@smu</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="I28" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J28" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H29" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J29" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>Texas Christian University</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>TCU 360</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>tcu</t>
         </is>
       </c>
-      <c r="D28" s="33" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>tcu360.com</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G28" s="33" t="n"/>
-      <c r="H28" s="33" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="n">
+        <v>25690</v>
+      </c>
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I28" s="33" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="J28" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@tcu</t>
+      <c r="I30" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J30" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -110,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -171,6 +172,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -765,7 +769,7 @@
       </c>
       <c r="J7" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@northwestern; 32750 of 70720 (46.3%). 403s still 32; network_error 1083.</t>
+          <t>newspaper-scraper@northwestern; 38600 of 70720 (54.6%). 403s still 32; network_error 1083.</t>
         </is>
       </c>
     </row>
@@ -811,7 +815,7 @@
       </c>
       <c r="J8" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@miami; 15050 of 25641 (58.7%). Watch http_403=2.</t>
+          <t>newspaper-scraper@miami; 21700 of 25641 (84.6%). Watch http_403=2.</t>
         </is>
       </c>
     </row>
@@ -857,7 +861,7 @@
       </c>
       <c r="J9" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@usf; 18099 of 32243 (56.1%).</t>
+          <t>newspaper-scraper@usf; 28449 of 32243 (88.2%).</t>
         </is>
       </c>
     </row>
@@ -1013,93 +1017,91 @@
       </c>
       <c r="J13" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan resumed after 168 KB field-limit crash. 16443 of 119764 (13.7%). http_301=440.</t>
+          <t>newspaper-scraper@michigan resumed after 168 KB field-limit crash. 25693 of 119764 (21.4%). http_301=440.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>University of California San Diego</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>The UCSD Guardian</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>ucsd</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>ucsdguardian.org</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G14" s="33" t="n"/>
+      <c r="H14" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J14" s="34" t="inlineStr">
+        <is>
+          <t>Wave 8 Cloudflare canary. SNO. Probe + 200-test before full run. Pace 10-14 s (~22.6k URLs). Honest UA first; browser UA allowed if refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="32" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="32" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B15" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C15" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G15" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H15" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I15" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J15" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
-        </is>
-      </c>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="32" t="n"/>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="32" t="n"/>
+      <c r="J15" s="32" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Denison University</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>The Denisonian</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>denison</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D16" s="33" t="inlineStr">
         <is>
-          <t>denisonian.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E16" s="33" t="inlineStr">
@@ -1113,7 +1115,7 @@
         </is>
       </c>
       <c r="G16" s="30" t="n">
-        <v>3671</v>
+        <v>4039</v>
       </c>
       <c r="H16" s="33" t="inlineStr">
         <is>
@@ -1121,33 +1123,33 @@
         </is>
       </c>
       <c r="I16" s="35" t="n">
-        <v>46294</v>
+        <v>46292</v>
       </c>
       <c r="J16" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>Franklin &amp; Marshall College</t>
+          <t>Denison University</t>
         </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>The College Reporter</t>
+          <t>The Denisonian</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>fandm</t>
+          <t>denison</t>
         </is>
       </c>
       <c r="D17" s="33" t="inlineStr">
         <is>
-          <t>the-college-reporter.com</t>
+          <t>denisonian.com</t>
         </is>
       </c>
       <c r="E17" s="33" t="inlineStr">
@@ -1161,7 +1163,7 @@
         </is>
       </c>
       <c r="G17" s="30" t="n">
-        <v>3449</v>
+        <v>3671</v>
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
@@ -1169,33 +1171,33 @@
         </is>
       </c>
       <c r="I17" s="35" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
+          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>Hillsdale College</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>The Collegian</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>hillsdale</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
         <is>
-          <t>hillsdalecollegian.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E18" s="33" t="inlineStr">
@@ -1209,7 +1211,7 @@
         </is>
       </c>
       <c r="G18" s="30" t="n">
-        <v>15573</v>
+        <v>3449</v>
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
@@ -1221,29 +1223,29 @@
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>Occidental College</t>
+          <t>Hillsdale College</t>
         </is>
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>The Occidental</t>
+          <t>The Collegian</t>
         </is>
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>occidental</t>
+          <t>hillsdale</t>
         </is>
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>theoccidentalnews.com</t>
+          <t>hillsdalecollegian.com</t>
         </is>
       </c>
       <c r="E19" s="33" t="inlineStr">
@@ -1257,7 +1259,7 @@
         </is>
       </c>
       <c r="G19" s="30" t="n">
-        <v>9892</v>
+        <v>15573</v>
       </c>
       <c r="H19" s="33" t="inlineStr">
         <is>
@@ -1269,29 +1271,29 @@
       </c>
       <c r="J19" s="34" t="inlineStr">
         <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>Swarthmore College</t>
+          <t>Occidental College</t>
         </is>
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>The Phoenix</t>
+          <t>The Occidental</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>swarthmore</t>
+          <t>occidental</t>
         </is>
       </c>
       <c r="D20" s="33" t="inlineStr">
         <is>
-          <t>swarthmorephoenix.com</t>
+          <t>theoccidentalnews.com</t>
         </is>
       </c>
       <c r="E20" s="33" t="inlineStr">
@@ -1305,7 +1307,7 @@
         </is>
       </c>
       <c r="G20" s="30" t="n">
-        <v>12798</v>
+        <v>9892</v>
       </c>
       <c r="H20" s="33" t="inlineStr">
         <is>
@@ -1317,29 +1319,29 @@
       </c>
       <c r="J20" s="34" t="inlineStr">
         <is>
-          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Union College (NY)</t>
+          <t>Swarthmore College</t>
         </is>
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>Concordiensis</t>
+          <t>The Phoenix</t>
         </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
-          <t>union</t>
+          <t>swarthmore</t>
         </is>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
-          <t>concordiensis.com</t>
+          <t>swarthmorephoenix.com</t>
         </is>
       </c>
       <c r="E21" s="33" t="inlineStr">
@@ -1353,7 +1355,7 @@
         </is>
       </c>
       <c r="G21" s="30" t="n">
-        <v>1604</v>
+        <v>12798</v>
       </c>
       <c r="H21" s="33" t="inlineStr">
         <is>
@@ -1365,185 +1367,187 @@
       </c>
       <c r="J21" s="34" t="inlineStr">
         <is>
+          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Union College (NY)</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Concordiensis</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>concordiensis.com</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>1604</v>
+      </c>
+      <c r="H22" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J22" s="34" t="inlineStr">
+        <is>
           <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Wesleyan University</t>
         </is>
       </c>
-      <c r="B22" s="33" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>The Wesleyan Argus</t>
         </is>
       </c>
-      <c r="C22" s="33" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>wesleyan</t>
         </is>
       </c>
-      <c r="D22" s="33" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>wesleyanargus.com</t>
         </is>
       </c>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="n">
+        <v>21881</v>
+      </c>
+      <c r="H23" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J23" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>Claremont Colleges</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>The Student Life</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>tsl</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>tsl.news</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G22" s="33" t="n"/>
-      <c r="H22" s="33" t="inlineStr">
+      <c r="G24" s="33" t="n"/>
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I22" s="35" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J22" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@wesleyan; 13300 of 21917 (60.7%). Titles present, authors empty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="33" t="inlineStr">
-        <is>
-          <t>Claremont Colleges</t>
-        </is>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>The Student Life</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>tsl</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>tsl.news</t>
-        </is>
-      </c>
-      <c r="E23" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F23" s="33" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G23" s="33" t="n"/>
-      <c r="H23" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I23" s="35" t="n">
+      <c r="I24" s="35" t="n">
         <v>46295</v>
       </c>
-      <c r="J23" s="34" t="inlineStr">
-        <is>
-          <t>Wave 7. Open WordPress Yoast. Probe + 200-test before full run. ~22.7k URLs; five Claremont colleges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="J24" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tsl full run after 200-test OK. Resuming 200 of 11437 (1.7%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="32" t="n"/>
-      <c r="J24" s="32" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G25" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H25" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I25" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J25" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
-        </is>
-      </c>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="32" t="n"/>
+      <c r="I25" s="32" t="n"/>
+      <c r="J25" s="32" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>Lipscomb University</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>Lipscomb Media</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>lipscomb</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D26" s="33" t="inlineStr">
         <is>
-          <t>lipscombmedia.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E26" s="33" t="inlineStr">
@@ -1557,7 +1561,7 @@
         </is>
       </c>
       <c r="G26" s="30" t="n">
-        <v>682</v>
+        <v>11331</v>
       </c>
       <c r="H26" s="33" t="inlineStr">
         <is>
@@ -1565,33 +1569,33 @@
         </is>
       </c>
       <c r="I26" s="35" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="J26" s="34" t="inlineStr">
         <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Point Loma Nazarene University</t>
+          <t>Lipscomb University</t>
         </is>
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>Loma Beat</t>
+          <t>Lipscomb Media</t>
         </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>lomabeat</t>
+          <t>lipscomb</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
         <is>
-          <t>lomabeat.com</t>
+          <t>lipscombmedia.com</t>
         </is>
       </c>
       <c r="E27" s="33" t="inlineStr">
@@ -1605,7 +1609,7 @@
         </is>
       </c>
       <c r="G27" s="30" t="n">
-        <v>3950</v>
+        <v>682</v>
       </c>
       <c r="H27" s="33" t="inlineStr">
         <is>
@@ -1613,38 +1617,38 @@
         </is>
       </c>
       <c r="I27" s="35" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="J27" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Point Loma Nazarene University</t>
         </is>
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>The Daily Campus</t>
+          <t>Loma Beat</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>smu</t>
+          <t>lomabeat</t>
         </is>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
-          <t>smudailycampus.com</t>
+          <t>lomabeat.com</t>
         </is>
       </c>
       <c r="E28" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | National Universities</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
@@ -1653,7 +1657,7 @@
         </is>
       </c>
       <c r="G28" s="30" t="n">
-        <v>26208</v>
+        <v>3950</v>
       </c>
       <c r="H28" s="33" t="inlineStr">
         <is>
@@ -1661,38 +1665,38 @@
         </is>
       </c>
       <c r="I28" s="35" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="J28" s="34" t="inlineStr">
         <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Southern Methodist University</t>
         </is>
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>The Daily Campus</t>
         </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>smu</t>
         </is>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>smudailycampus.com</t>
         </is>
       </c>
       <c r="E29" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Christian Colleges | National Universities</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -1701,7 +1705,7 @@
         </is>
       </c>
       <c r="G29" s="30" t="n">
-        <v>5048</v>
+        <v>26208</v>
       </c>
       <c r="H29" s="33" t="inlineStr">
         <is>
@@ -1709,57 +1713,105 @@
         </is>
       </c>
       <c r="I29" s="35" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="J29" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H30" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J30" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
           <t>Texas Christian University</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>TCU 360</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>tcu</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>tcu360.com</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G30" s="30" t="n">
+      <c r="G31" s="30" t="n">
         <v>25690</v>
       </c>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I30" s="35" t="n">
+      <c r="I31" s="35" t="n">
         <v>46291</v>
       </c>
-      <c r="J30" s="34" t="inlineStr">
+      <c r="J31" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -912,101 +912,101 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>Duke University</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>The Chronicle</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>duke</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>dukechronicle.com</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="n"/>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J11" s="34" t="inlineStr">
+        <is>
+          <t>VM probe OK with browser UA. Full mode is News-section listings only. 200-test before systemd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Public Universities</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n"/>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="32" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>University of California, Irvine</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>New University</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>uci</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>newuniversity.org</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G13" s="30" t="n">
         <v>17411</v>
       </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I12" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J12" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 17411 articles of 17447 URLs (99.8%); 165 empty_body. systemd inactive. File: ~/Downloads/uci.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>University of Michigan</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>The Michigan Daily</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="inlineStr">
-        <is>
-          <t>michigan</t>
-        </is>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>michigandaily.com</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F13" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G13" s="33" t="n"/>
       <c r="H13" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1017,29 +1017,29 @@
       </c>
       <c r="J13" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan resumed after 168 KB field-limit crash. 25693 of 119764 (21.4%). http_301=440.</t>
+          <t>Finished. 17411 articles of 17447 URLs (99.8%); 165 empty_body. systemd inactive. File: ~/Downloads/uci.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>University of Michigan</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>The UCSD Guardian</t>
+          <t>The Michigan Daily</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>ucsd</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>ucsdguardian.org</t>
+          <t>michigandaily.com</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F14" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G14" s="33" t="n"/>
@@ -1058,338 +1058,326 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I14" s="36" t="n">
+      <c r="I14" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J14" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@michigan resumed after 168 KB field-limit crash. 25693 of 119764 (21.4%). http_301=440.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>University of California San Diego</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>The UCSD Guardian</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>ucsd</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>ucsdguardian.org</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="n"/>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I15" s="36" t="n">
         <v>46296</v>
       </c>
-      <c r="J14" s="34" t="inlineStr">
-        <is>
-          <t>Wave 8 Cloudflare canary. SNO. Probe + 200-test before full run. Pace 10-14 s (~22.6k URLs). Honest UA first; browser UA allowed if refused.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="J15" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@ucsd full run after 200-test 200/200 OK on honest UA. Resuming 200 of 22,605.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>University of Texas at Austin</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Texan</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>texan</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>thedailytexan.com</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G16" s="33" t="n"/>
+      <c r="H16" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I16" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J16" s="34" t="inlineStr">
+        <is>
+          <t>Wave 9 Cloudflare SNO. Probe + 200-test. Pace 10-14 s (~51.6k URLs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>University of California, Santa Barbara</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Daily Nexus</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>nexus</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>dailynexus.com</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J17" s="34" t="inlineStr">
+        <is>
+          <t>Wave 9 Cloudflare WordPress Yoast. Probe + 200-test. Pace 10-14 s (~40.5k URLs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>University of Illinois Urbana-Champaign</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Illini</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>illini</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>dailyillini.com</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G18" s="33" t="n"/>
+      <c r="H18" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J18" s="34" t="inlineStr">
+        <is>
+          <t>Wave 9 Cloudflare SNO Yoast. Probe + 200-test. Pace 10-14 s (~100k URLs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>technician</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>technicianonline.com</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="n"/>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J19" s="34" t="inlineStr">
+        <is>
+          <t>Wave 9 Cloudflare SNO. Public flagship. Probe + 200-test. Pace 10-14 s (~41k URLs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Stony Brook University</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>The Statesman</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>statesman</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>sbstatesman.com</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G20" s="33" t="n"/>
+      <c r="H20" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J20" s="34" t="inlineStr">
+        <is>
+          <t>Wave 9 Cloudflare SNO. Public flagship. Probe + 200-test. Pace 10-14 s (~13.6k URLs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B15" s="32" t="n"/>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="32" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C16" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G16" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H16" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I16" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J16" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>Denison University</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>The Denisonian</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>denison</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>denisonian.com</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G17" s="30" t="n">
-        <v>3671</v>
-      </c>
-      <c r="H17" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I17" s="35" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J17" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>Franklin &amp; Marshall College</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>The College Reporter</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="inlineStr">
-        <is>
-          <t>fandm</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>the-college-reporter.com</t>
-        </is>
-      </c>
-      <c r="E18" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G18" s="30" t="n">
-        <v>3449</v>
-      </c>
-      <c r="H18" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I18" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J18" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>Hillsdale College</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>The Collegian</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="inlineStr">
-        <is>
-          <t>hillsdale</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>hillsdalecollegian.com</t>
-        </is>
-      </c>
-      <c r="E19" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G19" s="30" t="n">
-        <v>15573</v>
-      </c>
-      <c r="H19" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I19" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J19" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>Occidental College</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>The Occidental</t>
-        </is>
-      </c>
-      <c r="C20" s="33" t="inlineStr">
-        <is>
-          <t>occidental</t>
-        </is>
-      </c>
-      <c r="D20" s="33" t="inlineStr">
-        <is>
-          <t>theoccidentalnews.com</t>
-        </is>
-      </c>
-      <c r="E20" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G20" s="30" t="n">
-        <v>9892</v>
-      </c>
-      <c r="H20" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I20" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J20" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>Swarthmore College</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>The Phoenix</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="inlineStr">
-        <is>
-          <t>swarthmore</t>
-        </is>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>swarthmorephoenix.com</t>
-        </is>
-      </c>
-      <c r="E21" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G21" s="30" t="n">
-        <v>12798</v>
-      </c>
-      <c r="H21" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I21" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J21" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
-        </is>
-      </c>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="32" t="n"/>
+      <c r="J21" s="32" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>Union College (NY)</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>Concordiensis</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>union</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
-          <t>concordiensis.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E22" s="33" t="inlineStr">
@@ -1403,7 +1391,7 @@
         </is>
       </c>
       <c r="G22" s="30" t="n">
-        <v>1604</v>
+        <v>4039</v>
       </c>
       <c r="H22" s="33" t="inlineStr">
         <is>
@@ -1415,29 +1403,29 @@
       </c>
       <c r="J22" s="34" t="inlineStr">
         <is>
-          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>Wesleyan University</t>
+          <t>Denison University</t>
         </is>
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>The Wesleyan Argus</t>
+          <t>The Denisonian</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>wesleyan</t>
+          <t>denison</t>
         </is>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
-          <t>wesleyanargus.com</t>
+          <t>denisonian.com</t>
         </is>
       </c>
       <c r="E23" s="33" t="inlineStr">
@@ -1450,8 +1438,8 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G23" s="24" t="n">
-        <v>21881</v>
+      <c r="G23" s="30" t="n">
+        <v>3671</v>
       </c>
       <c r="H23" s="33" t="inlineStr">
         <is>
@@ -1463,29 +1451,29 @@
       </c>
       <c r="J23" s="34" t="inlineStr">
         <is>
-          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>Claremont Colleges</t>
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>The Student Life</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>tsl</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
-          <t>tsl.news</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E24" s="33" t="inlineStr">
@@ -1493,66 +1481,100 @@
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G24" s="33" t="n"/>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>3449</v>
+      </c>
       <c r="H24" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
       <c r="I24" s="35" t="n">
-        <v>46295</v>
+        <v>46292</v>
       </c>
       <c r="J24" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tsl full run after 200-test OK. Resuming 200 of 11437 (1.7%).</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="32" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="32" t="n"/>
-      <c r="F25" s="32" t="n"/>
-      <c r="G25" s="32" t="n"/>
-      <c r="H25" s="32" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="32" t="n"/>
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Hillsdale College</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>The Collegian</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>hillsdale</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>hillsdalecollegian.com</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>15573</v>
+      </c>
+      <c r="H25" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I25" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J25" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>Biola University</t>
+          <t>Occidental College</t>
         </is>
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>The Chimes</t>
+          <t>The Occidental</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>biola</t>
+          <t>occidental</t>
         </is>
       </c>
       <c r="D26" s="33" t="inlineStr">
         <is>
-          <t>chimesnewspaper.com</t>
+          <t>theoccidentalnews.com</t>
         </is>
       </c>
       <c r="E26" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges</t>
+          <t>Liberal Arts</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -1561,7 +1583,7 @@
         </is>
       </c>
       <c r="G26" s="30" t="n">
-        <v>11331</v>
+        <v>9892</v>
       </c>
       <c r="H26" s="33" t="inlineStr">
         <is>
@@ -1569,38 +1591,38 @@
         </is>
       </c>
       <c r="I26" s="35" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="J26" s="34" t="inlineStr">
         <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Lipscomb University</t>
+          <t>Swarthmore College</t>
         </is>
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>Lipscomb Media</t>
+          <t>The Phoenix</t>
         </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>lipscomb</t>
+          <t>swarthmore</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
         <is>
-          <t>lipscombmedia.com</t>
+          <t>swarthmorephoenix.com</t>
         </is>
       </c>
       <c r="E27" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges</t>
+          <t>Liberal Arts</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -1609,7 +1631,7 @@
         </is>
       </c>
       <c r="G27" s="30" t="n">
-        <v>682</v>
+        <v>12798</v>
       </c>
       <c r="H27" s="33" t="inlineStr">
         <is>
@@ -1621,34 +1643,34 @@
       </c>
       <c r="J27" s="34" t="inlineStr">
         <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
+          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Point Loma Nazarene University</t>
+          <t>Union College (NY)</t>
         </is>
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>Loma Beat</t>
+          <t>Concordiensis</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>lomabeat</t>
+          <t>union</t>
         </is>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
-          <t>lomabeat.com</t>
+          <t>concordiensis.com</t>
         </is>
       </c>
       <c r="E28" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges</t>
+          <t>Liberal Arts</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
@@ -1657,7 +1679,7 @@
         </is>
       </c>
       <c r="G28" s="30" t="n">
-        <v>3950</v>
+        <v>1604</v>
       </c>
       <c r="H28" s="33" t="inlineStr">
         <is>
@@ -1665,153 +1687,407 @@
         </is>
       </c>
       <c r="I28" s="35" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="J28" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
+          <t>Wesleyan University</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>The Wesleyan Argus</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>wesleyan</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>wesleyanargus.com</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="n">
+        <v>21881</v>
+      </c>
+      <c r="H29" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J29" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>Claremont Colleges</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>The Student Life</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>tsl</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>tsl.news</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F30" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J30" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tsl full run after 200-test OK. Resuming 200 of 11437 (1.7%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="n"/>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="32" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="32" t="n"/>
+      <c r="H31" s="32" t="n"/>
+      <c r="I31" s="32" t="n"/>
+      <c r="J31" s="32" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Biola University</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>The Chimes</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>biola</t>
+        </is>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>chimesnewspaper.com</t>
+        </is>
+      </c>
+      <c r="E32" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>11331</v>
+      </c>
+      <c r="H32" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I32" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J32" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Lipscomb University</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>Lipscomb Media</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>lipscomb</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>lipscombmedia.com</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>682</v>
+      </c>
+      <c r="H33" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I33" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J33" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Point Loma Nazarene University</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Loma Beat</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat</t>
+        </is>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat.com</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H34" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J34" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
           <t>Southern Methodist University</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>The Daily Campus</t>
         </is>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C35" s="33" t="inlineStr">
         <is>
           <t>smu</t>
         </is>
       </c>
-      <c r="D29" s="33" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>smudailycampus.com</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F35" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G29" s="30" t="n">
+      <c r="G35" s="30" t="n">
         <v>26208</v>
       </c>
-      <c r="H29" s="33" t="inlineStr">
+      <c r="H35" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I29" s="35" t="n">
+      <c r="I35" s="35" t="n">
         <v>46291</v>
       </c>
-      <c r="J29" s="34" t="inlineStr">
+      <c r="J35" s="34" t="inlineStr">
         <is>
           <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>St. Olaf College</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>Manitou Messenger</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>stolaf</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>olafmessenger.com</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | Liberal Arts</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G30" s="30" t="n">
+      <c r="G36" s="30" t="n">
         <v>5048</v>
       </c>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="H36" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I30" s="35" t="n">
+      <c r="I36" s="35" t="n">
         <v>46292</v>
       </c>
-      <c r="J30" s="34" t="inlineStr">
+      <c r="J36" s="34" t="inlineStr">
         <is>
           <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>Texas Christian University</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>TCU 360</t>
         </is>
       </c>
-      <c r="C31" s="33" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>tcu</t>
         </is>
       </c>
-      <c r="D31" s="33" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>tcu360.com</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F37" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G31" s="30" t="n">
+      <c r="G37" s="30" t="n">
         <v>25690</v>
       </c>
-      <c r="H31" s="33" t="inlineStr">
+      <c r="H37" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I31" s="35" t="n">
+      <c r="I37" s="35" t="n">
         <v>46291</v>
       </c>
-      <c r="J31" s="34" t="inlineStr">
+      <c r="J37" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -177,6 +177,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -769,17 +770,17 @@
       </c>
       <c r="J7" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@northwestern; 38600 of 70720 (54.6%). 403s still 32; network_error 1083.</t>
+          <t>newspaper-scraper@northwestern; 44850 of 70720 (63.4%) as of 2026-10-02 13:50 UTC. empty_body=1790, http_301=3, http_403=32 (stable), network_error=1083, pre_2000=37.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>University of Miami</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>The Miami Hurricane</t>
         </is>
@@ -799,12 +800,14 @@
           <t>National Universities</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="n"/>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="n">
+        <v>25622</v>
+      </c>
       <c r="H8" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -815,17 +818,17 @@
       </c>
       <c r="J8" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@miami; 21700 of 25641 (84.6%). Watch http_403=2.</t>
+          <t>Finished 2026-10-02. 25622 articles of 25641 URLs (99.9%); 8 empty_body, 2 http_403, 9 http_500, 5 network_error. systemd inactive. File: ~/Downloads/miami.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>University of South Florida</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>The Oracle</t>
         </is>
@@ -845,12 +848,14 @@
           <t>National Universities</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="n"/>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>31894</v>
+      </c>
       <c r="H9" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -861,7 +866,7 @@
       </c>
       <c r="J9" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@usf; 28449 of 32243 (88.2%).</t>
+          <t>Finished 2026-10-01. 31894 articles of 32243 URLs (98.9%); 501 empty_body, 2 network_error, 9 pre_2000. systemd inactive. File: ~/Downloads/usf.csv</t>
         </is>
       </c>
     </row>
@@ -907,7 +912,7 @@
       </c>
       <c r="J10" s="34" t="inlineStr">
         <is>
-          <t>Wave 7. Open WordPress Yoast. Probe + 200-test before full run. Crawl-delay 30; ~8.2k URLs.</t>
+          <t>Not cleared on the VM: homepage timeout, article pages HTTP 508. Crawl-delay 30; ~8.2k URLs. Retry from Mac, wait, or skip.</t>
         </is>
       </c>
     </row>
@@ -939,7 +944,7 @@
       </c>
       <c r="F11" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G11" s="33" t="n"/>
@@ -953,7 +958,7 @@
       </c>
       <c r="J11" s="34" t="inlineStr">
         <is>
-          <t>VM probe OK with browser UA. Full mode is News-section listings only. 200-test before systemd.</t>
+          <t>newspaper-scraper@duke News-section listings only. 4600 rows as of 2026-10-02 13:50 UTC (no sitemap inventory). empty_body=17. Browser UA.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1068,7 @@
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan resumed after 168 KB field-limit crash. 25693 of 119764 (21.4%). http_301=440.</t>
+          <t>newspaper-scraper@michigan; 35593 of 119764 (29.7%) as of 2026-10-02 13:50 UTC. empty_body=14, http_301=1130, http_429=3, network_error=2. Watch 429s.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@ucsd full run after 200-test 200/200 OK on honest UA. Resuming 200 of 22,605.</t>
+          <t>newspaper-scraper@ucsd Cloudflare canary 10-14s. 5450 of 22605 (24.1%) as of 2026-10-02 13:50 UTC. empty_body=3, http_500=2.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1146,7 @@
       </c>
       <c r="F16" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G16" s="33" t="n"/>
@@ -1155,7 +1160,7 @@
       </c>
       <c r="J16" s="34" t="inlineStr">
         <is>
-          <t>Wave 9 Cloudflare SNO. Probe + 200-test. Pace 10-14 s (~51.6k URLs).</t>
+          <t>newspaper-scraper@texan Cloudflare SNO 10-14s. 4747 of 51636 (9.2%) as of 2026-10-02 13:50 UTC. empty_body=74, http_500=3.</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1192,7 @@
       </c>
       <c r="F17" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G17" s="33" t="n"/>
@@ -1201,7 +1206,7 @@
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>Wave 9 Cloudflare WordPress Yoast. Probe + 200-test. Pace 10-14 s (~40.5k URLs).</t>
+          <t>newspaper-scraper@nexus Cloudflare WP 10-14s. 4637 of 40465 (11.5%) as of 2026-10-02 13:50 UTC. empty_body=453 (high; photo features). Watch.</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="F18" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G18" s="33" t="n"/>
@@ -1247,7 +1252,7 @@
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
-          <t>Wave 9 Cloudflare SNO Yoast. Probe + 200-test. Pace 10-14 s (~100k URLs).</t>
+          <t>newspaper-scraper@illini Cloudflare SNO 10-14s. 4900 of 100022 (4.9%) as of 2026-10-02 13:50 UTC. http_500=1, pre_2000=10.</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1284,7 @@
       </c>
       <c r="F19" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G19" s="33" t="n"/>
@@ -1293,7 +1298,7 @@
       </c>
       <c r="J19" s="34" t="inlineStr">
         <is>
-          <t>Wave 9 Cloudflare SNO. Public flagship. Probe + 200-test. Pace 10-14 s (~41k URLs).</t>
+          <t>newspaper-scraper@technician Cloudflare SNO 10-14s. 5083 of 41051 (12.4%) as of 2026-10-02 13:50 UTC. empty_body=82.</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="F20" s="33" t="inlineStr">
         <is>
-          <t>queued</t>
+          <t>running</t>
         </is>
       </c>
       <c r="G20" s="33" t="n"/>
@@ -1339,141 +1344,135 @@
       </c>
       <c r="J20" s="34" t="inlineStr">
         <is>
-          <t>Wave 9 Cloudflare SNO. Public flagship. Probe + 200-test. Pace 10-14 s (~13.6k URLs).</t>
+          <t>newspaper-scraper@statesman Cloudflare SNO 10-14s. 5047 of 13650 (37.0%) as of 2026-10-02 13:50 UTC. empty_body=106.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>University of North Carolina, Chapel Hill</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Daily Tar Heel</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>tarheel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>dailytarheel.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I21" s="37" t="n">
+        <v>46297</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Wave 10. Cloudflare SNO. wp-sitemap.xml (~82k URLs). Pace 10-14 s. Probe + 200-test before systemd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>University of California, Riverside</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Highlander</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>highlander</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>highlandernews.org</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I22" s="37" t="n">
+        <v>46297</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Wave 10. Public campus listed only on the National tab. Cloudflare Yoast WP (~10k URLs). Pace 10-14 s. Probe + 200-test before systemd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C22" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G22" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H22" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I22" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J22" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>Denison University</t>
-        </is>
-      </c>
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>The Denisonian</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>denison</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>denisonian.com</t>
-        </is>
-      </c>
-      <c r="E23" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G23" s="30" t="n">
-        <v>3671</v>
-      </c>
-      <c r="H23" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I23" s="35" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J23" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
-        </is>
-      </c>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
+      <c r="J23" s="32" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>Franklin &amp; Marshall College</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>The College Reporter</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>fandm</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
-          <t>the-college-reporter.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E24" s="33" t="inlineStr">
@@ -1487,7 +1486,7 @@
         </is>
       </c>
       <c r="G24" s="30" t="n">
-        <v>3449</v>
+        <v>4039</v>
       </c>
       <c r="H24" s="33" t="inlineStr">
         <is>
@@ -1499,29 +1498,29 @@
       </c>
       <c r="J24" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>Hillsdale College</t>
+          <t>Denison University</t>
         </is>
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>The Collegian</t>
+          <t>The Denisonian</t>
         </is>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
-          <t>hillsdale</t>
+          <t>denison</t>
         </is>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
-          <t>hillsdalecollegian.com</t>
+          <t>denisonian.com</t>
         </is>
       </c>
       <c r="E25" s="33" t="inlineStr">
@@ -1535,7 +1534,7 @@
         </is>
       </c>
       <c r="G25" s="30" t="n">
-        <v>15573</v>
+        <v>3671</v>
       </c>
       <c r="H25" s="33" t="inlineStr">
         <is>
@@ -1543,33 +1542,33 @@
         </is>
       </c>
       <c r="I25" s="35" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="J25" s="34" t="inlineStr">
         <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
+          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>Occidental College</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>The Occidental</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>occidental</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D26" s="33" t="inlineStr">
         <is>
-          <t>theoccidentalnews.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E26" s="33" t="inlineStr">
@@ -1583,7 +1582,7 @@
         </is>
       </c>
       <c r="G26" s="30" t="n">
-        <v>9892</v>
+        <v>3449</v>
       </c>
       <c r="H26" s="33" t="inlineStr">
         <is>
@@ -1595,29 +1594,29 @@
       </c>
       <c r="J26" s="34" t="inlineStr">
         <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Swarthmore College</t>
+          <t>Hillsdale College</t>
         </is>
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>The Phoenix</t>
+          <t>The Collegian</t>
         </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>swarthmore</t>
+          <t>hillsdale</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
         <is>
-          <t>swarthmorephoenix.com</t>
+          <t>hillsdalecollegian.com</t>
         </is>
       </c>
       <c r="E27" s="33" t="inlineStr">
@@ -1631,7 +1630,7 @@
         </is>
       </c>
       <c r="G27" s="30" t="n">
-        <v>12798</v>
+        <v>15573</v>
       </c>
       <c r="H27" s="33" t="inlineStr">
         <is>
@@ -1643,29 +1642,29 @@
       </c>
       <c r="J27" s="34" t="inlineStr">
         <is>
-          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Union College (NY)</t>
+          <t>Occidental College</t>
         </is>
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>Concordiensis</t>
+          <t>The Occidental</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>union</t>
+          <t>occidental</t>
         </is>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
-          <t>concordiensis.com</t>
+          <t>theoccidentalnews.com</t>
         </is>
       </c>
       <c r="E28" s="33" t="inlineStr">
@@ -1679,7 +1678,7 @@
         </is>
       </c>
       <c r="G28" s="30" t="n">
-        <v>1604</v>
+        <v>9892</v>
       </c>
       <c r="H28" s="33" t="inlineStr">
         <is>
@@ -1691,235 +1690,235 @@
       </c>
       <c r="J28" s="34" t="inlineStr">
         <is>
-          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>12798</v>
+      </c>
+      <c r="H29" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I29" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J29" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Union College (NY)</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>Concordiensis</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>concordiensis.com</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="n">
+        <v>1604</v>
+      </c>
+      <c r="H30" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J30" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
           <t>Wesleyan University</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>The Wesleyan Argus</t>
         </is>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>wesleyan</t>
         </is>
       </c>
-      <c r="D29" s="33" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>wesleyanargus.com</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G29" s="24" t="n">
+      <c r="G31" s="24" t="n">
         <v>21881</v>
       </c>
-      <c r="H29" s="33" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I29" s="35" t="n">
+      <c r="I31" s="35" t="n">
         <v>46294</v>
       </c>
-      <c r="J29" s="34" t="inlineStr">
+      <c r="J31" s="34" t="inlineStr">
         <is>
           <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>Claremont Colleges</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>The Student Life</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>tsl</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>tsl.news</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F30" s="33" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G30" s="33" t="n"/>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="G32" s="33" t="n"/>
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I30" s="35" t="n">
+      <c r="I32" s="35" t="n">
         <v>46295</v>
       </c>
-      <c r="J30" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@tsl full run after 200-test OK. Resuming 200 of 11437 (1.7%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="J32" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tsl; 9600 of 11437 (83.9%) as of 2026-10-02 13:50 UTC. empty_body=14, http_403=15. Closest to finishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="32" t="n"/>
-      <c r="H31" s="32" t="n"/>
-      <c r="I31" s="32" t="n"/>
-      <c r="J31" s="32" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E32" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F32" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H32" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I32" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J32" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C33" s="33" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F33" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G33" s="30" t="n">
-        <v>682</v>
-      </c>
-      <c r="H33" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I33" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J33" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
-        </is>
-      </c>
+      <c r="B33" s="32" t="n"/>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="32" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="32" t="n"/>
+      <c r="H33" s="32" t="n"/>
+      <c r="I33" s="32" t="n"/>
+      <c r="J33" s="32" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Point Loma Nazarene University</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>Loma Beat</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>lomabeat</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>lomabeat.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E34" s="33" t="inlineStr">
@@ -1933,7 +1932,7 @@
         </is>
       </c>
       <c r="G34" s="30" t="n">
-        <v>3950</v>
+        <v>11331</v>
       </c>
       <c r="H34" s="33" t="inlineStr">
         <is>
@@ -1941,38 +1940,38 @@
         </is>
       </c>
       <c r="I34" s="35" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="J34" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Lipscomb University</t>
         </is>
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>The Daily Campus</t>
+          <t>Lipscomb Media</t>
         </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>smu</t>
+          <t>lipscomb</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
-          <t>smudailycampus.com</t>
+          <t>lipscombmedia.com</t>
         </is>
       </c>
       <c r="E35" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | National Universities</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
@@ -1981,7 +1980,7 @@
         </is>
       </c>
       <c r="G35" s="30" t="n">
-        <v>26208</v>
+        <v>682</v>
       </c>
       <c r="H35" s="33" t="inlineStr">
         <is>
@@ -1989,38 +1988,38 @@
         </is>
       </c>
       <c r="I35" s="35" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="J35" s="34" t="inlineStr">
         <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Point Loma Nazarene University</t>
         </is>
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>Loma Beat</t>
         </is>
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>lomabeat</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>lomabeat.com</t>
         </is>
       </c>
       <c r="E36" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F36" s="24" t="inlineStr">
@@ -2029,7 +2028,7 @@
         </is>
       </c>
       <c r="G36" s="30" t="n">
-        <v>5048</v>
+        <v>3950</v>
       </c>
       <c r="H36" s="33" t="inlineStr">
         <is>
@@ -2037,33 +2036,33 @@
         </is>
       </c>
       <c r="I36" s="35" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="J36" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>Texas Christian University</t>
+          <t>Southern Methodist University</t>
         </is>
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>TCU 360</t>
+          <t>The Daily Campus</t>
         </is>
       </c>
       <c r="C37" s="33" t="inlineStr">
         <is>
-          <t>tcu</t>
+          <t>smu</t>
         </is>
       </c>
       <c r="D37" s="33" t="inlineStr">
         <is>
-          <t>tcu360.com</t>
+          <t>smudailycampus.com</t>
         </is>
       </c>
       <c r="E37" s="33" t="inlineStr">
@@ -2077,7 +2076,7 @@
         </is>
       </c>
       <c r="G37" s="30" t="n">
-        <v>25690</v>
+        <v>26208</v>
       </c>
       <c r="H37" s="33" t="inlineStr">
         <is>
@@ -2088,6 +2087,102 @@
         <v>46291</v>
       </c>
       <c r="J37" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H38" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I38" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J38" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Texas Christian University</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>TCU 360</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>tcu</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>tcu360.com</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G39" s="30" t="n">
+        <v>25690</v>
+      </c>
+      <c r="H39" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J39" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -1349,37 +1349,37 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>University of North Carolina, Chapel Hill</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>The Daily Tar Heel</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>tarheel</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>dailytarheel.com</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -1387,44 +1387,44 @@
       <c r="I21" s="37" t="n">
         <v>46297</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Wave 10. Cloudflare SNO. wp-sitemap.xml (~82k URLs). Pace 10-14 s. Probe + 200-test before systemd.</t>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tarheel full run after 129/200 (71 empty_body, almost all /multimedia/ galleries and videos; those URLs now excluded). Resuming 129 of ~82k. Cloudflare SNO 10-14 s.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>University of California, Riverside</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>The Highlander</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>highlander</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>highlandernews.org</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -1432,9 +1432,9 @@
       <c r="I22" s="37" t="n">
         <v>46297</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Wave 10. Public campus listed only on the National tab. Cloudflare Yoast WP (~10k URLs). Pace 10-14 s. Probe + 200-test before systemd.</t>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@highlander full run after 176/200 (24 empty_body). Resuming 176 of ~10144. Cloudflare Yoast WP 10-14 s. Public campus listed only on the National tab.</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -178,6 +178,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -770,7 +773,7 @@
       </c>
       <c r="J7" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@northwestern; 44850 of 70720 (63.4%) as of 2026-10-02 13:50 UTC. empty_body=1790, http_301=3, http_403=32 (stable), network_error=1083, pre_2000=37.</t>
+          <t>newspaper-scraper@northwestern; 59500 of 70720 (84.1%) as of 2026-10-04 23:44 UTC. empty_body=3420, http_403=32 (stable), network_error=1083.</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1071,7 @@
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan; 35593 of 119764 (29.7%) as of 2026-10-02 13:50 UTC. empty_body=14, http_301=1130, http_429=3, network_error=2. Watch 429s.</t>
+          <t>newspaper-scraper@michigan; 61043 of 119764 (51.0%) as of 2026-10-04 23:44 UTC. http_301=1821, http_429=15. Watch 429s.</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1117,7 @@
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@ucsd Cloudflare canary 10-14s. 5450 of 22605 (24.1%) as of 2026-10-02 13:50 UTC. empty_body=3, http_500=2.</t>
+          <t>newspaper-scraper@ucsd; 19850 of 22605 (87.8%) as of 2026-10-04 23:44 UTC. empty_body=1603, http_500=2. Closest Public finish after TSL.</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1306,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Stony Brook University</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>The Statesman</t>
         </is>
@@ -1328,12 +1331,14 @@
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G20" s="33" t="n"/>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G20" s="33" t="n">
+        <v>13354</v>
+      </c>
       <c r="H20" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1344,7 +1349,7 @@
       </c>
       <c r="J20" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@statesman Cloudflare SNO 10-14s. 5047 of 13650 (37.0%) as of 2026-10-02 13:50 UTC. empty_body=106.</t>
+          <t>Finished 2026-10-04. 13354 articles of 13650 URLs (97.8%); 517 empty_body, 32 pre_2000. systemd inactive. File: ~/Downloads/statesman.csv</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1399,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>University of California, Riverside</t>
         </is>
       </c>
-      <c r="B22" s="0" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>The Highlander</t>
         </is>
@@ -1419,10 +1424,13 @@
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
+      <c r="F22" s="38" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>9791</v>
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
@@ -1434,189 +1442,180 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@highlander full run after 176/200 (24 empty_body). Resuming 176 of ~10144. Cloudflare Yoast WP 10-14 s. Public campus listed only on the National tab.</t>
+          <t>Finished 2026-10-04. 9791 articles of 10144 URLs (96.5%); 550 empty_body, 1 http_520, 1 http_525. systemd inactive. File: ~/Downloads/highlander.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>University of Massachusetts, Amherst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Massachusetts Daily Collegian</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>collegian</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dailycollegian.com</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I23" s="37" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Wave 11. Cloudflare SNO. wp-sitemap.xml (~52k URLs). Pace 10-14 s. Public flagship listed only on the National tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>University of Minnesota, Twin Cities</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Minnesota Daily</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mndaily</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mndaily.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I24" s="37" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Wave 11. Cloudflare SNO Yoast (~81k URLs). Pace 10-14 s. Public flagship listed only on the National tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>University of Pittsburgh</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Pitt News</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pitt</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>pittnews.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I25" s="37" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Wave 11. Cloudflare SNO Yoast (~56k URLs). Pace 10-14 s. Public university listed only on the National tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C24" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G24" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H24" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I24" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J24" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>Denison University</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>The Denisonian</t>
-        </is>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>denison</t>
-        </is>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>denisonian.com</t>
-        </is>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G25" s="30" t="n">
-        <v>3671</v>
-      </c>
-      <c r="H25" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I25" s="35" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J25" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>Franklin &amp; Marshall College</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>The College Reporter</t>
-        </is>
-      </c>
-      <c r="C26" s="33" t="inlineStr">
-        <is>
-          <t>fandm</t>
-        </is>
-      </c>
-      <c r="D26" s="33" t="inlineStr">
-        <is>
-          <t>the-college-reporter.com</t>
-        </is>
-      </c>
-      <c r="E26" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G26" s="30" t="n">
-        <v>3449</v>
-      </c>
-      <c r="H26" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I26" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J26" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
-        </is>
-      </c>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
+      <c r="J26" s="32" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Hillsdale College</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>The Collegian</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>hillsdale</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D27" s="33" t="inlineStr">
         <is>
-          <t>hillsdalecollegian.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E27" s="33" t="inlineStr">
@@ -1630,7 +1629,7 @@
         </is>
       </c>
       <c r="G27" s="30" t="n">
-        <v>15573</v>
+        <v>4039</v>
       </c>
       <c r="H27" s="33" t="inlineStr">
         <is>
@@ -1642,29 +1641,29 @@
       </c>
       <c r="J27" s="34" t="inlineStr">
         <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Occidental College</t>
+          <t>Denison University</t>
         </is>
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>The Occidental</t>
+          <t>The Denisonian</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>occidental</t>
+          <t>denison</t>
         </is>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
-          <t>theoccidentalnews.com</t>
+          <t>denisonian.com</t>
         </is>
       </c>
       <c r="E28" s="33" t="inlineStr">
@@ -1678,7 +1677,7 @@
         </is>
       </c>
       <c r="G28" s="30" t="n">
-        <v>9892</v>
+        <v>3671</v>
       </c>
       <c r="H28" s="33" t="inlineStr">
         <is>
@@ -1686,33 +1685,33 @@
         </is>
       </c>
       <c r="I28" s="35" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="J28" s="34" t="inlineStr">
         <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>Swarthmore College</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>The Phoenix</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
-          <t>swarthmore</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
-          <t>swarthmorephoenix.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E29" s="33" t="inlineStr">
@@ -1726,7 +1725,7 @@
         </is>
       </c>
       <c r="G29" s="30" t="n">
-        <v>12798</v>
+        <v>3449</v>
       </c>
       <c r="H29" s="33" t="inlineStr">
         <is>
@@ -1738,29 +1737,29 @@
       </c>
       <c r="J29" s="34" t="inlineStr">
         <is>
-          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Union College (NY)</t>
+          <t>Hillsdale College</t>
         </is>
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>Concordiensis</t>
+          <t>The Collegian</t>
         </is>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>union</t>
+          <t>hillsdale</t>
         </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
-          <t>concordiensis.com</t>
+          <t>hillsdalecollegian.com</t>
         </is>
       </c>
       <c r="E30" s="33" t="inlineStr">
@@ -1774,7 +1773,7 @@
         </is>
       </c>
       <c r="G30" s="30" t="n">
-        <v>1604</v>
+        <v>15573</v>
       </c>
       <c r="H30" s="33" t="inlineStr">
         <is>
@@ -1786,29 +1785,29 @@
       </c>
       <c r="J30" s="34" t="inlineStr">
         <is>
-          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>Wesleyan University</t>
+          <t>Occidental College</t>
         </is>
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>The Wesleyan Argus</t>
+          <t>The Occidental</t>
         </is>
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>wesleyan</t>
+          <t>occidental</t>
         </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
-          <t>wesleyanargus.com</t>
+          <t>theoccidentalnews.com</t>
         </is>
       </c>
       <c r="E31" s="33" t="inlineStr">
@@ -1821,8 +1820,8 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G31" s="24" t="n">
-        <v>21881</v>
+      <c r="G31" s="30" t="n">
+        <v>9892</v>
       </c>
       <c r="H31" s="33" t="inlineStr">
         <is>
@@ -1830,33 +1829,33 @@
         </is>
       </c>
       <c r="I31" s="35" t="n">
-        <v>46294</v>
+        <v>46292</v>
       </c>
       <c r="J31" s="34" t="inlineStr">
         <is>
-          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="inlineStr">
-        <is>
-          <t>Claremont Colleges</t>
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Swarthmore College</t>
         </is>
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>The Student Life</t>
+          <t>The Phoenix</t>
         </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>tsl</t>
+          <t>swarthmore</t>
         </is>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
-          <t>tsl.news</t>
+          <t>swarthmorephoenix.com</t>
         </is>
       </c>
       <c r="E32" s="33" t="inlineStr">
@@ -1864,210 +1863,210 @@
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G32" s="33" t="n"/>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>12798</v>
+      </c>
       <c r="H32" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
       <c r="I32" s="35" t="n">
-        <v>46295</v>
+        <v>46292</v>
       </c>
       <c r="J32" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tsl; 9600 of 11437 (83.9%) as of 2026-10-02 13:50 UTC. empty_body=14, http_403=15. Closest to finishing.</t>
+          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="n"/>
-      <c r="C33" s="32" t="n"/>
-      <c r="D33" s="32" t="n"/>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="32" t="n"/>
-      <c r="H33" s="32" t="n"/>
-      <c r="I33" s="32" t="n"/>
-      <c r="J33" s="32" t="n"/>
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Union College (NY)</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>Concordiensis</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>concordiensis.com</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>1604</v>
+      </c>
+      <c r="H33" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I33" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J33" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Biola University</t>
+          <t>Wesleyan University</t>
         </is>
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>The Chimes</t>
+          <t>The Wesleyan Argus</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>biola</t>
+          <t>wesleyan</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>chimesnewspaper.com</t>
+          <t>wesleyanargus.com</t>
         </is>
       </c>
       <c r="E34" s="33" t="inlineStr">
         <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>21881</v>
+      </c>
+      <c r="H34" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J34" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>Claremont Colleges</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>The Student Life</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>tsl</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>tsl.news</t>
+        </is>
+      </c>
+      <c r="E35" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F35" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G35" s="33" t="n"/>
+      <c r="H35" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I35" s="35" t="n">
+        <v>46295</v>
+      </c>
+      <c r="J35" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tsl; 9600 of 11437 (83.9%) as of 2026-10-02 13:50 UTC. empty_body=14, http_403=15. Closest to finishing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G34" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H34" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I34" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J34" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C35" s="33" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E35" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G35" s="30" t="n">
-        <v>682</v>
-      </c>
-      <c r="H35" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I35" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J35" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>Point Loma Nazarene University</t>
-        </is>
-      </c>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>Loma Beat</t>
-        </is>
-      </c>
-      <c r="C36" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat</t>
-        </is>
-      </c>
-      <c r="D36" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat.com</t>
-        </is>
-      </c>
-      <c r="E36" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G36" s="30" t="n">
-        <v>3950</v>
-      </c>
-      <c r="H36" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I36" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J36" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
-        </is>
-      </c>
+      <c r="B36" s="32" t="n"/>
+      <c r="C36" s="32" t="n"/>
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="32" t="n"/>
+      <c r="G36" s="32" t="n"/>
+      <c r="H36" s="32" t="n"/>
+      <c r="I36" s="32" t="n"/>
+      <c r="J36" s="32" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>The Daily Campus</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C37" s="33" t="inlineStr">
         <is>
-          <t>smu</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D37" s="33" t="inlineStr">
         <is>
-          <t>smudailycampus.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E37" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | National Universities</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
@@ -2076,7 +2075,7 @@
         </is>
       </c>
       <c r="G37" s="30" t="n">
-        <v>26208</v>
+        <v>11331</v>
       </c>
       <c r="H37" s="33" t="inlineStr">
         <is>
@@ -2088,34 +2087,34 @@
       </c>
       <c r="J37" s="34" t="inlineStr">
         <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Lipscomb University</t>
         </is>
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>Lipscomb Media</t>
         </is>
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>lipscomb</t>
         </is>
       </c>
       <c r="D38" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>lipscombmedia.com</t>
         </is>
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F38" s="24" t="inlineStr">
@@ -2124,7 +2123,7 @@
         </is>
       </c>
       <c r="G38" s="30" t="n">
-        <v>5048</v>
+        <v>682</v>
       </c>
       <c r="H38" s="33" t="inlineStr">
         <is>
@@ -2136,53 +2135,197 @@
       </c>
       <c r="J38" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="24" t="inlineStr">
         <is>
+          <t>Point Loma Nazarene University</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>Loma Beat</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat.com</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G39" s="30" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H39" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J39" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Campus</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>smu</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>smudailycampus.com</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G40" s="30" t="n">
+        <v>26208</v>
+      </c>
+      <c r="H40" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J40" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E41" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G41" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H41" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I41" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J41" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
           <t>Texas Christian University</t>
         </is>
       </c>
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>TCU 360</t>
         </is>
       </c>
-      <c r="C39" s="33" t="inlineStr">
+      <c r="C42" s="33" t="inlineStr">
         <is>
           <t>tcu</t>
         </is>
       </c>
-      <c r="D39" s="33" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
         <is>
           <t>tcu360.com</t>
         </is>
       </c>
-      <c r="E39" s="33" t="inlineStr">
+      <c r="E42" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G39" s="30" t="n">
+      <c r="G42" s="30" t="n">
         <v>25690</v>
       </c>
-      <c r="H39" s="33" t="inlineStr">
+      <c r="H42" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I39" s="35" t="n">
+      <c r="I42" s="35" t="n">
         <v>46291</v>
       </c>
-      <c r="J39" s="34" t="inlineStr">
+      <c r="J42" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -920,12 +920,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Duke University</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>The Chronicle</t>
         </is>
@@ -945,12 +945,14 @@
           <t>National Universities</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="n"/>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="n">
+        <v>22155</v>
+      </c>
       <c r="H11" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -961,7 +963,7 @@
       </c>
       <c r="J11" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@duke News-section listings only. 4600 rows as of 2026-10-02 13:50 UTC (no sitemap inventory). empty_body=17. Browser UA.</t>
+          <t>Finished 2026-10-05. News-section listings only, 22155 articles; 217 empty_body, 3 pre_2000. systemd inactive. Other Chronicle sections later. File: ~/Downloads/duke.csv</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1078,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>University of California San Diego</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>The UCSD Guardian</t>
         </is>
@@ -1101,12 +1103,14 @@
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F15" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="n"/>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="n">
+        <v>21079</v>
+      </c>
       <c r="H15" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@ucsd; 19850 of 22605 (87.8%) as of 2026-10-04 23:44 UTC. empty_body=1603, http_500=2. Closest Public finish after TSL.</t>
+          <t>Finished 2026-10-05. 21079 articles of 22605 URLs (93.2%); 1660 empty_body, 2 http_500. systemd inactive. File: ~/Downloads/ucsd.csv</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1433,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="0" t="n">
         <v>9791</v>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1447,37 +1451,37 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>University of Massachusetts, Amherst</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>The Massachusetts Daily Collegian</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>collegian</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>dailycollegian.com</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -1485,44 +1489,44 @@
       <c r="I23" s="37" t="n">
         <v>46299</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Wave 11. Cloudflare SNO. wp-sitemap.xml (~52k URLs). Pace 10-14 s. Public flagship listed only on the National tab.</t>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@collegian full run after 187/200 (2024 lastmod bucket). Resuming 187 of ~52k. Cloudflare SNO 10-14 s. /YYYY/MM/ pre-2000 skipped without fetch.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>University of Minnesota, Twin Cities</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>The Minnesota Daily</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>mndaily</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>mndaily.com</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -1530,44 +1534,44 @@
       <c r="I24" s="37" t="n">
         <v>46299</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Wave 11. Cloudflare SNO Yoast (~81k URLs). Pace 10-14 s. Public flagship listed only on the National tab.</t>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@mndaily; 190 of 80516 after 200-test. Was fetching 1996 /MM/DD/YYYY/ URLs; permalink skip added 2026-10-05 so pre-2000 does not consume fetches. Restart after deploy.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>University of Pittsburgh</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>The Pitt News</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>pitt</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>pittnews.com</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>queued</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -1575,143 +1579,137 @@
       <c r="I25" s="37" t="n">
         <v>46299</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Wave 11. Cloudflare SNO Yoast (~56k URLs). Pace 10-14 s. Public university listed only on the National tab.</t>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>Not cleared. VM 200-test hit HTTP 403 on /opinions/satire/ and entered block cooldown. Probe of two news articles was OK. Do not start full until a later 200-test passes.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Clemson University</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The Tiger</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>tiger</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>thetigercu.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I26" s="37" t="n">
+        <v>46300</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Wave 12. Cloudflare SNO Yoast (~7.4k URLs). Pace 10-14 s. Public university listed only on the National tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>New Jersey Institute of Technology</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Vector</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>vector</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>njitvector.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I27" s="37" t="n">
+        <v>46300</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Wave 12. Cloudflare SNO (~336 URLs). Pace 10-14 s. Public university listed only on the National tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="32" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E27" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G27" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H27" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I27" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J27" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>Denison University</t>
-        </is>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>The Denisonian</t>
-        </is>
-      </c>
-      <c r="C28" s="33" t="inlineStr">
-        <is>
-          <t>denison</t>
-        </is>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>denisonian.com</t>
-        </is>
-      </c>
-      <c r="E28" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G28" s="30" t="n">
-        <v>3671</v>
-      </c>
-      <c r="H28" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I28" s="35" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J28" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
-        </is>
-      </c>
+      <c r="B28" s="32" t="n"/>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="32" t="n"/>
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="n"/>
+      <c r="G28" s="32" t="n"/>
+      <c r="H28" s="32" t="n"/>
+      <c r="I28" s="32" t="n"/>
+      <c r="J28" s="32" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>Franklin &amp; Marshall College</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>The College Reporter</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
-          <t>fandm</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
-          <t>the-college-reporter.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E29" s="33" t="inlineStr">
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="G29" s="30" t="n">
-        <v>3449</v>
+        <v>4039</v>
       </c>
       <c r="H29" s="33" t="inlineStr">
         <is>
@@ -1737,29 +1735,29 @@
       </c>
       <c r="J29" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Hillsdale College</t>
+          <t>Denison University</t>
         </is>
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>The Collegian</t>
+          <t>The Denisonian</t>
         </is>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>hillsdale</t>
+          <t>denison</t>
         </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
-          <t>hillsdalecollegian.com</t>
+          <t>denisonian.com</t>
         </is>
       </c>
       <c r="E30" s="33" t="inlineStr">
@@ -1773,7 +1771,7 @@
         </is>
       </c>
       <c r="G30" s="30" t="n">
-        <v>15573</v>
+        <v>3671</v>
       </c>
       <c r="H30" s="33" t="inlineStr">
         <is>
@@ -1781,33 +1779,33 @@
         </is>
       </c>
       <c r="I30" s="35" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="J30" s="34" t="inlineStr">
         <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
+          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>Occidental College</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>The Occidental</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>occidental</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
-          <t>theoccidentalnews.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E31" s="33" t="inlineStr">
@@ -1821,7 +1819,7 @@
         </is>
       </c>
       <c r="G31" s="30" t="n">
-        <v>9892</v>
+        <v>3449</v>
       </c>
       <c r="H31" s="33" t="inlineStr">
         <is>
@@ -1833,29 +1831,29 @@
       </c>
       <c r="J31" s="34" t="inlineStr">
         <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>Swarthmore College</t>
+          <t>Hillsdale College</t>
         </is>
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>The Phoenix</t>
+          <t>The Collegian</t>
         </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>swarthmore</t>
+          <t>hillsdale</t>
         </is>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
-          <t>swarthmorephoenix.com</t>
+          <t>hillsdalecollegian.com</t>
         </is>
       </c>
       <c r="E32" s="33" t="inlineStr">
@@ -1869,7 +1867,7 @@
         </is>
       </c>
       <c r="G32" s="30" t="n">
-        <v>12798</v>
+        <v>15573</v>
       </c>
       <c r="H32" s="33" t="inlineStr">
         <is>
@@ -1881,29 +1879,29 @@
       </c>
       <c r="J32" s="34" t="inlineStr">
         <is>
-          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>Union College (NY)</t>
+          <t>Occidental College</t>
         </is>
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>Concordiensis</t>
+          <t>The Occidental</t>
         </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
-          <t>union</t>
+          <t>occidental</t>
         </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
-          <t>concordiensis.com</t>
+          <t>theoccidentalnews.com</t>
         </is>
       </c>
       <c r="E33" s="33" t="inlineStr">
@@ -1917,7 +1915,7 @@
         </is>
       </c>
       <c r="G33" s="30" t="n">
-        <v>1604</v>
+        <v>9892</v>
       </c>
       <c r="H33" s="33" t="inlineStr">
         <is>
@@ -1929,288 +1927,285 @@
       </c>
       <c r="J33" s="34" t="inlineStr">
         <is>
-          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="n">
+        <v>12798</v>
+      </c>
+      <c r="H34" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I34" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J34" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Union College (NY)</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Concordiensis</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>concordiensis.com</t>
+        </is>
+      </c>
+      <c r="E35" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G35" s="30" t="n">
+        <v>1604</v>
+      </c>
+      <c r="H35" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I35" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J35" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
           <t>Wesleyan University</t>
         </is>
       </c>
-      <c r="B34" s="33" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>The Wesleyan Argus</t>
         </is>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>wesleyan</t>
         </is>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>wesleyanargus.com</t>
         </is>
       </c>
-      <c r="E34" s="33" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G36" s="24" t="n">
         <v>21881</v>
       </c>
-      <c r="H34" s="33" t="inlineStr">
+      <c r="H36" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I34" s="35" t="n">
+      <c r="I36" s="35" t="n">
         <v>46294</v>
       </c>
-      <c r="J34" s="34" t="inlineStr">
+      <c r="J36" s="34" t="inlineStr">
         <is>
           <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="33" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>Claremont Colleges</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>The Student Life</t>
         </is>
       </c>
-      <c r="C35" s="33" t="inlineStr">
+      <c r="C37" s="33" t="inlineStr">
         <is>
           <t>tsl</t>
         </is>
       </c>
-      <c r="D35" s="33" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>tsl.news</t>
         </is>
       </c>
-      <c r="E35" s="33" t="inlineStr">
+      <c r="E37" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F35" s="33" t="inlineStr">
+      <c r="F37" s="33" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G35" s="33" t="n"/>
-      <c r="H35" s="33" t="inlineStr">
+      <c r="G37" s="33" t="n"/>
+      <c r="H37" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I35" s="35" t="n">
+      <c r="I37" s="35" t="n">
         <v>46295</v>
       </c>
-      <c r="J35" s="34" t="inlineStr">
+      <c r="J37" s="34" t="inlineStr">
         <is>
           <t>newspaper-scraper@tsl; 9600 of 11437 (83.9%) as of 2026-10-02 13:50 UTC. empty_body=14, http_403=15. Closest to finishing.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Carleton College</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The Carletonian</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>carleton</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>thecarletonian.com</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I38" s="37" t="n">
+        <v>46300</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Wave 12. Cloudflare SNO (~7.9k URLs). Pace 10-14 s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B36" s="32" t="n"/>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="32" t="n"/>
-      <c r="H36" s="32" t="n"/>
-      <c r="I36" s="32" t="n"/>
-      <c r="J36" s="32" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C37" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E37" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G37" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H37" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I37" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J37" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C38" s="33" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D38" s="33" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E38" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G38" s="30" t="n">
-        <v>682</v>
-      </c>
-      <c r="H38" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I38" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J38" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>Point Loma Nazarene University</t>
-        </is>
-      </c>
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t>Loma Beat</t>
-        </is>
-      </c>
-      <c r="C39" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat</t>
-        </is>
-      </c>
-      <c r="D39" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat.com</t>
-        </is>
-      </c>
-      <c r="E39" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G39" s="30" t="n">
-        <v>3950</v>
-      </c>
-      <c r="H39" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I39" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J39" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
-        </is>
-      </c>
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="32" t="n"/>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="32" t="n"/>
+      <c r="H39" s="32" t="n"/>
+      <c r="I39" s="32" t="n"/>
+      <c r="J39" s="32" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>The Daily Campus</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>smu</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D40" s="33" t="inlineStr">
         <is>
-          <t>smudailycampus.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E40" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | National Universities</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F40" s="24" t="inlineStr">
@@ -2219,7 +2214,7 @@
         </is>
       </c>
       <c r="G40" s="30" t="n">
-        <v>26208</v>
+        <v>11331</v>
       </c>
       <c r="H40" s="33" t="inlineStr">
         <is>
@@ -2231,34 +2226,34 @@
       </c>
       <c r="J40" s="34" t="inlineStr">
         <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Lipscomb University</t>
         </is>
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>Lipscomb Media</t>
         </is>
       </c>
       <c r="C41" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>lipscomb</t>
         </is>
       </c>
       <c r="D41" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>lipscombmedia.com</t>
         </is>
       </c>
       <c r="E41" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F41" s="24" t="inlineStr">
@@ -2267,7 +2262,7 @@
         </is>
       </c>
       <c r="G41" s="30" t="n">
-        <v>5048</v>
+        <v>682</v>
       </c>
       <c r="H41" s="33" t="inlineStr">
         <is>
@@ -2279,53 +2274,197 @@
       </c>
       <c r="J41" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="24" t="inlineStr">
         <is>
+          <t>Point Loma Nazarene University</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>Loma Beat</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat.com</t>
+        </is>
+      </c>
+      <c r="E42" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G42" s="30" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H42" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I42" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J42" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Campus</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>smu</t>
+        </is>
+      </c>
+      <c r="D43" s="33" t="inlineStr">
+        <is>
+          <t>smudailycampus.com</t>
+        </is>
+      </c>
+      <c r="E43" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G43" s="30" t="n">
+        <v>26208</v>
+      </c>
+      <c r="H43" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I43" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J43" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E44" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G44" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H44" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I44" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J44" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
           <t>Texas Christian University</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>TCU 360</t>
         </is>
       </c>
-      <c r="C42" s="33" t="inlineStr">
+      <c r="C45" s="33" t="inlineStr">
         <is>
           <t>tcu</t>
         </is>
       </c>
-      <c r="D42" s="33" t="inlineStr">
+      <c r="D45" s="33" t="inlineStr">
         <is>
           <t>tcu360.com</t>
         </is>
       </c>
-      <c r="E42" s="33" t="inlineStr">
+      <c r="E45" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F45" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G42" s="30" t="n">
+      <c r="G45" s="30" t="n">
         <v>25690</v>
       </c>
-      <c r="H42" s="33" t="inlineStr">
+      <c r="H45" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I42" s="35" t="n">
+      <c r="I45" s="35" t="n">
         <v>46291</v>
       </c>
-      <c r="J42" s="34" t="inlineStr">
+      <c r="J45" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -732,12 +732,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Northwestern University</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>The Daily Northwestern</t>
         </is>
@@ -757,12 +757,14 @@
           <t>National Universities</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G7" s="33" t="n"/>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>69041</v>
+      </c>
       <c r="H7" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -773,7 +775,7 @@
       </c>
       <c r="J7" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@northwestern; 59500 of 70720 (84.1%) as of 2026-10-04 23:44 UTC. empty_body=3420, http_403=32 (stable), network_error=1083.</t>
+          <t>Finished 2026-10-06. 69041 articles of 70720 URLs (97.6%); empty_body=3558, http_301=11, http_403=32, network_error=1083, pre_2000=46. systemd inactive. File: ~/Downloads/northwestern.csv</t>
         </is>
       </c>
     </row>
@@ -963,7 +965,7 @@
       </c>
       <c r="J11" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-05. News-section listings only, 22155 articles; 217 empty_body, 3 pre_2000. systemd inactive. Other Chronicle sections later. File: ~/Downloads/duke.csv</t>
+          <t>Finished 2026-10-05. News-section listings only, 22155 articles; 217 empty_body, 3 pre_2000. Other Chronicle sections later. File: ~/Downloads/duke.csv</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1075,7 @@
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan; 61043 of 119764 (51.0%) as of 2026-10-04 23:44 UTC. http_301=1821, http_429=15. Watch 429s.</t>
+          <t>newspaper-scraper@michigan; 78143 of 119764 (65.2%) as of 2026-10-06 14:31 UTC. http_429=15 (stable).</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1123,7 @@
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-05. 21079 articles of 22605 URLs (93.2%); 1660 empty_body, 2 http_500. systemd inactive. File: ~/Downloads/ucsd.csv</t>
+          <t>Finished 2026-10-05 before later downloads. 21079 articles of 22605 URLs (93.2%); 1660 empty_body, 2 http_500. systemd inactive. File: ~/Downloads/ucsd.csv</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1169,7 @@
       </c>
       <c r="J16" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@texan Cloudflare SNO 10-14s. 4747 of 51636 (9.2%) as of 2026-10-02 13:50 UTC. empty_body=74, http_500=3.</t>
+          <t>newspaper-scraper@texan; 31397 of 51636 (60.8%) as of 2026-10-06 14:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1215,7 @@
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@nexus Cloudflare WP 10-14s. 4637 of 40465 (11.5%) as of 2026-10-02 13:50 UTC. empty_body=453 (high; photo features). Watch.</t>
+          <t>newspaper-scraper@nexus; 28787 of 40465 (71.1%) as of 2026-10-06 14:31 UTC. empty_body=3838.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1261,7 @@
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@illini Cloudflare SNO 10-14s. 4900 of 100022 (4.9%) as of 2026-10-02 13:50 UTC. http_500=1, pre_2000=10.</t>
+          <t>newspaper-scraper@illini; 31000 of 100022 (31.0%) as of 2026-10-06 14:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1307,7 @@
       </c>
       <c r="J19" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@technician Cloudflare SNO 10-14s. 5083 of 41051 (12.4%) as of 2026-10-02 13:50 UTC. empty_body=82.</t>
+          <t>newspaper-scraper@technician; 32283 of 41051 (78.6%) as of 2026-10-06 14:31 UTC. empty_body=750.</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1355,7 @@
       </c>
       <c r="J20" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-04. 13354 articles of 13650 URLs (97.8%); 517 empty_body, 32 pre_2000. systemd inactive. File: ~/Downloads/statesman.csv</t>
+          <t>Finished 2026-10-04. 13354 of 13650 (97.8%); 517 empty_body, 32 pre_2000. File: ~/Downloads/statesman.csv</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1400,7 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tarheel full run after 129/200 (71 empty_body, almost all /multimedia/ galleries and videos; those URLs now excluded). Resuming 129 of ~82k. Cloudflare SNO 10-14 s.</t>
+          <t>newspaper-scraper@tarheel; 23379 of 81683 (28.6%) as of 2026-10-06 14:31 UTC. empty_body=3581, http_403=19.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1448,7 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>Finished 2026-10-04. 9791 articles of 10144 URLs (96.5%); 550 empty_body, 1 http_520, 1 http_525. systemd inactive. File: ~/Downloads/highlander.csv</t>
+          <t>Finished 2026-10-04. 9791 of 10144 (96.5%); 550 empty_body, 1 http_520, 1 http_525. File: ~/Downloads/highlander.csv</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1493,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@collegian full run after 187/200 (2024 lastmod bucket). Resuming 187 of ~52k. Cloudflare SNO 10-14 s. /YYYY/MM/ pre-2000 skipped without fetch.</t>
+          <t>newspaper-scraper@collegian; 10537 of 52185 (20.2%) as of 2026-10-06 14:31 UTC. empty_body=26, pre_2000=234.</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1538,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@mndaily; 190 of 80516 after 200-test. Was fetching 1996 /MM/DD/YYYY/ URLs; permalink skip added 2026-10-05 so pre-2000 does not consume fetches. Restart after deploy.</t>
+          <t>newspaper-scraper@mndaily; 7240 of 80516 (9.0%) as of 2026-10-06 14:31 UTC. pre_2000=14440 skipped.</t>
         </is>
       </c>
     </row>
@@ -1581,42 +1583,42 @@
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>Not cleared. VM 200-test hit HTTP 403 on /opinions/satire/ and entered block cooldown. Probe of two news articles was OK. Do not start full until a later 200-test passes.</t>
+          <t>Not cleared. VM 200-test HTTP 403 on /opinions/satire/; block cooldown. Probe of two news articles OK. Do not start full until a later 200-test passes.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>Clemson University</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>The Tiger</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>tiger</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>thetigercu.com</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -1624,44 +1626,47 @@
       <c r="I26" s="37" t="n">
         <v>46300</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Wave 12. Cloudflare SNO Yoast (~7.4k URLs). Pace 10-14 s. Public university listed only on the National tab.</t>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tiger; 5688 of 7455 (76.3%) as of 2026-10-06 14:31 UTC. empty_body=125.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>New Jersey Institute of Technology</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>The Vector</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>vector</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>njitvector.com</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="F27" s="38" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>335</v>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -1669,9 +1674,9 @@
       <c r="I27" s="37" t="n">
         <v>46300</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Wave 12. Cloudflare SNO (~336 URLs). Pace 10-14 s. Public university listed only on the National tab.</t>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>Finished 2026-10-05. 335 of 336 (99.7%); 1 empty_body. File: ~/Downloads/vector.csv</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2081,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>Claremont Colleges</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>The Student Life</t>
         </is>
@@ -2101,12 +2106,14 @@
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F37" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G37" s="33" t="n"/>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G37" s="33" t="n">
+        <v>11405</v>
+      </c>
       <c r="H37" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -2117,42 +2124,42 @@
       </c>
       <c r="J37" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tsl; 9600 of 11437 (83.9%) as of 2026-10-02 13:50 UTC. empty_body=14, http_403=15. Closest to finishing.</t>
+          <t>Finished 2026-10-04. 11405 of 11437 (99.7%); 16 empty_body, 15 http_403, 1 http_404. File: ~/Downloads/tsl.csv</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>Carleton College</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>The Carletonian</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>carleton</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>thecarletonian.com</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
@@ -2160,143 +2167,137 @@
       <c r="I38" s="37" t="n">
         <v>46300</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Wave 12. Cloudflare SNO (~7.9k URLs). Pace 10-14 s.</t>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@carleton; 5800 of 7941 (73.0%) as of 2026-10-06 14:31 UTC. empty_body=14.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>Macalester College</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>The Mac Weekly</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>macweekly</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>themacweekly.com</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I39" s="37" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>Wave 13 Liberal Arts SNO (Yoast). ~9418 URLs, Cloudflare 10–14 s. Fills a slot after Northwestern. Probe + 200-test next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>Grinnell College</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>Scarlet &amp; Black</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>sandb</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>thesandb.com</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I40" s="37" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>Wave 13 Liberal Arts SNO. ~9196 URLs, Cloudflare 10–14 s. Use wp-sitemap.xml. Fills a slot after Vector. Probe + 200-test next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="32" t="n"/>
-      <c r="D39" s="32" t="n"/>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="32" t="n"/>
-      <c r="H39" s="32" t="n"/>
-      <c r="I39" s="32" t="n"/>
-      <c r="J39" s="32" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C40" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D40" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E40" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G40" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H40" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I40" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J40" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B41" s="33" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C41" s="33" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D41" s="33" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E41" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G41" s="30" t="n">
-        <v>682</v>
-      </c>
-      <c r="H41" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I41" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J41" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
-        </is>
-      </c>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="32" t="n"/>
+      <c r="D41" s="32" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="32" t="n"/>
+      <c r="H41" s="32" t="n"/>
+      <c r="I41" s="32" t="n"/>
+      <c r="J41" s="32" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>Point Loma Nazarene University</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>Loma Beat</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>lomabeat</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>lomabeat.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E42" s="33" t="inlineStr">
@@ -2310,7 +2311,7 @@
         </is>
       </c>
       <c r="G42" s="30" t="n">
-        <v>3950</v>
+        <v>11331</v>
       </c>
       <c r="H42" s="33" t="inlineStr">
         <is>
@@ -2318,38 +2319,38 @@
         </is>
       </c>
       <c r="I42" s="35" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="J42" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Lipscomb University</t>
         </is>
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>The Daily Campus</t>
+          <t>Lipscomb Media</t>
         </is>
       </c>
       <c r="C43" s="33" t="inlineStr">
         <is>
-          <t>smu</t>
+          <t>lipscomb</t>
         </is>
       </c>
       <c r="D43" s="33" t="inlineStr">
         <is>
-          <t>smudailycampus.com</t>
+          <t>lipscombmedia.com</t>
         </is>
       </c>
       <c r="E43" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | National Universities</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F43" s="24" t="inlineStr">
@@ -2358,7 +2359,7 @@
         </is>
       </c>
       <c r="G43" s="30" t="n">
-        <v>26208</v>
+        <v>682</v>
       </c>
       <c r="H43" s="33" t="inlineStr">
         <is>
@@ -2366,38 +2367,38 @@
         </is>
       </c>
       <c r="I43" s="35" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="J43" s="34" t="inlineStr">
         <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Point Loma Nazarene University</t>
         </is>
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>Loma Beat</t>
         </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>lomabeat</t>
         </is>
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>lomabeat.com</t>
         </is>
       </c>
       <c r="E44" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F44" s="24" t="inlineStr">
@@ -2406,7 +2407,7 @@
         </is>
       </c>
       <c r="G44" s="30" t="n">
-        <v>5048</v>
+        <v>3950</v>
       </c>
       <c r="H44" s="33" t="inlineStr">
         <is>
@@ -2414,33 +2415,33 @@
         </is>
       </c>
       <c r="I44" s="35" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="J44" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>Texas Christian University</t>
+          <t>Southern Methodist University</t>
         </is>
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>TCU 360</t>
+          <t>The Daily Campus</t>
         </is>
       </c>
       <c r="C45" s="33" t="inlineStr">
         <is>
-          <t>tcu</t>
+          <t>smu</t>
         </is>
       </c>
       <c r="D45" s="33" t="inlineStr">
         <is>
-          <t>tcu360.com</t>
+          <t>smudailycampus.com</t>
         </is>
       </c>
       <c r="E45" s="33" t="inlineStr">
@@ -2454,7 +2455,7 @@
         </is>
       </c>
       <c r="G45" s="30" t="n">
-        <v>25690</v>
+        <v>26208</v>
       </c>
       <c r="H45" s="33" t="inlineStr">
         <is>
@@ -2465,6 +2466,102 @@
         <v>46291</v>
       </c>
       <c r="J45" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D46" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E46" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G46" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H46" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I46" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J46" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>Texas Christian University</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>TCU 360</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>tcu</t>
+        </is>
+      </c>
+      <c r="D47" s="33" t="inlineStr">
+        <is>
+          <t>tcu360.com</t>
+        </is>
+      </c>
+      <c r="E47" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G47" s="30" t="n">
+        <v>25690</v>
+      </c>
+      <c r="H47" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I47" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J47" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -2201,8 +2201,11 @@
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>191</v>
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
@@ -2214,7 +2217,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>Wave 13 Liberal Arts SNO (Yoast). ~9418 URLs, Cloudflare 10–14 s. Fills a slot after Northwestern. Probe + 200-test next.</t>
+          <t>newspaper-scraper@macweekly; 200-test OK (191/200, empty_body=9). systemd enabled 2026-10-06 16:28 UTC. Liberal Arts SNO Yoast, ~9420 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
         </is>
       </c>
     </row>
@@ -2246,8 +2249,11 @@
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>190</v>
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
@@ -2259,7 +2265,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>Wave 13 Liberal Arts SNO. ~9196 URLs, Cloudflare 10–14 s. Use wp-sitemap.xml. Fills a slot after Vector. Probe + 200-test next.</t>
+          <t>newspaper-scraper@sandb; 200-test OK (190/200, empty_body=10, mostly comics/photos). systemd enabled 2026-10-06 16:28 UTC. Liberal Arts SNO, ~9228 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -1615,8 +1615,11 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>7337</v>
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
@@ -1628,7 +1631,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tiger; 5688 of 7455 (76.3%) as of 2026-10-06 14:31 UTC. empty_body=125.</t>
+          <t>Finished 2026-10-06. 7337 of 7455 (98.4%); empty_body=130. systemd inactive. File: ~/Downloads/tiger.csv</t>
         </is>
       </c>
     </row>
@@ -2156,8 +2159,11 @@
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>7805</v>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
@@ -2169,7 +2175,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@carleton; 5800 of 7941 (73.0%) as of 2026-10-06 14:31 UTC. empty_body=14.</t>
+          <t>Finished 2026-10-06. 7805 of 7941 (98.3%); empty_body=135, http_404=1. systemd inactive. File: ~/Downloads/carleton.csv</t>
         </is>
       </c>
     </row>
@@ -2204,8 +2210,8 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>191</v>
+      <c r="G39" s="0" t="n">
+        <v>6141</v>
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
@@ -2217,7 +2223,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@macweekly; 200-test OK (191/200, empty_body=9). systemd enabled 2026-10-06 16:28 UTC. Liberal Arts SNO Yoast, ~9420 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
+          <t>newspaper-scraper@macweekly; 6141 of 9420 (65.2%) as of 2026-10-07 14:02 UTC. empty_body=218.</t>
         </is>
       </c>
     </row>
@@ -2252,8 +2258,8 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>190</v>
+      <c r="G40" s="0" t="n">
+        <v>6190</v>
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
@@ -2265,141 +2271,137 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@sandb; 200-test OK (190/200, empty_body=10, mostly comics/photos). systemd enabled 2026-10-06 16:28 UTC. Liberal Arts SNO, ~9228 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
+          <t>newspaper-scraper@sandb; 6190 of 9228 (67.1%) as of 2026-10-07 14:02 UTC. empty_body=80.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>Colgate University</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>The Colgate Maroon-News</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>colgate</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>thecolgatemaroonnews.com</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="n"/>
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I41" s="37" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>Wave 14 Liberal Arts SNO. ~15458 URLs, Cloudflare 10–14 s. Use wp-sitemap.xml. Fills a slot after Carleton. Probe + 200-test next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>Bucknell University</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>The Bucknellian</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>bucknellian</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>bucknellian.net</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="n"/>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I42" s="37" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>Wave 14 Liberal Arts SNO (Yoast). ~11585 URLs, Cloudflare 10–14 s. Fills a slot after Clemson. Probe + 200-test next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B41" s="32" t="n"/>
-      <c r="C41" s="32" t="n"/>
-      <c r="D41" s="32" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="32" t="n"/>
-      <c r="H41" s="32" t="n"/>
-      <c r="I41" s="32" t="n"/>
-      <c r="J41" s="32" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C42" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D42" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E42" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G42" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H42" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I42" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J42" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B43" s="33" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C43" s="33" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D43" s="33" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E43" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G43" s="30" t="n">
-        <v>682</v>
-      </c>
-      <c r="H43" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I43" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J43" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
-        </is>
-      </c>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="32" t="n"/>
+      <c r="D43" s="32" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="32" t="n"/>
+      <c r="J43" s="32" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>Point Loma Nazarene University</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>Loma Beat</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>lomabeat</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>lomabeat.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E44" s="33" t="inlineStr">
@@ -2413,7 +2415,7 @@
         </is>
       </c>
       <c r="G44" s="30" t="n">
-        <v>3950</v>
+        <v>11331</v>
       </c>
       <c r="H44" s="33" t="inlineStr">
         <is>
@@ -2421,38 +2423,38 @@
         </is>
       </c>
       <c r="I44" s="35" t="n">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="J44" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Lipscomb University</t>
         </is>
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>The Daily Campus</t>
+          <t>Lipscomb Media</t>
         </is>
       </c>
       <c r="C45" s="33" t="inlineStr">
         <is>
-          <t>smu</t>
+          <t>lipscomb</t>
         </is>
       </c>
       <c r="D45" s="33" t="inlineStr">
         <is>
-          <t>smudailycampus.com</t>
+          <t>lipscombmedia.com</t>
         </is>
       </c>
       <c r="E45" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | National Universities</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F45" s="24" t="inlineStr">
@@ -2461,7 +2463,7 @@
         </is>
       </c>
       <c r="G45" s="30" t="n">
-        <v>26208</v>
+        <v>682</v>
       </c>
       <c r="H45" s="33" t="inlineStr">
         <is>
@@ -2469,38 +2471,38 @@
         </is>
       </c>
       <c r="I45" s="35" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="J45" s="34" t="inlineStr">
         <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Point Loma Nazarene University</t>
         </is>
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>Loma Beat</t>
         </is>
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>lomabeat</t>
         </is>
       </c>
       <c r="D46" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>lomabeat.com</t>
         </is>
       </c>
       <c r="E46" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F46" s="24" t="inlineStr">
@@ -2509,7 +2511,7 @@
         </is>
       </c>
       <c r="G46" s="30" t="n">
-        <v>5048</v>
+        <v>3950</v>
       </c>
       <c r="H46" s="33" t="inlineStr">
         <is>
@@ -2517,33 +2519,33 @@
         </is>
       </c>
       <c r="I46" s="35" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="J46" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>Texas Christian University</t>
+          <t>Southern Methodist University</t>
         </is>
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>TCU 360</t>
+          <t>The Daily Campus</t>
         </is>
       </c>
       <c r="C47" s="33" t="inlineStr">
         <is>
-          <t>tcu</t>
+          <t>smu</t>
         </is>
       </c>
       <c r="D47" s="33" t="inlineStr">
         <is>
-          <t>tcu360.com</t>
+          <t>smudailycampus.com</t>
         </is>
       </c>
       <c r="E47" s="33" t="inlineStr">
@@ -2557,7 +2559,7 @@
         </is>
       </c>
       <c r="G47" s="30" t="n">
-        <v>25690</v>
+        <v>26208</v>
       </c>
       <c r="H47" s="33" t="inlineStr">
         <is>
@@ -2568,6 +2570,102 @@
         <v>46291</v>
       </c>
       <c r="J47" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D48" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E48" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H48" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I48" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J48" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>Texas Christian University</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>TCU 360</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>tcu</t>
+        </is>
+      </c>
+      <c r="D49" s="33" t="inlineStr">
+        <is>
+          <t>tcu360.com</t>
+        </is>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G49" s="30" t="n">
+        <v>25690</v>
+      </c>
+      <c r="H49" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I49" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J49" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -1618,7 +1618,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="0" t="n">
         <v>7337</v>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -2162,7 +2162,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="0" t="n">
         <v>7805</v>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2303,10 +2303,12 @@
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G41" s="0" t="n"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>200</v>
+      </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -2317,7 +2319,7 @@
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>Wave 14 Liberal Arts SNO. ~15458 URLs, Cloudflare 10–14 s. Use wp-sitemap.xml. Fills a slot after Carleton. Probe + 200-test next.</t>
+          <t>newspaper-scraper@colgate; 200-test OK (200/200, no failures). systemd enabled 2026-10-07 16:27 UTC. Liberal Arts SNO, ~15489 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
         </is>
       </c>
     </row>
@@ -2349,10 +2351,12 @@
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G42" s="0" t="n"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>200</v>
+      </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -2363,7 +2367,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>Wave 14 Liberal Arts SNO (Yoast). ~11585 URLs, Cloudflare 10–14 s. Fills a slot after Clemson. Probe + 200-test next.</t>
+          <t>newspaper-scraper@bucknellian; 200-test OK (200/200, no failures). systemd enabled 2026-10-07 16:27 UTC. Liberal Arts SNO Yoast, ~11583 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -1064,7 +1064,9 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G14" s="33" t="n"/>
+      <c r="G14" s="33" t="n">
+        <v>99943</v>
+      </c>
       <c r="H14" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1075,7 +1077,7 @@
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan; 78143 of 119764 (65.2%) as of 2026-10-06 14:31 UTC. http_429=15 (stable).</t>
+          <t>newspaper-scraper@michigan; 99943 of 119764 (83.4%) as of 2026-10-08 17:11 UTC. http_429=21 (was 16 on Oct 7). http_301=1821.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1160,9 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G16" s="33" t="n"/>
+      <c r="G16" s="33" t="n">
+        <v>45147</v>
+      </c>
       <c r="H16" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="J16" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@texan; 31397 of 51636 (60.8%) as of 2026-10-06 14:31 UTC.</t>
+          <t>newspaper-scraper@texan; 45147 of 51636 (87.4%) as of 2026-10-08 17:11 UTC. empty_body=407, http_403=7.</t>
         </is>
       </c>
     </row>
@@ -1201,10 +1205,12 @@
       </c>
       <c r="F17" s="33" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G17" s="33" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>37215</v>
+      </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1215,7 +1221,7 @@
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@nexus; 28787 of 40465 (71.1%) as of 2026-10-06 14:31 UTC. empty_body=3838.</t>
+          <t>Finished 2026-10-07. 37215 of 40465 (92.0%); empty_body=4202, http_404=1. systemd inactive. File: ~/Downloads/nexus.csv</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1256,9 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G18" s="33" t="n"/>
+      <c r="G18" s="33" t="n">
+        <v>44450</v>
+      </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1261,7 +1269,7 @@
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@illini; 31000 of 100022 (31.0%) as of 2026-10-06 14:31 UTC.</t>
+          <t>newspaper-scraper@illini; 44450 of 100022 (44.4%) as of 2026-10-08 17:11 UTC.</t>
         </is>
       </c>
     </row>
@@ -1293,10 +1301,12 @@
       </c>
       <c r="F19" s="33" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G19" s="33" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="n">
+        <v>40280</v>
+      </c>
       <c r="H19" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1307,7 +1317,7 @@
       </c>
       <c r="J19" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@technician; 32283 of 41051 (78.6%) as of 2026-10-06 14:31 UTC. empty_body=750.</t>
+          <t>Finished 2026-10-07. 40280 of 41051 (98.1%); empty_body=1017, http_521=1. systemd inactive. File: ~/Downloads/technician.csv</t>
         </is>
       </c>
     </row>
@@ -1390,6 +1400,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G21" s="0" t="n">
+        <v>36129</v>
+      </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1400,7 +1413,7 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tarheel; 23379 of 81683 (28.6%) as of 2026-10-06 14:31 UTC. empty_body=3581, http_403=19.</t>
+          <t>newspaper-scraper@tarheel; 36129 of 81683 (44.2%) as of 2026-10-08 17:11 UTC. empty_body=5194, http_403=28.</t>
         </is>
       </c>
     </row>
@@ -1483,6 +1496,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G23" s="0" t="n">
+        <v>24237</v>
+      </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1493,7 +1509,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@collegian; 10537 of 52185 (20.2%) as of 2026-10-06 14:31 UTC. empty_body=26, pre_2000=234.</t>
+          <t>newspaper-scraper@collegian; 24237 of 52185 (46.4%) as of 2026-10-08 17:11 UTC. empty_body=306, pre_2000=234.</t>
         </is>
       </c>
     </row>
@@ -1528,6 +1544,9 @@
           <t>running</t>
         </is>
       </c>
+      <c r="G24" s="0" t="n">
+        <v>21590</v>
+      </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
@@ -1538,7 +1557,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@mndaily; 7240 of 80516 (9.0%) as of 2026-10-06 14:31 UTC. pre_2000=14440 skipped.</t>
+          <t>newspaper-scraper@mndaily; 21590 of 80516 (26.8%) as of 2026-10-08 17:11 UTC. pre_2000=14440 skipped.</t>
         </is>
       </c>
     </row>
@@ -2207,11 +2226,11 @@
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G39" s="0" t="n">
-        <v>6141</v>
+        <v>9036</v>
       </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
@@ -2223,7 +2242,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@macweekly; 6141 of 9420 (65.2%) as of 2026-10-07 14:02 UTC. empty_body=218.</t>
+          <t>Finished 2026-10-08. 9036 of 9420 (95.9%); empty_body=392, network_error=1. systemd inactive. File: ~/Downloads/macweekly.csv</t>
         </is>
       </c>
     </row>
@@ -2255,11 +2274,11 @@
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G40" s="0" t="n">
-        <v>6190</v>
+        <v>9054</v>
       </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
@@ -2271,7 +2290,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@sandb; 6190 of 9228 (67.1%) as of 2026-10-07 14:02 UTC. empty_body=80.</t>
+          <t>Finished 2026-10-08. 9054 of 9228 (98.1%); empty_body=184. systemd inactive. File: ~/Downloads/sandb.csv</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2326,7 @@
         </is>
       </c>
       <c r="G41" s="0" t="n">
-        <v>200</v>
+        <v>7250</v>
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
@@ -2319,7 +2338,7 @@
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@colgate; 200-test OK (200/200, no failures). systemd enabled 2026-10-07 16:27 UTC. Liberal Arts SNO, ~15489 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
+          <t>newspaper-scraper@colgate; 7250 of 15489 (46.8%) as of 2026-10-08 17:11 UTC. http_500=1.</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2374,7 @@
         </is>
       </c>
       <c r="G42" s="0" t="n">
-        <v>200</v>
+        <v>7300</v>
       </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
@@ -2367,7 +2386,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@bucknellian; 200-test OK (200/200, no failures). systemd enabled 2026-10-07 16:27 UTC. Liberal Arts SNO Yoast, ~11583 URLs, Cloudflare 10–14 s. Resumes from 200-test CSV.</t>
+          <t>newspaper-scraper@bucknellian; 7300 of 11583 (63.0%) as of 2026-10-08 17:11 UTC. empty_body=11, http_404=2.</t>
         </is>
       </c>
     </row>
@@ -5497,6 +5516,11 @@
           <t>#50</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://bachelor.wabash.edu/</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -5507,6 +5531,11 @@
       <c r="B55" s="9" t="inlineStr">
         <is>
           <t>#50</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://wheatonwire.com/</t>
         </is>
       </c>
     </row>
@@ -6138,6 +6167,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -970,280 +970,272 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>Public Universities</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="32" t="n"/>
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>George Washington University</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>The Hatchet</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>hatchet</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>gwhatchet.com</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G12" s="33" t="n"/>
+      <c r="H12" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J12" s="34" t="inlineStr">
+        <is>
+          <t>Wave 15 ready buffer. Cloudflare SNO ~60k URLs. Probe + 200-test next.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>New University</t>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>The Stanford Daily</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>uci</t>
+          <t>stanford</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>newuniversity.org</t>
+          <t>stanforddaily.com</t>
         </is>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>National Universities | Public Universities</t>
+          <t>National Universities</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G13" s="30" t="n">
-        <v>17411</v>
-      </c>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="n"/>
       <c r="H13" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I13" s="35" t="n">
-        <v>46293</v>
+      <c r="I13" s="36" t="n">
+        <v>46303</v>
       </c>
       <c r="J13" s="34" t="inlineStr">
         <is>
-          <t>Finished. 17411 articles of 17447 URLs (99.8%); 165 empty_body. systemd inactive. File: ~/Downloads/uci.csv</t>
+          <t>Wave 15 ready buffer. Cloudflare WP Yoast ~39k URLs. Probe + 200-test next.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>University of Michigan</t>
-        </is>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>The Michigan Daily</t>
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Marquette University</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Marquette Wire</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>michigan</t>
+          <t>marquette</t>
         </is>
       </c>
       <c r="D14" s="33" t="inlineStr">
         <is>
-          <t>michigandaily.com</t>
+          <t>marquettewire.org</t>
         </is>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F14" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G14" s="33" t="n">
-        <v>99943</v>
-      </c>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G14" s="33" t="n"/>
       <c r="H14" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I14" s="35" t="n">
-        <v>46293</v>
+      <c r="I14" s="36" t="n">
+        <v>46303</v>
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan; 99943 of 119764 (83.4%) as of 2026-10-08 17:11 UTC. http_429=21 (was 16 on Oct 7). http_301=1821.</t>
+          <t>Wave 15 ready buffer. Cloudflare SNO ~32k URLs. Probe + 200-test next.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>The UCSD Guardian</t>
+          <t>Washington Square News</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>ucsd</t>
+          <t>nyu</t>
         </is>
       </c>
       <c r="D15" s="33" t="inlineStr">
         <is>
-          <t>ucsdguardian.org</t>
+          <t>nyunews.com</t>
         </is>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="n"/>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I15" s="36" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J15" s="34" t="inlineStr">
+        <is>
+          <t>Wave 15 ready buffer. Cloudflare SNO Yoast ~22k URLs. Probe + 200-test next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Public Universities</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+      <c r="H16" s="32" t="n"/>
+      <c r="I16" s="32" t="n"/>
+      <c r="J16" s="32" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>University of California, Irvine</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>New University</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>uci</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>newuniversity.org</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G15" s="33" t="n">
-        <v>21079</v>
-      </c>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="G17" s="30" t="n">
+        <v>17411</v>
+      </c>
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I15" s="36" t="n">
-        <v>46296</v>
-      </c>
-      <c r="J15" s="34" t="inlineStr">
-        <is>
-          <t>Finished 2026-10-05 before later downloads. 21079 articles of 22605 URLs (93.2%); 1660 empty_body, 2 http_500. systemd inactive. File: ~/Downloads/ucsd.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>University of Texas at Austin</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>The Daily Texan</t>
-        </is>
-      </c>
-      <c r="C16" s="33" t="inlineStr">
-        <is>
-          <t>texan</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>thedailytexan.com</t>
-        </is>
-      </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F16" s="33" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G16" s="33" t="n">
-        <v>45147</v>
-      </c>
-      <c r="H16" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>46296</v>
-      </c>
-      <c r="J16" s="34" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@texan; 45147 of 51636 (87.4%) as of 2026-10-08 17:11 UTC. empty_body=407, http_403=7.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
-        <is>
-          <t>University of California, Santa Barbara</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>Daily Nexus</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>nexus</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>dailynexus.com</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F17" s="33" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G17" s="33" t="n">
-        <v>37215</v>
-      </c>
-      <c r="H17" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I17" s="36" t="n">
-        <v>46296</v>
+      <c r="I17" s="35" t="n">
+        <v>46293</v>
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-07. 37215 of 40465 (92.0%); empty_body=4202, http_404=1. systemd inactive. File: ~/Downloads/nexus.csv</t>
+          <t>Finished. 17411 articles of 17447 URLs (99.8%); 165 empty_body. systemd inactive. File: ~/Downloads/uci.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Michigan</t>
         </is>
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>The Daily Illini</t>
+          <t>The Michigan Daily</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>illini</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="D18" s="33" t="inlineStr">
         <is>
-          <t>dailyillini.com</t>
+          <t>michigandaily.com</t>
         </is>
       </c>
       <c r="E18" s="33" t="inlineStr">
@@ -1257,41 +1249,41 @@
         </is>
       </c>
       <c r="G18" s="33" t="n">
-        <v>44450</v>
+        <v>99943</v>
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I18" s="36" t="n">
-        <v>46296</v>
+      <c r="I18" s="35" t="n">
+        <v>46293</v>
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@illini; 44450 of 100022 (44.4%) as of 2026-10-08 17:11 UTC.</t>
+          <t>newspaper-scraper@michigan; 99943 of 119764 (83.4%) as of 2026-10-08 17:11 UTC. http_429=21 (was 16 on Oct 7). http_301=1821.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
-        <is>
-          <t>North Carolina State University</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>Technician</t>
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>University of California San Diego</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>The UCSD Guardian</t>
         </is>
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>technician</t>
+          <t>ucsd</t>
         </is>
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>technicianonline.com</t>
+          <t>ucsdguardian.org</t>
         </is>
       </c>
       <c r="E19" s="33" t="inlineStr">
@@ -1299,13 +1291,13 @@
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
       <c r="G19" s="33" t="n">
-        <v>40280</v>
+        <v>21079</v>
       </c>
       <c r="H19" s="33" t="inlineStr">
         <is>
@@ -1317,29 +1309,29 @@
       </c>
       <c r="J19" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-07. 40280 of 41051 (98.1%); empty_body=1017, http_521=1. systemd inactive. File: ~/Downloads/technician.csv</t>
+          <t>Finished 2026-10-05 before later downloads. 21079 articles of 22605 URLs (93.2%); 1660 empty_body, 2 http_500. systemd inactive. File: ~/Downloads/ucsd.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>Stony Brook University</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>The Statesman</t>
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>University of Texas at Austin</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Texan</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>statesman</t>
+          <t>texan</t>
         </is>
       </c>
       <c r="D20" s="33" t="inlineStr">
         <is>
-          <t>sbstatesman.com</t>
+          <t>thedailytexan.com</t>
         </is>
       </c>
       <c r="E20" s="33" t="inlineStr">
@@ -1347,13 +1339,13 @@
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
         </is>
       </c>
       <c r="G20" s="33" t="n">
-        <v>13354</v>
+        <v>45147</v>
       </c>
       <c r="H20" s="33" t="inlineStr">
         <is>
@@ -1365,570 +1357,570 @@
       </c>
       <c r="J20" s="34" t="inlineStr">
         <is>
+          <t>newspaper-scraper@texan; 45147 of 51636 (87.4%) as of 2026-10-08 17:11 UTC. empty_body=407, http_403=7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>University of California, Santa Barbara</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Daily Nexus</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>nexus</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>dailynexus.com</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="n">
+        <v>37215</v>
+      </c>
+      <c r="H21" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J21" s="34" t="inlineStr">
+        <is>
+          <t>Finished 2026-10-07. 37215 of 40465 (92.0%); empty_body=4202, http_404=1. systemd inactive. File: ~/Downloads/nexus.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>University of Illinois Urbana-Champaign</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Illini</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>illini</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>dailyillini.com</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="n">
+        <v>44450</v>
+      </c>
+      <c r="H22" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I22" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J22" s="34" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@illini; 44450 of 100022 (44.4%) as of 2026-10-08 17:11 UTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>North Carolina State University</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>technician</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>technicianonline.com</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G23" s="33" t="n">
+        <v>40280</v>
+      </c>
+      <c r="H23" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I23" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J23" s="34" t="inlineStr">
+        <is>
+          <t>Finished 2026-10-07. 40280 of 41051 (98.1%); empty_body=1017, http_521=1. systemd inactive. File: ~/Downloads/technician.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Stony Brook University</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>The Statesman</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>statesman</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>sbstatesman.com</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G24" s="33" t="n">
+        <v>13354</v>
+      </c>
+      <c r="H24" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I24" s="36" t="n">
+        <v>46296</v>
+      </c>
+      <c r="J24" s="34" t="inlineStr">
+        <is>
           <t>Finished 2026-10-04. 13354 of 13650 (97.8%); 517 empty_body, 32 pre_2000. File: ~/Downloads/statesman.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>University of North Carolina, Chapel Hill</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>The Daily Tar Heel</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>tarheel</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t>dailytarheel.com</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G21" s="0" t="n">
-        <v>36129</v>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I21" s="37" t="n">
-        <v>46297</v>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@tarheel; 36129 of 81683 (44.2%) as of 2026-10-08 17:11 UTC. empty_body=5194, http_403=28.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>University of California, Riverside</t>
-        </is>
-      </c>
-      <c r="B22" s="38" t="inlineStr">
-        <is>
-          <t>The Highlander</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>highlander</t>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>highlandernews.org</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F22" s="38" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="n">
-        <v>9791</v>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I22" s="37" t="n">
-        <v>46297</v>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>Finished 2026-10-04. 9791 of 10144 (96.5%); 550 empty_body, 1 http_520, 1 http_525. File: ~/Downloads/highlander.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t>University of Massachusetts, Amherst</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>The Massachusetts Daily Collegian</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>collegian</t>
-        </is>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>dailycollegian.com</t>
-        </is>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="n">
-        <v>24237</v>
-      </c>
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I23" s="37" t="n">
-        <v>46299</v>
-      </c>
-      <c r="J23" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@collegian; 24237 of 52185 (46.4%) as of 2026-10-08 17:11 UTC. empty_body=306, pre_2000=234.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t>University of Minnesota, Twin Cities</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>The Minnesota Daily</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>mndaily</t>
-        </is>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>mndaily.com</t>
-        </is>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>National Universities | Public Universities</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G24" s="0" t="n">
-        <v>21590</v>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I24" s="37" t="n">
-        <v>46299</v>
-      </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@mndaily; 21590 of 80516 (26.8%) as of 2026-10-08 17:11 UTC. pre_2000=14440 skipped.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
+          <t>University of North Carolina, Chapel Hill</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>The Daily Tar Heel</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>tarheel</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>dailytarheel.com</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>36129</v>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I25" s="37" t="n">
+        <v>46297</v>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@tarheel; 36129 of 81683 (44.2%) as of 2026-10-08 17:11 UTC. empty_body=5194, http_403=28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>University of California, Riverside</t>
+        </is>
+      </c>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>The Highlander</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>highlander</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>highlandernews.org</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F26" s="38" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>9791</v>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I26" s="37" t="n">
+        <v>46297</v>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t>Finished 2026-10-04. 9791 of 10144 (96.5%); 550 empty_body, 1 http_520, 1 http_525. File: ~/Downloads/highlander.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>University of Massachusetts, Amherst</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>The Massachusetts Daily Collegian</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>collegian</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>dailycollegian.com</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>24237</v>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I27" s="37" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@collegian; 24237 of 52185 (46.4%) as of 2026-10-08 17:11 UTC. empty_body=306, pre_2000=234.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>University of Minnesota, Twin Cities</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>The Minnesota Daily</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>mndaily</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>mndaily.com</t>
+        </is>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>National Universities | Public Universities</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>21590</v>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I28" s="37" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@mndaily; 21590 of 80516 (26.8%) as of 2026-10-08 17:11 UTC. pre_2000=14440 skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
           <t>University of Pittsburgh</t>
         </is>
       </c>
-      <c r="B25" s="0" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>The Pitt News</t>
         </is>
       </c>
-      <c r="C25" s="0" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>pitt</t>
         </is>
       </c>
-      <c r="D25" s="0" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>pittnews.com</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F25" s="0" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>queued</t>
         </is>
       </c>
-      <c r="H25" s="0" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I25" s="37" t="n">
+      <c r="I29" s="37" t="n">
         <v>46299</v>
       </c>
-      <c r="J25" s="0" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>Not cleared. VM 200-test HTTP 403 on /opinions/satire/; block cooldown. Probe of two news articles OK. Do not start full until a later 200-test passes.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>Clemson University</t>
         </is>
       </c>
-      <c r="B26" s="0" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>The Tiger</t>
         </is>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>tiger</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>thetigercu.com</t>
         </is>
       </c>
-      <c r="E26" s="0" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F26" s="0" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G30" s="0" t="n">
         <v>7337</v>
       </c>
-      <c r="H26" s="0" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I26" s="37" t="n">
+      <c r="I30" s="37" t="n">
         <v>46300</v>
       </c>
-      <c r="J26" s="0" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>Finished 2026-10-06. 7337 of 7455 (98.4%); empty_body=130. systemd inactive. File: ~/Downloads/tiger.csv</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="38" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>New Jersey Institute of Technology</t>
         </is>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>The Vector</t>
         </is>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>vector</t>
         </is>
       </c>
-      <c r="D27" s="0" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>njitvector.com</t>
         </is>
       </c>
-      <c r="E27" s="0" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>National Universities | Public Universities</t>
         </is>
       </c>
-      <c r="F27" s="38" t="inlineStr">
+      <c r="F31" s="38" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G31" s="0" t="n">
         <v>335</v>
       </c>
-      <c r="H27" s="0" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I27" s="37" t="n">
+      <c r="I31" s="37" t="n">
         <v>46300</v>
       </c>
-      <c r="J27" s="0" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>Finished 2026-10-05. 335 of 336 (99.7%); 1 empty_body. File: ~/Downloads/vector.csv</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="B28" s="32" t="n"/>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="32" t="n"/>
-      <c r="G28" s="32" t="n"/>
-      <c r="H28" s="32" t="n"/>
-      <c r="I28" s="32" t="n"/>
-      <c r="J28" s="32" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>Connecticut College</t>
-        </is>
-      </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>The College Voice</t>
-        </is>
-      </c>
-      <c r="C29" s="33" t="inlineStr">
-        <is>
-          <t>conncoll</t>
-        </is>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>thecollegevoice.org</t>
-        </is>
-      </c>
-      <c r="E29" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G29" s="30" t="n">
-        <v>4039</v>
-      </c>
-      <c r="H29" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I29" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J29" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>Denison University</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>The Denisonian</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>denison</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>denisonian.com</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G30" s="30" t="n">
-        <v>3671</v>
-      </c>
-      <c r="H30" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I30" s="35" t="n">
-        <v>46294</v>
-      </c>
-      <c r="J30" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>Franklin &amp; Marshall College</t>
-        </is>
-      </c>
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>The College Reporter</t>
-        </is>
-      </c>
-      <c r="C31" s="33" t="inlineStr">
-        <is>
-          <t>fandm</t>
-        </is>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>the-college-reporter.com</t>
-        </is>
-      </c>
-      <c r="E31" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G31" s="30" t="n">
-        <v>3449</v>
-      </c>
-      <c r="H31" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I31" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J31" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>Hillsdale College</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>The Collegian</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="inlineStr">
-        <is>
-          <t>hillsdale</t>
-        </is>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>hillsdalecollegian.com</t>
-        </is>
-      </c>
-      <c r="E32" s="33" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F32" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="n">
-        <v>15573</v>
-      </c>
-      <c r="H32" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I32" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J32" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
-        </is>
-      </c>
+      <c r="B32" s="32" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="32" t="n"/>
+      <c r="E32" s="32" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="32" t="n"/>
+      <c r="H32" s="32" t="n"/>
+      <c r="I32" s="32" t="n"/>
+      <c r="J32" s="32" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>Occidental College</t>
+          <t>Connecticut College</t>
         </is>
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>The Occidental</t>
+          <t>The College Voice</t>
         </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
-          <t>occidental</t>
+          <t>conncoll</t>
         </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
-          <t>theoccidentalnews.com</t>
+          <t>thecollegevoice.org</t>
         </is>
       </c>
       <c r="E33" s="33" t="inlineStr">
@@ -1942,7 +1934,7 @@
         </is>
       </c>
       <c r="G33" s="30" t="n">
-        <v>9892</v>
+        <v>4039</v>
       </c>
       <c r="H33" s="33" t="inlineStr">
         <is>
@@ -1954,29 +1946,29 @@
       </c>
       <c r="J33" s="34" t="inlineStr">
         <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Swarthmore College</t>
+          <t>Denison University</t>
         </is>
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>The Phoenix</t>
+          <t>The Denisonian</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>swarthmore</t>
+          <t>denison</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>swarthmorephoenix.com</t>
+          <t>denisonian.com</t>
         </is>
       </c>
       <c r="E34" s="33" t="inlineStr">
@@ -1990,7 +1982,7 @@
         </is>
       </c>
       <c r="G34" s="30" t="n">
-        <v>12798</v>
+        <v>3671</v>
       </c>
       <c r="H34" s="33" t="inlineStr">
         <is>
@@ -1998,33 +1990,33 @@
         </is>
       </c>
       <c r="I34" s="35" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="J34" s="34" t="inlineStr">
         <is>
-          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>Union College (NY)</t>
+          <t>Franklin &amp; Marshall College</t>
         </is>
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>Concordiensis</t>
+          <t>The College Reporter</t>
         </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>union</t>
+          <t>fandm</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
-          <t>concordiensis.com</t>
+          <t>the-college-reporter.com</t>
         </is>
       </c>
       <c r="E35" s="33" t="inlineStr">
@@ -2038,7 +2030,7 @@
         </is>
       </c>
       <c r="G35" s="30" t="n">
-        <v>1604</v>
+        <v>3449</v>
       </c>
       <c r="H35" s="33" t="inlineStr">
         <is>
@@ -2050,29 +2042,29 @@
       </c>
       <c r="J35" s="34" t="inlineStr">
         <is>
-          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>Wesleyan University</t>
+          <t>Hillsdale College</t>
         </is>
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>The Wesleyan Argus</t>
+          <t>The Collegian</t>
         </is>
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>wesleyan</t>
+          <t>hillsdale</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
         <is>
-          <t>wesleyanargus.com</t>
+          <t>hillsdalecollegian.com</t>
         </is>
       </c>
       <c r="E36" s="33" t="inlineStr">
@@ -2085,8 +2077,8 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G36" s="24" t="n">
-        <v>21881</v>
+      <c r="G36" s="30" t="n">
+        <v>15573</v>
       </c>
       <c r="H36" s="33" t="inlineStr">
         <is>
@@ -2094,534 +2086,534 @@
         </is>
       </c>
       <c r="I36" s="35" t="n">
-        <v>46294</v>
+        <v>46292</v>
       </c>
       <c r="J36" s="34" t="inlineStr">
         <is>
-          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
+          <t>Occidental College</t>
+        </is>
+      </c>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>The Occidental</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>occidental</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="inlineStr">
+        <is>
+          <t>theoccidentalnews.com</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G37" s="30" t="n">
+        <v>9892</v>
+      </c>
+      <c r="H37" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I37" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J37" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Swarthmore College</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>The Phoenix</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>swarthmore</t>
+        </is>
+      </c>
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>swarthmorephoenix.com</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="n">
+        <v>12798</v>
+      </c>
+      <c r="H38" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I38" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J38" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Union College (NY)</t>
+        </is>
+      </c>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>Concordiensis</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>union</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>concordiensis.com</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G39" s="30" t="n">
+        <v>1604</v>
+      </c>
+      <c r="H39" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J39" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Wesleyan University</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>The Wesleyan Argus</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>wesleyan</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>wesleyanargus.com</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="n">
+        <v>21881</v>
+      </c>
+      <c r="H40" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>46294</v>
+      </c>
+      <c r="J40" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
           <t>Claremont Colleges</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>The Student Life</t>
         </is>
       </c>
-      <c r="C37" s="33" t="inlineStr">
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>tsl</t>
         </is>
       </c>
-      <c r="D37" s="33" t="inlineStr">
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t>tsl.news</t>
         </is>
       </c>
-      <c r="E37" s="33" t="inlineStr">
+      <c r="E41" s="33" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F37" s="24" t="inlineStr">
+      <c r="F41" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G37" s="33" t="n">
+      <c r="G41" s="33" t="n">
         <v>11405</v>
       </c>
-      <c r="H37" s="33" t="inlineStr">
+      <c r="H41" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I37" s="35" t="n">
+      <c r="I41" s="35" t="n">
         <v>46295</v>
       </c>
-      <c r="J37" s="34" t="inlineStr">
+      <c r="J41" s="34" t="inlineStr">
         <is>
           <t>Finished 2026-10-04. 11405 of 11437 (99.7%); 16 empty_body, 15 http_403, 1 http_404. File: ~/Downloads/tsl.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="inlineStr">
-        <is>
-          <t>Carleton College</t>
-        </is>
-      </c>
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t>The Carletonian</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>carleton</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>thecarletonian.com</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G38" s="0" t="n">
-        <v>7805</v>
-      </c>
-      <c r="H38" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I38" s="37" t="n">
-        <v>46300</v>
-      </c>
-      <c r="J38" s="0" t="inlineStr">
-        <is>
-          <t>Finished 2026-10-06. 7805 of 7941 (98.3%); empty_body=135, http_404=1. systemd inactive. File: ~/Downloads/carleton.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="inlineStr">
-        <is>
-          <t>Macalester College</t>
-        </is>
-      </c>
-      <c r="B39" s="0" t="inlineStr">
-        <is>
-          <t>The Mac Weekly</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>macweekly</t>
-        </is>
-      </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>themacweekly.com</t>
-        </is>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G39" s="0" t="n">
-        <v>9036</v>
-      </c>
-      <c r="H39" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I39" s="37" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J39" s="0" t="inlineStr">
-        <is>
-          <t>Finished 2026-10-08. 9036 of 9420 (95.9%); empty_body=392, network_error=1. systemd inactive. File: ~/Downloads/macweekly.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="inlineStr">
-        <is>
-          <t>Grinnell College</t>
-        </is>
-      </c>
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t>Scarlet &amp; Black</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>sandb</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>thesandb.com</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G40" s="0" t="n">
-        <v>9054</v>
-      </c>
-      <c r="H40" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I40" s="37" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J40" s="0" t="inlineStr">
-        <is>
-          <t>Finished 2026-10-08. 9054 of 9228 (98.1%); empty_body=184. systemd inactive. File: ~/Downloads/sandb.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="inlineStr">
-        <is>
-          <t>Colgate University</t>
-        </is>
-      </c>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>The Colgate Maroon-News</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>colgate</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>thecolgatemaroonnews.com</t>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>Liberal Arts</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G41" s="0" t="n">
-        <v>7250</v>
-      </c>
-      <c r="H41" s="0" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I41" s="37" t="n">
-        <v>46302</v>
-      </c>
-      <c r="J41" s="0" t="inlineStr">
-        <is>
-          <t>newspaper-scraper@colgate; 7250 of 15489 (46.8%) as of 2026-10-08 17:11 UTC. http_500=1.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
+          <t>Carleton College</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>The Carletonian</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>carleton</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>thecarletonian.com</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>7805</v>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I42" s="37" t="n">
+        <v>46300</v>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>Finished 2026-10-06. 7805 of 7941 (98.3%); empty_body=135, http_404=1. systemd inactive. File: ~/Downloads/carleton.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>Macalester College</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>The Mac Weekly</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>macweekly</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>themacweekly.com</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>9036</v>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I43" s="37" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>Finished 2026-10-08. 9036 of 9420 (95.9%); empty_body=392, network_error=1. systemd inactive. File: ~/Downloads/macweekly.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>Grinnell College</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>Scarlet &amp; Black</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>sandb</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>thesandb.com</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>9054</v>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I44" s="37" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>Finished 2026-10-08. 9054 of 9228 (98.1%); empty_body=184. systemd inactive. File: ~/Downloads/sandb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>Colgate University</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>The Colgate Maroon-News</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>colgate</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>thecolgatemaroonnews.com</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>7250</v>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I45" s="37" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@colgate; 7250 of 15489 (46.8%) as of 2026-10-08 17:11 UTC. http_500=1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
           <t>Bucknell University</t>
         </is>
       </c>
-      <c r="B42" s="0" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>The Bucknellian</t>
         </is>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>bucknellian</t>
         </is>
       </c>
-      <c r="D42" s="0" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>bucknellian.net</t>
         </is>
       </c>
-      <c r="E42" s="0" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F42" s="0" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G46" s="0" t="n">
         <v>7300</v>
       </c>
-      <c r="H42" s="0" t="inlineStr">
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I42" s="37" t="n">
+      <c r="I46" s="37" t="n">
         <v>46302</v>
       </c>
-      <c r="J42" s="0" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>newspaper-scraper@bucknellian; 7300 of 11583 (63.0%) as of 2026-10-08 17:11 UTC. empty_body=11, http_404=2.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="32" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="32" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="32" t="n"/>
-      <c r="D43" s="32" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="32" t="n"/>
-      <c r="H43" s="32" t="n"/>
-      <c r="I43" s="32" t="n"/>
-      <c r="J43" s="32" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>Biola University</t>
-        </is>
-      </c>
-      <c r="B44" s="33" t="inlineStr">
-        <is>
-          <t>The Chimes</t>
-        </is>
-      </c>
-      <c r="C44" s="33" t="inlineStr">
-        <is>
-          <t>biola</t>
-        </is>
-      </c>
-      <c r="D44" s="33" t="inlineStr">
-        <is>
-          <t>chimesnewspaper.com</t>
-        </is>
-      </c>
-      <c r="E44" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G44" s="30" t="n">
-        <v>11331</v>
-      </c>
-      <c r="H44" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I44" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J44" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>Lipscomb University</t>
-        </is>
-      </c>
-      <c r="B45" s="33" t="inlineStr">
-        <is>
-          <t>Lipscomb Media</t>
-        </is>
-      </c>
-      <c r="C45" s="33" t="inlineStr">
-        <is>
-          <t>lipscomb</t>
-        </is>
-      </c>
-      <c r="D45" s="33" t="inlineStr">
-        <is>
-          <t>lipscombmedia.com</t>
-        </is>
-      </c>
-      <c r="E45" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F45" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G45" s="30" t="n">
-        <v>682</v>
-      </c>
-      <c r="H45" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I45" s="35" t="n">
-        <v>46292</v>
-      </c>
-      <c r="J45" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>Point Loma Nazarene University</t>
-        </is>
-      </c>
-      <c r="B46" s="33" t="inlineStr">
-        <is>
-          <t>Loma Beat</t>
-        </is>
-      </c>
-      <c r="C46" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat</t>
-        </is>
-      </c>
-      <c r="D46" s="33" t="inlineStr">
-        <is>
-          <t>lomabeat.com</t>
-        </is>
-      </c>
-      <c r="E46" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges</t>
-        </is>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G46" s="30" t="n">
-        <v>3950</v>
-      </c>
-      <c r="H46" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I46" s="35" t="n">
-        <v>46293</v>
-      </c>
-      <c r="J46" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>Southern Methodist University</t>
-        </is>
-      </c>
-      <c r="B47" s="33" t="inlineStr">
-        <is>
-          <t>The Daily Campus</t>
-        </is>
-      </c>
-      <c r="C47" s="33" t="inlineStr">
-        <is>
-          <t>smu</t>
-        </is>
-      </c>
-      <c r="D47" s="33" t="inlineStr">
-        <is>
-          <t>smudailycampus.com</t>
-        </is>
-      </c>
-      <c r="E47" s="33" t="inlineStr">
-        <is>
-          <t>Christian Colleges | National Universities</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="G47" s="30" t="n">
-        <v>26208</v>
-      </c>
-      <c r="H47" s="33" t="inlineStr">
-        <is>
-          <t>AWS VM</t>
-        </is>
-      </c>
-      <c r="I47" s="35" t="n">
-        <v>46291</v>
-      </c>
-      <c r="J47" s="34" t="inlineStr">
-        <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
-        </is>
-      </c>
+      <c r="B47" s="32" t="n"/>
+      <c r="C47" s="32" t="n"/>
+      <c r="D47" s="32" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="32" t="n"/>
+      <c r="H47" s="32" t="n"/>
+      <c r="I47" s="32" t="n"/>
+      <c r="J47" s="32" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>St. Olaf College</t>
+          <t>Biola University</t>
         </is>
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>Manitou Messenger</t>
+          <t>The Chimes</t>
         </is>
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>stolaf</t>
+          <t>biola</t>
         </is>
       </c>
       <c r="D48" s="33" t="inlineStr">
         <is>
-          <t>olafmessenger.com</t>
+          <t>chimesnewspaper.com</t>
         </is>
       </c>
       <c r="E48" s="33" t="inlineStr">
         <is>
-          <t>Christian Colleges | Liberal Arts</t>
+          <t>Christian Colleges</t>
         </is>
       </c>
       <c r="F48" s="24" t="inlineStr">
@@ -2630,7 +2622,7 @@
         </is>
       </c>
       <c r="G48" s="30" t="n">
-        <v>5048</v>
+        <v>11331</v>
       </c>
       <c r="H48" s="33" t="inlineStr">
         <is>
@@ -2638,57 +2630,249 @@
         </is>
       </c>
       <c r="I48" s="35" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="J48" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="24" t="inlineStr">
         <is>
+          <t>Lipscomb University</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>Lipscomb Media</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>lipscomb</t>
+        </is>
+      </c>
+      <c r="D49" s="33" t="inlineStr">
+        <is>
+          <t>lipscombmedia.com</t>
+        </is>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G49" s="30" t="n">
+        <v>682</v>
+      </c>
+      <c r="H49" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I49" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J49" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>Point Loma Nazarene University</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>Loma Beat</t>
+        </is>
+      </c>
+      <c r="C50" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat</t>
+        </is>
+      </c>
+      <c r="D50" s="33" t="inlineStr">
+        <is>
+          <t>lomabeat.com</t>
+        </is>
+      </c>
+      <c r="E50" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G50" s="30" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H50" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I50" s="35" t="n">
+        <v>46293</v>
+      </c>
+      <c r="J50" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>The Daily Campus</t>
+        </is>
+      </c>
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>smu</t>
+        </is>
+      </c>
+      <c r="D51" s="33" t="inlineStr">
+        <is>
+          <t>smudailycampus.com</t>
+        </is>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | National Universities</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G51" s="30" t="n">
+        <v>26208</v>
+      </c>
+      <c r="H51" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I51" s="35" t="n">
+        <v>46291</v>
+      </c>
+      <c r="J51" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>St. Olaf College</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>Manitou Messenger</t>
+        </is>
+      </c>
+      <c r="C52" s="33" t="inlineStr">
+        <is>
+          <t>stolaf</t>
+        </is>
+      </c>
+      <c r="D52" s="33" t="inlineStr">
+        <is>
+          <t>olafmessenger.com</t>
+        </is>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
+        <is>
+          <t>Christian Colleges | Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="n">
+        <v>5048</v>
+      </c>
+      <c r="H52" s="33" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I52" s="35" t="n">
+        <v>46292</v>
+      </c>
+      <c r="J52" s="34" t="inlineStr">
+        <is>
+          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
           <t>Texas Christian University</t>
         </is>
       </c>
-      <c r="B49" s="33" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>TCU 360</t>
         </is>
       </c>
-      <c r="C49" s="33" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>tcu</t>
         </is>
       </c>
-      <c r="D49" s="33" t="inlineStr">
+      <c r="D53" s="33" t="inlineStr">
         <is>
           <t>tcu360.com</t>
         </is>
       </c>
-      <c r="E49" s="33" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>Christian Colleges | National Universities</t>
         </is>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F53" s="24" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="G49" s="30" t="n">
+      <c r="G53" s="30" t="n">
         <v>25690</v>
       </c>
-      <c r="H49" s="33" t="inlineStr">
+      <c r="H53" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I49" s="35" t="n">
+      <c r="I53" s="35" t="n">
         <v>46291</v>
       </c>
-      <c r="J49" s="34" t="inlineStr">
+      <c r="J53" s="34" t="inlineStr">
         <is>
           <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
         </is>
@@ -5516,7 +5700,7 @@
           <t>#50</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>https://bachelor.wabash.edu/</t>
         </is>
@@ -5533,7 +5717,7 @@
           <t>#50</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>https://wheatonwire.com/</t>
         </is>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -180,6 +180,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -579,11 +582,11 @@
         </is>
       </c>
       <c r="I3" s="35" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="J3" s="34" t="inlineStr">
         <is>
-          <t>Finished. 2137 articles of 2140 URLs (99.9%); 5 empty_body. systemd inactive. File: repo output/rit.csv</t>
+          <t>Finished as of 2026-10-13. 2137 articles. systemd inactive. File: ~/Downloads/rit.csv</t>
         </is>
       </c>
     </row>
@@ -627,11 +630,11 @@
         </is>
       </c>
       <c r="I4" s="35" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="J4" s="34" t="inlineStr">
         <is>
-          <t>Finished. 6899 articles of 6992 URLs (98.7%); 67 empty_body, 26 pre_2000. systemd inactive. File: ~/Downloads/ucsc.csv</t>
+          <t>Finished as of 2026-10-13. 6899 articles. systemd inactive. File: ~/Downloads/ucsc.csv</t>
         </is>
       </c>
     </row>
@@ -675,11 +678,11 @@
         </is>
       </c>
       <c r="I5" s="35" t="n">
-        <v>46291</v>
+        <v>46308</v>
       </c>
       <c r="J5" s="34" t="inlineStr">
         <is>
-          <t>Finished. 22117 articles of 22493 URLs (98.3%); 371 empty_body, 2 http_301, 3 http_404. systemd inactive. File: repo output/chicago.csv</t>
+          <t>Finished as of 2026-10-13. 22117 articles. systemd inactive. File: ~/Downloads/chicago.csv</t>
         </is>
       </c>
     </row>
@@ -723,11 +726,11 @@
         </is>
       </c>
       <c r="I6" s="35" t="n">
-        <v>46294</v>
+        <v>46308</v>
       </c>
       <c r="J6" s="34" t="inlineStr">
         <is>
-          <t>Finished. 4175 articles of 4678 URLs (89.2%); 41 empty_body, 464 pre_2000. systemd inactive. File: ~/Downloads/yu.csv</t>
+          <t>Finished as of 2026-10-13. 4175 articles. systemd inactive. File: ~/Downloads/yu.csv</t>
         </is>
       </c>
     </row>
@@ -762,7 +765,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="39" t="n">
         <v>69041</v>
       </c>
       <c r="H7" s="33" t="inlineStr">
@@ -771,11 +774,11 @@
         </is>
       </c>
       <c r="I7" s="35" t="n">
-        <v>46290</v>
+        <v>46308</v>
       </c>
       <c r="J7" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-06. 69041 articles of 70720 URLs (97.6%); empty_body=3558, http_301=11, http_403=32, network_error=1083, pre_2000=46. systemd inactive. File: ~/Downloads/northwestern.csv</t>
+          <t>Finished as of 2026-10-13. 69041 articles. systemd inactive. File: ~/Downloads/northwestern.csv</t>
         </is>
       </c>
     </row>
@@ -810,8 +813,8 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G8" s="33" t="n">
-        <v>25622</v>
+      <c r="G8" s="39" t="n">
+        <v>25632</v>
       </c>
       <c r="H8" s="33" t="inlineStr">
         <is>
@@ -819,11 +822,11 @@
         </is>
       </c>
       <c r="I8" s="35" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="J8" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-02. 25622 articles of 25641 URLs (99.9%); 8 empty_body, 2 http_403, 9 http_500, 5 network_error. systemd inactive. File: ~/Downloads/miami.csv</t>
+          <t>Finished as of 2026-10-13. 25632 articles. systemd inactive. File: ~/Downloads/miami.csv</t>
         </is>
       </c>
     </row>
@@ -858,7 +861,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G9" s="33" t="n">
+      <c r="G9" s="39" t="n">
         <v>31894</v>
       </c>
       <c r="H9" s="33" t="inlineStr">
@@ -867,11 +870,11 @@
         </is>
       </c>
       <c r="I9" s="35" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="J9" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-01. 31894 articles of 32243 URLs (98.9%); 501 empty_body, 2 network_error, 9 pre_2000. systemd inactive. File: ~/Downloads/usf.csv</t>
+          <t>Finished as of 2026-10-13. 31894 articles. systemd inactive. File: ~/Downloads/usf.csv</t>
         </is>
       </c>
     </row>
@@ -952,7 +955,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G11" s="33" t="n">
+      <c r="G11" s="39" t="n">
         <v>22155</v>
       </c>
       <c r="H11" s="33" t="inlineStr">
@@ -960,12 +963,12 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I11" s="36" t="n">
-        <v>46296</v>
+      <c r="I11" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J11" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-05. News-section listings only, 22155 articles; 217 empty_body, 3 pre_2000. Other Chronicle sections later. File: ~/Downloads/duke.csv</t>
+          <t>Finished as of 2026-10-13. 22155 articles. systemd inactive. File: ~/Downloads/duke.csv</t>
         </is>
       </c>
     </row>
@@ -997,21 +1000,23 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G12" s="33" t="n"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>30994</v>
+      </c>
       <c r="H12" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I12" s="36" t="n">
-        <v>46303</v>
+      <c r="I12" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J12" s="34" t="inlineStr">
         <is>
-          <t>Wave 15 ready buffer. Cloudflare SNO ~60k URLs. Probe + 200-test next.</t>
+          <t>newspaper-scraper@hatchet; 30994 articles as of 2026-10-13. systemd active on AWS VM.</t>
         </is>
       </c>
     </row>
@@ -1043,21 +1048,23 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G13" s="33" t="n"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>30550</v>
+      </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I13" s="36" t="n">
-        <v>46303</v>
+      <c r="I13" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J13" s="34" t="inlineStr">
         <is>
-          <t>Wave 15 ready buffer. Cloudflare WP Yoast ~39k URLs. Probe + 200-test next.</t>
+          <t>newspaper-scraper@stanford; 30550 articles as of 2026-10-13. systemd active on AWS VM.</t>
         </is>
       </c>
     </row>
@@ -1089,21 +1096,23 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G14" s="33" t="n"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>30250</v>
+      </c>
       <c r="H14" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I14" s="36" t="n">
-        <v>46303</v>
+      <c r="I14" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>Wave 15 ready buffer. Cloudflare SNO ~32k URLs. Probe + 200-test next.</t>
+          <t>newspaper-scraper@marquette; 30250 articles as of 2026-10-13. systemd active on AWS VM.</t>
         </is>
       </c>
     </row>
@@ -1135,21 +1144,23 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="n"/>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>21935</v>
+      </c>
       <c r="H15" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I15" s="36" t="n">
-        <v>46303</v>
+      <c r="I15" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J15" s="34" t="inlineStr">
         <is>
-          <t>Wave 15 ready buffer. Cloudflare SNO Yoast ~22k URLs. Probe + 200-test next.</t>
+          <t>Finished as of 2026-10-13. 21935 articles. systemd inactive. File: ~/Downloads/nyu.csv</t>
         </is>
       </c>
     </row>
@@ -1209,11 +1220,11 @@
         </is>
       </c>
       <c r="I17" s="35" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="J17" s="34" t="inlineStr">
         <is>
-          <t>Finished. 17411 articles of 17447 URLs (99.8%); 165 empty_body. systemd inactive. File: ~/Downloads/uci.csv</t>
+          <t>Finished as of 2026-10-13. 17411 articles. systemd inactive. File: ~/Downloads/uci.csv</t>
         </is>
       </c>
     </row>
@@ -1245,11 +1256,11 @@
       </c>
       <c r="F18" s="33" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G18" s="33" t="n">
-        <v>99943</v>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G18" s="39" t="n">
+        <v>118949</v>
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
@@ -1257,11 +1268,11 @@
         </is>
       </c>
       <c r="I18" s="35" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="J18" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@michigan; 99943 of 119764 (83.4%) as of 2026-10-08 17:11 UTC. http_429=21 (was 16 on Oct 7). http_301=1821.</t>
+          <t>Finished as of 2026-10-13. 118949 articles. systemd inactive. File: ~/Downloads/michigan.csv</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1307,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G19" s="33" t="n">
+      <c r="G19" s="39" t="n">
         <v>21079</v>
       </c>
       <c r="H19" s="33" t="inlineStr">
@@ -1304,12 +1315,12 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I19" s="36" t="n">
-        <v>46296</v>
+      <c r="I19" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J19" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-05 before later downloads. 21079 articles of 22605 URLs (93.2%); 1660 empty_body, 2 http_500. systemd inactive. File: ~/Downloads/ucsd.csv</t>
+          <t>Finished as of 2026-10-13. 21079 articles. systemd inactive. File: ~/Downloads/ucsd.csv</t>
         </is>
       </c>
     </row>
@@ -1341,23 +1352,23 @@
       </c>
       <c r="F20" s="33" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G20" s="33" t="n">
-        <v>45147</v>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G20" s="39" t="n">
+        <v>50898</v>
       </c>
       <c r="H20" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I20" s="36" t="n">
-        <v>46296</v>
+      <c r="I20" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J20" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@texan; 45147 of 51636 (87.4%) as of 2026-10-08 17:11 UTC. empty_body=407, http_403=7.</t>
+          <t>Finished as of 2026-10-13. 50898 articles. systemd inactive. File: ~/Downloads/texan.csv</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1403,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G21" s="33" t="n">
+      <c r="G21" s="39" t="n">
         <v>37215</v>
       </c>
       <c r="H21" s="33" t="inlineStr">
@@ -1400,12 +1411,12 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I21" s="36" t="n">
-        <v>46296</v>
+      <c r="I21" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J21" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-07. 37215 of 40465 (92.0%); empty_body=4202, http_404=1. systemd inactive. File: ~/Downloads/nexus.csv</t>
+          <t>Finished as of 2026-10-13. 37215 articles. systemd inactive. File: ~/Downloads/nexus.csv</t>
         </is>
       </c>
     </row>
@@ -1440,20 +1451,20 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G22" s="33" t="n">
-        <v>44450</v>
+      <c r="G22" s="39" t="n">
+        <v>75850</v>
       </c>
       <c r="H22" s="33" t="inlineStr">
         <is>
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I22" s="36" t="n">
-        <v>46296</v>
+      <c r="I22" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J22" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@illini; 44450 of 100022 (44.4%) as of 2026-10-08 17:11 UTC.</t>
+          <t>newspaper-scraper@illini; 75850 articles as of 2026-10-13. systemd active on AWS VM.</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1499,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G23" s="33" t="n">
+      <c r="G23" s="39" t="n">
         <v>40280</v>
       </c>
       <c r="H23" s="33" t="inlineStr">
@@ -1496,12 +1507,12 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I23" s="36" t="n">
-        <v>46296</v>
+      <c r="I23" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J23" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-07. 40280 of 41051 (98.1%); empty_body=1017, http_521=1. systemd inactive. File: ~/Downloads/technician.csv</t>
+          <t>Finished as of 2026-10-13. 40280 articles. systemd inactive. File: ~/Downloads/technician.csv</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1547,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G24" s="33" t="n">
+      <c r="G24" s="39" t="n">
         <v>13354</v>
       </c>
       <c r="H24" s="33" t="inlineStr">
@@ -1544,12 +1555,12 @@
           <t>AWS VM</t>
         </is>
       </c>
-      <c r="I24" s="36" t="n">
-        <v>46296</v>
+      <c r="I24" s="35" t="n">
+        <v>46308</v>
       </c>
       <c r="J24" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-04. 13354 of 13650 (97.8%); 517 empty_body, 32 pre_2000. File: ~/Downloads/statesman.csv</t>
+          <t>Finished as of 2026-10-13. 13354 articles. systemd inactive. File: ~/Downloads/statesman.csv</t>
         </is>
       </c>
     </row>
@@ -1584,8 +1595,8 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G25" s="0" t="n">
-        <v>36129</v>
+      <c r="G25" s="22" t="n">
+        <v>56979</v>
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
@@ -1593,11 +1604,11 @@
         </is>
       </c>
       <c r="I25" s="37" t="n">
-        <v>46297</v>
+        <v>46308</v>
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tarheel; 36129 of 81683 (44.2%) as of 2026-10-08 17:11 UTC. empty_body=5194, http_403=28.</t>
+          <t>newspaper-scraper@tarheel; 56979 articles as of 2026-10-13. systemd active on AWS VM.</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1643,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="22" t="n">
         <v>9791</v>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1641,11 +1652,11 @@
         </is>
       </c>
       <c r="I26" s="37" t="n">
-        <v>46297</v>
+        <v>46308</v>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>Finished 2026-10-04. 9791 of 10144 (96.5%); 550 empty_body, 1 http_520, 1 http_525. File: ~/Downloads/highlander.csv</t>
+          <t>Finished as of 2026-10-13. 9791 articles. systemd inactive. File: ~/Downloads/highlander.csv</t>
         </is>
       </c>
     </row>
@@ -1677,11 +1688,11 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G27" s="0" t="n">
-        <v>24237</v>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>51122</v>
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
@@ -1689,11 +1700,11 @@
         </is>
       </c>
       <c r="I27" s="37" t="n">
-        <v>46299</v>
+        <v>46308</v>
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@collegian; 24237 of 52185 (46.4%) as of 2026-10-08 17:11 UTC. empty_body=306, pre_2000=234.</t>
+          <t>Finished as of 2026-10-13. 51122 articles. systemd inactive. File: ~/Downloads/collegian.csv</t>
         </is>
       </c>
     </row>
@@ -1728,8 +1739,8 @@
           <t>running</t>
         </is>
       </c>
-      <c r="G28" s="0" t="n">
-        <v>21590</v>
+      <c r="G28" s="22" t="n">
+        <v>53190</v>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
@@ -1737,11 +1748,11 @@
         </is>
       </c>
       <c r="I28" s="37" t="n">
-        <v>46299</v>
+        <v>46308</v>
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@mndaily; 21590 of 80516 (26.8%) as of 2026-10-08 17:11 UTC. pre_2000=14440 skipped.</t>
+          <t>newspaper-scraper@mndaily; 53190 articles as of 2026-10-13. systemd active on AWS VM.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1832,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G30" s="0" t="n">
+      <c r="G30" s="22" t="n">
         <v>7337</v>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -1830,11 +1841,11 @@
         </is>
       </c>
       <c r="I30" s="37" t="n">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>Finished 2026-10-06. 7337 of 7455 (98.4%); empty_body=130. systemd inactive. File: ~/Downloads/tiger.csv</t>
+          <t>Finished as of 2026-10-13. 7337 articles. systemd inactive. File: ~/Downloads/tiger.csv</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1880,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G31" s="0" t="n">
+      <c r="G31" s="22" t="n">
         <v>335</v>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -1878,11 +1889,11 @@
         </is>
       </c>
       <c r="I31" s="37" t="n">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>Finished 2026-10-05. 335 of 336 (99.7%); 1 empty_body. File: ~/Downloads/vector.csv</t>
+          <t>Finished as of 2026-10-13. 335 articles. systemd inactive. File: ~/Downloads/vector.csv</t>
         </is>
       </c>
     </row>
@@ -1942,11 +1953,11 @@
         </is>
       </c>
       <c r="I33" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J33" s="34" t="inlineStr">
         <is>
-          <t>Finished. 4039 articles of 4320 URLs (93.5%); 288 empty_body. systemd inactive. File: ~/Downloads/conncoll.csv</t>
+          <t>Finished as of 2026-10-13. 4039 articles. systemd inactive. File: ~/Downloads/conncoll.csv</t>
         </is>
       </c>
     </row>
@@ -1990,11 +2001,11 @@
         </is>
       </c>
       <c r="I34" s="35" t="n">
-        <v>46294</v>
+        <v>46308</v>
       </c>
       <c r="J34" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3671 articles of 3696 URLs (99.3%); 29 empty_body. systemd inactive. File: ~/Downloads/denison.csv</t>
+          <t>Finished as of 2026-10-13. 3671 articles. systemd inactive. File: ~/Downloads/denison.csv</t>
         </is>
       </c>
     </row>
@@ -2038,11 +2049,11 @@
         </is>
       </c>
       <c r="I35" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J35" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3449 articles of 3583 URLs (96.3%); 135 empty_body, 3 network_error. systemd inactive. File: ~/Downloads/fandm.csv</t>
+          <t>Finished as of 2026-10-13. 3449 articles. systemd inactive. File: ~/Downloads/fandm.csv</t>
         </is>
       </c>
     </row>
@@ -2086,11 +2097,11 @@
         </is>
       </c>
       <c r="I36" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J36" s="34" t="inlineStr">
         <is>
-          <t>Finished. 15573 articles of 15690 URLs (99.3%); 124 empty_body. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
+          <t>Finished as of 2026-10-13. 15573 articles. systemd inactive. File: ~/Downloads/hillsdale.csv</t>
         </is>
       </c>
     </row>
@@ -2134,11 +2145,11 @@
         </is>
       </c>
       <c r="I37" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J37" s="34" t="inlineStr">
         <is>
-          <t>Finished. 9892 articles of 10055 URLs (98.4%); 176 empty_body, 1 http_500, 3 network_error. systemd inactive. File: ~/Downloads/occidental.csv</t>
+          <t>Finished as of 2026-10-13. 9892 articles. systemd inactive. File: ~/Downloads/occidental.csv</t>
         </is>
       </c>
     </row>
@@ -2182,11 +2193,11 @@
         </is>
       </c>
       <c r="I38" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J38" s="34" t="inlineStr">
         <is>
-          <t>Finished. 12798 articles of 13251 URLs (96.6%); 75 empty_body, 578 pre_2000. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
+          <t>Finished as of 2026-10-13. 12798 articles. systemd inactive. File: ~/Downloads/swarthmore.csv</t>
         </is>
       </c>
     </row>
@@ -2230,11 +2241,11 @@
         </is>
       </c>
       <c r="I39" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J39" s="34" t="inlineStr">
         <is>
-          <t>Finished. 1604 articles of 1626 URLs (98.6%); 44 empty_body. systemd inactive. File: ~/Downloads/union.csv</t>
+          <t>Finished as of 2026-10-13. 1604 articles. systemd inactive. File: ~/Downloads/union.csv</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2280,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G40" s="24" t="n">
+      <c r="G40" s="30" t="n">
         <v>21881</v>
       </c>
       <c r="H40" s="33" t="inlineStr">
@@ -2278,11 +2289,11 @@
         </is>
       </c>
       <c r="I40" s="35" t="n">
-        <v>46294</v>
+        <v>46308</v>
       </c>
       <c r="J40" s="34" t="inlineStr">
         <is>
-          <t>Finished. 21881 articles of 21917 URLs (99.8%); 43 empty_body. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
+          <t>Finished as of 2026-10-13. 21881 articles. systemd inactive. File: ~/Downloads/wesleyan.csv</t>
         </is>
       </c>
     </row>
@@ -2317,8 +2328,8 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G41" s="33" t="n">
-        <v>11405</v>
+      <c r="G41" s="39" t="n">
+        <v>11420</v>
       </c>
       <c r="H41" s="33" t="inlineStr">
         <is>
@@ -2326,11 +2337,11 @@
         </is>
       </c>
       <c r="I41" s="35" t="n">
-        <v>46295</v>
+        <v>46308</v>
       </c>
       <c r="J41" s="34" t="inlineStr">
         <is>
-          <t>Finished 2026-10-04. 11405 of 11437 (99.7%); 16 empty_body, 15 http_403, 1 http_404. File: ~/Downloads/tsl.csv</t>
+          <t>Finished as of 2026-10-13. 11420 articles. systemd inactive. File: ~/Downloads/tsl.csv</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2376,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G42" s="0" t="n">
+      <c r="G42" s="22" t="n">
         <v>7805</v>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2374,11 +2385,11 @@
         </is>
       </c>
       <c r="I42" s="37" t="n">
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>Finished 2026-10-06. 7805 of 7941 (98.3%); empty_body=135, http_404=1. systemd inactive. File: ~/Downloads/carleton.csv</t>
+          <t>Finished as of 2026-10-13. 7805 articles. systemd inactive. File: ~/Downloads/carleton.csv</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2424,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G43" s="0" t="n">
+      <c r="G43" s="22" t="n">
         <v>9036</v>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2422,11 +2433,11 @@
         </is>
       </c>
       <c r="I43" s="37" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>Finished 2026-10-08. 9036 of 9420 (95.9%); empty_body=392, network_error=1. systemd inactive. File: ~/Downloads/macweekly.csv</t>
+          <t>Finished as of 2026-10-13. 9036 articles. systemd inactive. File: ~/Downloads/macweekly.csv</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2472,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="G44" s="0" t="n">
+      <c r="G44" s="22" t="n">
         <v>9054</v>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2470,11 +2481,11 @@
         </is>
       </c>
       <c r="I44" s="37" t="n">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>Finished 2026-10-08. 9054 of 9228 (98.1%); empty_body=184. systemd inactive. File: ~/Downloads/sandb.csv</t>
+          <t>Finished as of 2026-10-13. 9054 articles. systemd inactive. File: ~/Downloads/sandb.csv</t>
         </is>
       </c>
     </row>
@@ -2506,11 +2517,11 @@
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G45" s="0" t="n">
-        <v>7250</v>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="n">
+        <v>15466</v>
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
@@ -2518,11 +2529,11 @@
         </is>
       </c>
       <c r="I45" s="37" t="n">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@colgate; 7250 of 15489 (46.8%) as of 2026-10-08 17:11 UTC. http_500=1.</t>
+          <t>Finished as of 2026-10-13. 15466 articles. systemd inactive. File: ~/Downloads/colgate.csv</t>
         </is>
       </c>
     </row>
@@ -2554,11 +2565,11 @@
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="G46" s="0" t="n">
-        <v>7300</v>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>11555</v>
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
@@ -2566,11 +2577,11 @@
         </is>
       </c>
       <c r="I46" s="37" t="n">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@bucknellian; 7300 of 11583 (63.0%) as of 2026-10-08 17:11 UTC. empty_body=11, http_404=2.</t>
+          <t>Finished as of 2026-10-13. 11555 articles. systemd inactive. File: ~/Downloads/bucknellian.csv</t>
         </is>
       </c>
     </row>
@@ -2630,11 +2641,11 @@
         </is>
       </c>
       <c r="I48" s="35" t="n">
-        <v>46291</v>
+        <v>46308</v>
       </c>
       <c r="J48" s="34" t="inlineStr">
         <is>
-          <t>Finished. 11331 articles of 11390 URLs (99.5%); 569 empty_body, 1 http_404. systemd inactive. File: ~/Downloads/biola.csv</t>
+          <t>Finished as of 2026-10-13. 11331 articles. systemd inactive. File: ~/Downloads/biola.csv</t>
         </is>
       </c>
     </row>
@@ -2678,11 +2689,11 @@
         </is>
       </c>
       <c r="I49" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J49" s="34" t="inlineStr">
         <is>
-          <t>Finished. 682 articles of 698 URLs (97.7%); 2 empty_body, 28 pre_2000. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
+          <t>Finished as of 2026-10-13. 682 articles. systemd inactive. File: ~/Downloads/lipscomb.csv</t>
         </is>
       </c>
     </row>
@@ -2726,11 +2737,11 @@
         </is>
       </c>
       <c r="I50" s="35" t="n">
-        <v>46293</v>
+        <v>46308</v>
       </c>
       <c r="J50" s="34" t="inlineStr">
         <is>
-          <t>Finished. 3950 articles of 4044 URLs (97.7%); 98 empty_body. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
+          <t>Finished as of 2026-10-13. 3950 articles. systemd inactive. File: ~/Downloads/lomabeat.csv</t>
         </is>
       </c>
     </row>
@@ -2774,11 +2785,11 @@
         </is>
       </c>
       <c r="I51" s="35" t="n">
-        <v>46291</v>
+        <v>46308</v>
       </c>
       <c r="J51" s="34" t="inlineStr">
         <is>
-          <t>Finished. 26208 articles of 26572 URLs (98.6%); 649 empty_body, 1 network_error. systemd inactive. File: ~/Downloads/smu.csv</t>
+          <t>Finished as of 2026-10-13. 26208 articles. systemd inactive. File: ~/Downloads/smu.csv</t>
         </is>
       </c>
     </row>
@@ -2822,11 +2833,11 @@
         </is>
       </c>
       <c r="I52" s="35" t="n">
-        <v>46292</v>
+        <v>46308</v>
       </c>
       <c r="J52" s="34" t="inlineStr">
         <is>
-          <t>Finished. 5048 articles of 5208 URLs (96.9%); 320 empty_body. systemd inactive. File: ~/Downloads/stolaf.csv</t>
+          <t>Finished as of 2026-10-13. 5048 articles. systemd inactive. File: ~/Downloads/stolaf.csv | Blank Liberal Arts ranking row; covered under Christian Colleges / stolaf (already finished).</t>
         </is>
       </c>
     </row>
@@ -2870,11 +2881,1500 @@
         </is>
       </c>
       <c r="I53" s="35" t="n">
-        <v>46291</v>
+        <v>46308</v>
       </c>
       <c r="J53" s="34" t="inlineStr">
         <is>
-          <t>Finished. 25690 articles of 26172 URLs (98.2%); 862 empty_body, 6 http_404, 6 pre_2000. systemd inactive. File: ~/Downloads/tcu.csv</t>
+          <t>Finished as of 2026-10-13. 25690 articles. systemd inactive. File: ~/Downloads/tcu.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>Wabash College</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>The Bachelor</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>bachelor.wabash.edu</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>692</v>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I54" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 692 articles. systemd inactive. File: ~/Downloads/bachelor.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>Bates College</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>The Bates Student</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>bates</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>thebatesstudent.com</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="n">
+        <v>2297</v>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I55" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J55" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 2297 articles. systemd inactive. File: ~/Downloads/bates.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>Baylor University</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>The Baylor Lariat</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>baylor</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>baylorlariat.com</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="n">
+        <v>4796</v>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I56" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J56" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@baylor; 4796 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>Bowdoin College</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>The Bowdoin Orient</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>bowdoin</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>bowdoinorient.com</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="n">
+        <v>5981</v>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I57" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 5981 articles. systemd inactive. File: ~/Downloads/bowdoin.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>University of Rochester</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>Campus Times</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>campustimes</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>campustimes.org</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G58" s="21" t="n">
+        <v>7948</v>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I58" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@campustimes; 7948 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>Case Western Reserve University</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>The Observer</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>observer.case.edu</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="n">
+        <v>10125</v>
+      </c>
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I59" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 10125 articles. systemd inactive. File: ~/Downloads/case.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>Davidson College</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>The Davidsonian</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>davidson</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>thedavidsonian.news</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G60" s="21" t="n">
+        <v>518</v>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I60" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 518 articles. systemd inactive. File: ~/Downloads/davidson.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>Dickinson College</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>The Dickinsonian</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>dickinson</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="inlineStr">
+        <is>
+          <t>thedickinsonian.com</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="n">
+        <v>4871</v>
+      </c>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I61" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 4871 articles. systemd inactive. File: ~/Downloads/dickinson.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>Fordham University</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>The Fordham Ram</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>fordham</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="inlineStr">
+        <is>
+          <t>thefordhamram.com</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G62" s="21" t="n">
+        <v>6575</v>
+      </c>
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I62" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J62" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@fordham; 6575 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>Boston University</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>The Daily Free Press</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>freepress</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="inlineStr">
+        <is>
+          <t>dailyfreepress.com</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="n">
+        <v>2050</v>
+      </c>
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I63" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@freepress; 2050 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>Rutgers University, Camden</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>The Gleaner</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>gleaner</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="inlineStr">
+        <is>
+          <t>gleaner.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G64" s="21" t="n">
+        <v>373</v>
+      </c>
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I64" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 373 articles. systemd inactive. File: ~/Downloads/gleaner.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>Hamilton College</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>The Spectator</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>hamilton</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="inlineStr">
+        <is>
+          <t>hcspectator.com</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G65" s="21" t="n">
+        <v>2884</v>
+      </c>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I65" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 2884 articles. systemd inactive. File: ~/Downloads/hamilton.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>Tulane University of Louisiana</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>The Tulane Hullabaloo</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>hullabaloo</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="inlineStr">
+        <is>
+          <t>tulanehullabaloo.com</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G66" s="21" t="n">
+        <v>650</v>
+      </c>
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I66" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J66" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@hullabaloo; 650 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>Lafayette College</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>The Lafayette</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>lafayette</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="inlineStr">
+        <is>
+          <t>lafayettestudentnews.com</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G67" s="21" t="n">
+        <v>8987</v>
+      </c>
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I67" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J67" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 8987 articles. systemd inactive. File: ~/Downloads/lafayette.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>Lehigh University</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>The Brown and White</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>lehigh</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="inlineStr">
+        <is>
+          <t>thebrownandwhite.com</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="n">
+        <v>6399</v>
+      </c>
+      <c r="H68" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I68" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J68" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@lehigh; 6399 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>The Huntington News</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>northeastern</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="inlineStr">
+        <is>
+          <t>huntnewsnu.com</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="n">
+        <v>6298</v>
+      </c>
+      <c r="H69" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I69" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J69" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@northeastern; 6298 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>Furman Univeristy</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>The Paladin</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>paladin</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="inlineStr">
+        <is>
+          <t>thepaladin.news</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="n">
+        <v>2798</v>
+      </c>
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I70" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J70" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 2798 articles. systemd inactive. File: ~/Downloads/paladin.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>Pepperdine University</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>Pepperdine Graphic</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>pepperdine</t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="inlineStr">
+        <is>
+          <t>pepperdine-graphic.com</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G71" s="21" t="n">
+        <v>1036</v>
+      </c>
+      <c r="H71" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I71" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J71" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 1036 articles. systemd inactive. File: ~/Downloads/pepperdine.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>Washington and Lee Univeristy</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>The Ring-tum Phi</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>ringtumphi</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>ringtumphi.net</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G72" s="21" t="n">
+        <v>2673</v>
+      </c>
+      <c r="H72" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I72" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 2673 articles. systemd inactive. File: ~/Downloads/ringtumphi.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>Smith College</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>The Sophian</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>sophian</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>thesophian.com</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G73" s="21" t="n">
+        <v>2087</v>
+      </c>
+      <c r="H73" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I73" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 2087 articles. systemd inactive. File: ~/Downloads/sophian.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>Trinity University</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>The Trinitonian</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>trinitonian</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>trinitonian.com</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G74" s="21" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H74" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I74" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J74" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@trinitonian; 5500 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>Trinity College</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>The Trinity Tripod</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>tripod</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>trinitytripod.com</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G75" s="21" t="n">
+        <v>3925</v>
+      </c>
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I75" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J75" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 3925 articles. systemd inactive. File: ~/Downloads/tripod.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>Vanderbilt University</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>The Vanderbilt Hustler</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>vanderbilt</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>vanderbilthustler.com</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G76" s="21" t="n">
+        <v>6398</v>
+      </c>
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I76" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@vanderbilt; 6398 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>Villanova University</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>The Villanovan</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>villanova</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>villanovan.com</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G77" s="21" t="n">
+        <v>6745</v>
+      </c>
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I77" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@villanova; 6745 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t>Wake Forest University</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>Old Gold &amp; Black</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>wakeforest</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>wfuogb.com</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="G78" s="21" t="n">
+        <v>6482</v>
+      </c>
+      <c r="H78" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I78" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t>newspaper-scraper@wakeforest; 6482 articles as of 2026-10-13. systemd active on AWS VM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>Wellesley College</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>The Wellesley News</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>wellesley</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>thewellesleynews.com</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F79" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G79" s="21" t="n">
+        <v>4796</v>
+      </c>
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I79" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J79" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 4796 articles. systemd inactive. File: ~/Downloads/wellesley.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t>Wheaton College</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>The Wheaton Wire</t>
+        </is>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>wheatonwire</t>
+        </is>
+      </c>
+      <c r="D80" s="0" t="inlineStr">
+        <is>
+          <t>wheatonwire.com</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G80" s="21" t="n">
+        <v>947</v>
+      </c>
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I80" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J80" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 947 articles. systemd inactive. File: ~/Downloads/wheatonwire.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>Williams College</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>The Williams Record</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>williams</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="inlineStr">
+        <is>
+          <t>williamsrecord.com</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="n">
+        <v>4226</v>
+      </c>
+      <c r="H81" s="0" t="inlineStr">
+        <is>
+          <t>AWS VM</t>
+        </is>
+      </c>
+      <c r="I81" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J81" s="0" t="inlineStr">
+        <is>
+          <t>Finished as of 2026-10-13. 4226 articles. systemd inactive. File: ~/Downloads/williams.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>College of the Ozarks</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>The Outlook</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="I82" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>No dedicated student-paper site found. cofo.edu/News is institutional only (2026-10-13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Moody Bible Institute</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>The Moody Standard</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="I83" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Closed 2019 after 84 years. moodystandard.com DNS dead; historical archive only (2026-10-13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>United States Air Force Academy</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Academy Spirit</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="I84" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Print ended 2015. usafa.af.mil is institutional, not independent student paper (2026-10-13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>United States Military Academy at West Point</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pointer View</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>westpoint.edu</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>needs_adapter</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="I85" s="37" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Live: westpoint.edu/pointer-view. Historical: usmalibrary.contentdm. Needs adapter (2026-10-13).</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -4234,27 +4234,27 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>College of the Ozarks</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>The Outlook</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="0" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="0" t="inlineStr">
         <is>
           <t>excluded</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" s="0" t="inlineStr">
         <is>
           <t>research</t>
         </is>
@@ -4262,34 +4262,34 @@
       <c r="I82" s="37" t="n">
         <v>46308</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="0" t="inlineStr">
         <is>
           <t>No dedicated student-paper site found. cofo.edu/News is institutional only (2026-10-13).</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>Moody Bible Institute</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="0" t="inlineStr">
         <is>
           <t>The Moody Standard</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="0" t="inlineStr">
         <is>
           <t>Christian Colleges</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="0" t="inlineStr">
         <is>
           <t>excluded</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="0" t="inlineStr">
         <is>
           <t>research</t>
         </is>
@@ -4297,34 +4297,34 @@
       <c r="I83" s="37" t="n">
         <v>46308</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="0" t="inlineStr">
         <is>
           <t>Closed 2019 after 84 years. moodystandard.com DNS dead; historical archive only (2026-10-13).</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>United States Air Force Academy</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>Academy Spirit</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="0" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="0" t="inlineStr">
         <is>
           <t>excluded</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="0" t="inlineStr">
         <is>
           <t>research</t>
         </is>
@@ -4332,39 +4332,39 @@
       <c r="I84" s="37" t="n">
         <v>46308</v>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="0" t="inlineStr">
         <is>
           <t>Print ended 2015. usafa.af.mil is institutional, not independent student paper (2026-10-13).</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>United States Military Academy at West Point</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>Pointer View</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="0" t="inlineStr">
         <is>
           <t>westpoint.edu</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="0" t="inlineStr">
         <is>
           <t>Liberal Arts</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="0" t="inlineStr">
         <is>
           <t>needs_adapter</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="0" t="inlineStr">
         <is>
           <t>research</t>
         </is>
@@ -4372,9 +4372,150 @@
       <c r="I85" s="37" t="n">
         <v>46308</v>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="0" t="inlineStr">
         <is>
           <t>Live: westpoint.edu/pointer-view. Historical: usmalibrary.contentdm. Needs adapter (2026-10-13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t>Boston College</t>
+        </is>
+      </c>
+      <c r="B86" s="0" t="inlineStr">
+        <is>
+          <t>The Heights</t>
+        </is>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>bcheights.com</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t>t3.xlarge</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J86" s="0" t="inlineStr">
+        <is>
+          <t>Started wave21 full scrape 2026-10-13 (CAP 20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>Berea College</t>
+        </is>
+      </c>
+      <c r="B87" s="0" t="inlineStr">
+        <is>
+          <t>The Pinnacle</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>berea</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>pinnacle.berea.edu</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t>t3.xlarge</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J87" s="0" t="inlineStr">
+        <is>
+          <t>Started wave21 full scrape 2026-10-13 (CAP 20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>The University of the South</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>The Sewanee Purple</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>sewanee</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="inlineStr">
+        <is>
+          <t>thesewaneepurple.org</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t>t3.xlarge</t>
+        </is>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="inlineStr">
+        <is>
+          <t>Started wave21 full scrape 2026-10-13 (CAP 20).</t>
         </is>
       </c>
     </row>

--- a/data/targets_raw.xlsx
+++ b/data/targets_raw.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="19" min="1" max="1"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="J10" s="34" t="inlineStr">
         <is>
-          <t>Not cleared on the VM: homepage timeout, article pages HTTP 508. Crawl-delay 30; ~8.2k URLs. Retry from Mac, wait, or skip.</t>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
         </is>
       </c>
     </row>
@@ -1000,11 +1000,11 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G12" s="39" t="n">
-        <v>30994</v>
+        <v>33200</v>
       </c>
       <c r="H12" s="33" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="J12" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@hatchet; 30994 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@hatchet; 30994 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (33200 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -1048,11 +1048,11 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G13" s="39" t="n">
-        <v>30550</v>
+        <v>36807</v>
       </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="J13" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@stanford; 30550 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@stanford; 30550 articles as of 2026-10-13. systemd active on AWS VM. | Finished as of 2026-10-14. 36807 articles. File: ~/Downloads/stanford.csv</t>
         </is>
       </c>
     </row>
@@ -1096,11 +1096,11 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G14" s="39" t="n">
-        <v>30250</v>
+        <v>31890</v>
       </c>
       <c r="H14" s="33" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J14" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@marquette; 30250 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@marquette; 30250 articles as of 2026-10-13. systemd active on AWS VM. | Finished as of 2026-10-14. 31890 articles. File: ~/Downloads/marquette.csv</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
-          <t>National Universities | Public Universities</t>
+          <t>Public Universities</t>
         </is>
       </c>
       <c r="F22" s="33" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H22" s="33" t="inlineStr">
         <is>
-          <t>AWS VM</t>
+          <t>t3.xlarge</t>
         </is>
       </c>
       <c r="I22" s="35" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="J22" s="34" t="inlineStr">
         <is>
-          <t>newspaper-scraper@illini; 75850 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@illini; 75850 articles as of 2026-10-13. systemd active on AWS VM. | Still running as of 2026-10-14 (CAP 20).</t>
         </is>
       </c>
     </row>
@@ -1587,16 +1587,16 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>National Universities | Public Universities</t>
+          <t>Public Universities</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>56979</v>
+        <v>58600</v>
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@tarheel; 56979 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@tarheel; 56979 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (58600 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>University of Minnesota, Twin Cities</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
@@ -1731,16 +1731,16 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>National Universities | Public Universities</t>
+          <t>National Universities</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>53190</v>
+        <v>54761</v>
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@mndaily; 53190 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@mndaily; 53190 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (54761 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>Not cleared. VM 200-test HTTP 403 on /opinions/satire/; block cooldown. Probe of two news articles OK. Do not start full until a later 200-test passes.</t>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>AWS VM</t>
+          <t>t3.xlarge</t>
         </is>
       </c>
       <c r="I56" s="37" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@baylor; 4796 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@baylor; 4796 articles as of 2026-10-13. systemd active on AWS VM. | Still running as of 2026-10-14 (CAP 20).</t>
         </is>
       </c>
     </row>
@@ -3109,11 +3109,11 @@
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G58" s="21" t="n">
-        <v>7948</v>
+        <v>14989</v>
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@campustimes; 7948 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@campustimes; 7948 articles as of 2026-10-13. systemd active on AWS VM. | Finished as of 2026-10-14. 14989 articles. File: ~/Downloads/campustimes.csv</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>Finished as of 2026-10-13. 10125 articles. systemd inactive. File: ~/Downloads/case.csv</t>
+          <t>Finished as of 2026-10-13. 10125 articles. systemd inactive. File: ~/Downloads/case.csv | Finished as of 2026-10-14. 10125 articles. File: ~/Downloads/case.csv</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
-          <t>thefordhamram.com</t>
+          <t>fordhamram.com</t>
         </is>
       </c>
       <c r="E62" s="0" t="inlineStr">
@@ -3301,11 +3301,11 @@
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G62" s="21" t="n">
-        <v>6575</v>
+        <v>8902</v>
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@fordham; 6575 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@fordham; 6575 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (8902 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -3349,11 +3349,11 @@
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G63" s="21" t="n">
-        <v>2050</v>
+        <v>4379</v>
       </c>
       <c r="H63" s="0" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@freepress; 2050 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@freepress; 2050 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (4379 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t>Tulane University of Louisiana</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
@@ -3493,11 +3493,11 @@
       </c>
       <c r="F66" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G66" s="21" t="n">
-        <v>650</v>
+        <v>2991</v>
       </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@hullabaloo; 650 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@hullabaloo; 650 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (2991 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G68" s="21" t="n">
-        <v>6399</v>
+        <v>9739</v>
       </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@lehigh; 6399 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@lehigh; 6399 articles as of 2026-10-13. systemd active on AWS VM. | Finished as of 2026-10-14. 9739 articles. File: ~/Downloads/lehigh.csv</t>
         </is>
       </c>
     </row>
@@ -3637,11 +3637,11 @@
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G69" s="21" t="n">
-        <v>6298</v>
+        <v>8556</v>
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@northeastern; 6298 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@northeastern; 6298 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (8556 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>Finished as of 2026-10-13. 2798 articles. systemd inactive. File: ~/Downloads/paladin.csv</t>
+          <t>Finished as of 2026-10-13. 2798 articles. systemd inactive. File: ~/Downloads/paladin.csv | Finished as of 2026-10-14. 2798 articles. File: ~/Downloads/paladin.csv</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>Finished as of 2026-10-13. 2673 articles. systemd inactive. File: ~/Downloads/ringtumphi.csv</t>
+          <t>Finished as of 2026-10-13. 2673 articles. systemd inactive. File: ~/Downloads/ringtumphi.csv | Finished as of 2026-10-14. 2673 articles. File: ~/Downloads/ringtumphi.csv</t>
         </is>
       </c>
     </row>
@@ -3877,11 +3877,11 @@
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G74" s="21" t="n">
-        <v>5500</v>
+        <v>7754</v>
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@trinitonian; 5500 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@trinitonian; 5500 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (7754 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -3973,11 +3973,11 @@
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G76" s="21" t="n">
-        <v>6398</v>
+        <v>8660</v>
       </c>
       <c r="H76" s="0" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@vanderbilt; 6398 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@vanderbilt; 6398 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (8660 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -4021,11 +4021,11 @@
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="G77" s="21" t="n">
-        <v>6745</v>
+        <v>9110</v>
       </c>
       <c r="H77" s="0" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@villanova; 6745 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@villanova; 6745 articles as of 2026-10-13. systemd active on AWS VM. | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (9110 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -4069,11 +4069,11 @@
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>done</t>
         </is>
       </c>
       <c r="G78" s="21" t="n">
-        <v>6482</v>
+        <v>7837</v>
       </c>
       <c r="H78" s="0" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>newspaper-scraper@wakeforest; 6482 articles as of 2026-10-13. systemd active on AWS VM.</t>
+          <t>newspaper-scraper@wakeforest; 6482 articles as of 2026-10-13. systemd active on AWS VM. | Finished as of 2026-10-14. 7837 articles. File: ~/Downloads/wakeforest.csv</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>Finished as of 2026-10-13. 4796 articles. systemd inactive. File: ~/Downloads/wellesley.csv</t>
+          <t>Finished as of 2026-10-13. 4796 articles. systemd inactive. File: ~/Downloads/wellesley.csv | Finished as of 2026-10-14. 4796 articles. File: ~/Downloads/wellesley.csv</t>
         </is>
       </c>
     </row>
@@ -4406,8 +4406,11 @@
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="n">
+        <v>1210</v>
       </c>
       <c r="H86" s="0" t="inlineStr">
         <is>
@@ -4421,7 +4424,7 @@
       </c>
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>Started wave21 full scrape 2026-10-13 (CAP 20).</t>
+          <t>Started wave21 full scrape 2026-10-13 (CAP 20). | SITE BLOCKED exit-75 after 4x 403 cooldowns ~2026-10-14 02:36Z. Progress saved (1210 rows). Left alone for now.</t>
         </is>
       </c>
     </row>
@@ -4453,8 +4456,11 @@
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="n">
+        <v>874</v>
       </c>
       <c r="H87" s="0" t="inlineStr">
         <is>
@@ -4468,7 +4474,7 @@
       </c>
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>Started wave21 full scrape 2026-10-13 (CAP 20).</t>
+          <t>Started wave21 full scrape 2026-10-13 (CAP 20). | Finished as of 2026-10-14. 874 articles. File: ~/Downloads/berea.csv</t>
         </is>
       </c>
     </row>
@@ -4500,8 +4506,11 @@
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="n">
+        <v>3230</v>
       </c>
       <c r="H88" s="0" t="inlineStr">
         <is>
@@ -4515,7 +4524,469 @@
       </c>
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>Started wave21 full scrape 2026-10-13 (CAP 20).</t>
+          <t>Started wave21 full scrape 2026-10-13 (CAP 20). | Finished as of 2026-10-14. 3230 articles. File: ~/Downloads/sewanee.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Colby College</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>The Colby Echo</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>colby</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>colbyecho.news</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Colorado College</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>The Catalyst</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>catalyst</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>thecatalystnews.com</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>College of the Holy Cross</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>The Spire</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>holycross</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>hcspire.com</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Liberal Arts</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Wheaton College--Illinois</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>The Wheaton Record</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>wheatonrecord</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>thewheatonrecord.com</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Christian Colleges</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>University of Connecticut</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>The Daily Campus</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>dailycampus</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>dailycampus.com</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Florida International University</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PantherNOW</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>panthernow</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>panthernow.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Drexel University</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>The Triangle</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>triangle</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>thetriangle.org</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>The Ohio State University</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>The Lantern</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>lantern</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>thelantern.com</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Public Universities</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>The Battalion</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>batt</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>thebatt.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Washington University in St. Louis</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Student Life</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>studlife</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>studlife.com</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Santa Clara University</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>The Santa Clara</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>santaclara</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>thesantaclara.org</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>National Universities</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>queued</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Wave 22 staged 2026-10-14 (refill after 403 blocks; blocked SNO left alone).</t>
         </is>
       </c>
     </row>
